--- a/public/templates/equiwings-rider-import-template.xlsx
+++ b/public/templates/equiwings-rider-import-template.xlsx
@@ -202,116 +202,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Equiwings</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>REQUIRED
-Rider's first name. Required.</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>REQUIRED
-Rider's surname. Required.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>REQUIRED
-10-digit Indian mobile of the parent/rider. Required.
-Digits only — 9876543210. +91, spaces and 0-prefix are accepted and cleaned.
-Used for SMS/WhatsApp, so a wrong number means the family hears nothing.</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>REQUIRED
-Date of birth, exactly YYYY-MM-DD (e.g. 2014-08-23). Required.
-Type it as text. Do NOT let Excel reformat it.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-The RIDER's own email, if they have one. Usually blank for children.</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-STRONGLY RECOMMENDED — a parent's email address.
-This is where the indemnity signing link, the signed copy, monthly
-progress reports and portal login details are sent. Without it the
-family cannot be contacted by the system at all, and consent has to
-be collected on paper instead.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-Optional. Parent / guardian name.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-Optional. Parent's number, if different from the mobile column.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-Optional. male / female / other (m, f, o also accepted).</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-Optional. School name.</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-Optional. Class / grade — 5, V, Grade 5, XI-Science. Free text.</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-Optional. Section — A, B, etc.</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-Optional. YYYY-MM-DD. Defaults to the upload date if blank.</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-Optional but recommended — this is what makes attendance work.
-Must EXACTLY match a batch name at the centre you're uploading to.
-See the 'Batch names' sheet. An unknown name fails the whole upload.</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional
-Optional. 1-50. Only set this if the rider should be scheduled
-for a promotion exam at that level. Leave blank otherwise.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17708,7 +17598,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/public/templates/equiwings-rider-import-template.xlsx
+++ b/public/templates/equiwings-rider-import-template.xlsx
@@ -9,10 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riders" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch names" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Riders'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Riders'!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,14 +49,6 @@
     <font>
       <name val="Menlo"/>
       <color rgb="00444444"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <i val="1"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -105,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,16 +109,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1001"/>
+  <dimension ref="A1:N1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -509,8 +490,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -581,11 +561,6 @@
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>batch</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
           <t>level</t>
         </is>
       </c>
@@ -605,7 +580,6 @@
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -622,7 +596,6 @@
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -639,7 +612,6 @@
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -656,7 +628,6 @@
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -673,7 +644,6 @@
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -690,7 +660,6 @@
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
       <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -707,7 +676,6 @@
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
       <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -724,7 +692,6 @@
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -741,7 +708,6 @@
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
       <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -758,7 +724,6 @@
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
       <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -775,7 +740,6 @@
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
       <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -792,7 +756,6 @@
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -809,7 +772,6 @@
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
       <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -826,7 +788,6 @@
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
       <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -843,7 +804,6 @@
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
       <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -860,7 +820,6 @@
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
       <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -877,7 +836,6 @@
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n"/>
       <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -894,7 +852,6 @@
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -911,7 +868,6 @@
       <c r="L20" s="3" t="n"/>
       <c r="M20" s="3" t="n"/>
       <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -928,7 +884,6 @@
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3" t="n"/>
       <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -945,7 +900,6 @@
       <c r="L22" s="3" t="n"/>
       <c r="M22" s="3" t="n"/>
       <c r="N22" s="3" t="n"/>
-      <c r="O22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -962,7 +916,6 @@
       <c r="L23" s="3" t="n"/>
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -979,7 +932,6 @@
       <c r="L24" s="3" t="n"/>
       <c r="M24" s="3" t="n"/>
       <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -996,7 +948,6 @@
       <c r="L25" s="3" t="n"/>
       <c r="M25" s="3" t="n"/>
       <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -1013,7 +964,6 @@
       <c r="L26" s="3" t="n"/>
       <c r="M26" s="3" t="n"/>
       <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -1030,7 +980,6 @@
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
       <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -1047,7 +996,6 @@
       <c r="L28" s="3" t="n"/>
       <c r="M28" s="3" t="n"/>
       <c r="N28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -1064,7 +1012,6 @@
       <c r="L29" s="3" t="n"/>
       <c r="M29" s="3" t="n"/>
       <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -1081,7 +1028,6 @@
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="n"/>
       <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -1098,7 +1044,6 @@
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="n"/>
       <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -1115,7 +1060,6 @@
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="n"/>
       <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -1132,7 +1076,6 @@
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="n"/>
       <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -1149,7 +1092,6 @@
       <c r="L34" s="3" t="n"/>
       <c r="M34" s="3" t="n"/>
       <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -1166,7 +1108,6 @@
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -1183,7 +1124,6 @@
       <c r="L36" s="3" t="n"/>
       <c r="M36" s="3" t="n"/>
       <c r="N36" s="3" t="n"/>
-      <c r="O36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -1200,7 +1140,6 @@
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="3" t="n"/>
       <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -1217,7 +1156,6 @@
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n"/>
-      <c r="O38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -1234,7 +1172,6 @@
       <c r="L39" s="3" t="n"/>
       <c r="M39" s="3" t="n"/>
       <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -1251,7 +1188,6 @@
       <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n"/>
       <c r="N40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -1268,7 +1204,6 @@
       <c r="L41" s="3" t="n"/>
       <c r="M41" s="3" t="n"/>
       <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -1285,7 +1220,6 @@
       <c r="L42" s="3" t="n"/>
       <c r="M42" s="3" t="n"/>
       <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -1302,7 +1236,6 @@
       <c r="L43" s="3" t="n"/>
       <c r="M43" s="3" t="n"/>
       <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -1319,7 +1252,6 @@
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
       <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -1336,7 +1268,6 @@
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -1353,7 +1284,6 @@
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="n"/>
       <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -1370,7 +1300,6 @@
       <c r="L47" s="3" t="n"/>
       <c r="M47" s="3" t="n"/>
       <c r="N47" s="3" t="n"/>
-      <c r="O47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -1387,7 +1316,6 @@
       <c r="L48" s="3" t="n"/>
       <c r="M48" s="3" t="n"/>
       <c r="N48" s="3" t="n"/>
-      <c r="O48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -1404,7 +1332,6 @@
       <c r="L49" s="3" t="n"/>
       <c r="M49" s="3" t="n"/>
       <c r="N49" s="3" t="n"/>
-      <c r="O49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -1421,7 +1348,6 @@
       <c r="L50" s="3" t="n"/>
       <c r="M50" s="3" t="n"/>
       <c r="N50" s="3" t="n"/>
-      <c r="O50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -1438,7 +1364,6 @@
       <c r="L51" s="3" t="n"/>
       <c r="M51" s="3" t="n"/>
       <c r="N51" s="3" t="n"/>
-      <c r="O51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -1455,7 +1380,6 @@
       <c r="L52" s="3" t="n"/>
       <c r="M52" s="3" t="n"/>
       <c r="N52" s="3" t="n"/>
-      <c r="O52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -1472,7 +1396,6 @@
       <c r="L53" s="3" t="n"/>
       <c r="M53" s="3" t="n"/>
       <c r="N53" s="3" t="n"/>
-      <c r="O53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -1489,7 +1412,6 @@
       <c r="L54" s="3" t="n"/>
       <c r="M54" s="3" t="n"/>
       <c r="N54" s="3" t="n"/>
-      <c r="O54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -1506,7 +1428,6 @@
       <c r="L55" s="3" t="n"/>
       <c r="M55" s="3" t="n"/>
       <c r="N55" s="3" t="n"/>
-      <c r="O55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -1523,7 +1444,6 @@
       <c r="L56" s="3" t="n"/>
       <c r="M56" s="3" t="n"/>
       <c r="N56" s="3" t="n"/>
-      <c r="O56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n"/>
@@ -1540,7 +1460,6 @@
       <c r="L57" s="3" t="n"/>
       <c r="M57" s="3" t="n"/>
       <c r="N57" s="3" t="n"/>
-      <c r="O57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
@@ -1557,7 +1476,6 @@
       <c r="L58" s="3" t="n"/>
       <c r="M58" s="3" t="n"/>
       <c r="N58" s="3" t="n"/>
-      <c r="O58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
@@ -1574,7 +1492,6 @@
       <c r="L59" s="3" t="n"/>
       <c r="M59" s="3" t="n"/>
       <c r="N59" s="3" t="n"/>
-      <c r="O59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
@@ -1591,7 +1508,6 @@
       <c r="L60" s="3" t="n"/>
       <c r="M60" s="3" t="n"/>
       <c r="N60" s="3" t="n"/>
-      <c r="O60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
@@ -1608,7 +1524,6 @@
       <c r="L61" s="3" t="n"/>
       <c r="M61" s="3" t="n"/>
       <c r="N61" s="3" t="n"/>
-      <c r="O61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
@@ -1625,7 +1540,6 @@
       <c r="L62" s="3" t="n"/>
       <c r="M62" s="3" t="n"/>
       <c r="N62" s="3" t="n"/>
-      <c r="O62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
@@ -1642,7 +1556,6 @@
       <c r="L63" s="3" t="n"/>
       <c r="M63" s="3" t="n"/>
       <c r="N63" s="3" t="n"/>
-      <c r="O63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
@@ -1659,7 +1572,6 @@
       <c r="L64" s="3" t="n"/>
       <c r="M64" s="3" t="n"/>
       <c r="N64" s="3" t="n"/>
-      <c r="O64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
@@ -1676,7 +1588,6 @@
       <c r="L65" s="3" t="n"/>
       <c r="M65" s="3" t="n"/>
       <c r="N65" s="3" t="n"/>
-      <c r="O65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -1693,7 +1604,6 @@
       <c r="L66" s="3" t="n"/>
       <c r="M66" s="3" t="n"/>
       <c r="N66" s="3" t="n"/>
-      <c r="O66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
@@ -1710,7 +1620,6 @@
       <c r="L67" s="3" t="n"/>
       <c r="M67" s="3" t="n"/>
       <c r="N67" s="3" t="n"/>
-      <c r="O67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
@@ -1727,7 +1636,6 @@
       <c r="L68" s="3" t="n"/>
       <c r="M68" s="3" t="n"/>
       <c r="N68" s="3" t="n"/>
-      <c r="O68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n"/>
@@ -1744,7 +1652,6 @@
       <c r="L69" s="3" t="n"/>
       <c r="M69" s="3" t="n"/>
       <c r="N69" s="3" t="n"/>
-      <c r="O69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
@@ -1761,7 +1668,6 @@
       <c r="L70" s="3" t="n"/>
       <c r="M70" s="3" t="n"/>
       <c r="N70" s="3" t="n"/>
-      <c r="O70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -1778,7 +1684,6 @@
       <c r="L71" s="3" t="n"/>
       <c r="M71" s="3" t="n"/>
       <c r="N71" s="3" t="n"/>
-      <c r="O71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
@@ -1795,7 +1700,6 @@
       <c r="L72" s="3" t="n"/>
       <c r="M72" s="3" t="n"/>
       <c r="N72" s="3" t="n"/>
-      <c r="O72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
@@ -1812,7 +1716,6 @@
       <c r="L73" s="3" t="n"/>
       <c r="M73" s="3" t="n"/>
       <c r="N73" s="3" t="n"/>
-      <c r="O73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -1829,7 +1732,6 @@
       <c r="L74" s="3" t="n"/>
       <c r="M74" s="3" t="n"/>
       <c r="N74" s="3" t="n"/>
-      <c r="O74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
@@ -1846,7 +1748,6 @@
       <c r="L75" s="3" t="n"/>
       <c r="M75" s="3" t="n"/>
       <c r="N75" s="3" t="n"/>
-      <c r="O75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
@@ -1863,7 +1764,6 @@
       <c r="L76" s="3" t="n"/>
       <c r="M76" s="3" t="n"/>
       <c r="N76" s="3" t="n"/>
-      <c r="O76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
@@ -1880,7 +1780,6 @@
       <c r="L77" s="3" t="n"/>
       <c r="M77" s="3" t="n"/>
       <c r="N77" s="3" t="n"/>
-      <c r="O77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
@@ -1897,7 +1796,6 @@
       <c r="L78" s="3" t="n"/>
       <c r="M78" s="3" t="n"/>
       <c r="N78" s="3" t="n"/>
-      <c r="O78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
@@ -1914,7 +1812,6 @@
       <c r="L79" s="3" t="n"/>
       <c r="M79" s="3" t="n"/>
       <c r="N79" s="3" t="n"/>
-      <c r="O79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
@@ -1931,7 +1828,6 @@
       <c r="L80" s="3" t="n"/>
       <c r="M80" s="3" t="n"/>
       <c r="N80" s="3" t="n"/>
-      <c r="O80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
@@ -1948,7 +1844,6 @@
       <c r="L81" s="3" t="n"/>
       <c r="M81" s="3" t="n"/>
       <c r="N81" s="3" t="n"/>
-      <c r="O81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
@@ -1965,7 +1860,6 @@
       <c r="L82" s="3" t="n"/>
       <c r="M82" s="3" t="n"/>
       <c r="N82" s="3" t="n"/>
-      <c r="O82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
@@ -1982,7 +1876,6 @@
       <c r="L83" s="3" t="n"/>
       <c r="M83" s="3" t="n"/>
       <c r="N83" s="3" t="n"/>
-      <c r="O83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -1999,7 +1892,6 @@
       <c r="L84" s="3" t="n"/>
       <c r="M84" s="3" t="n"/>
       <c r="N84" s="3" t="n"/>
-      <c r="O84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
@@ -2016,7 +1908,6 @@
       <c r="L85" s="3" t="n"/>
       <c r="M85" s="3" t="n"/>
       <c r="N85" s="3" t="n"/>
-      <c r="O85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
@@ -2033,7 +1924,6 @@
       <c r="L86" s="3" t="n"/>
       <c r="M86" s="3" t="n"/>
       <c r="N86" s="3" t="n"/>
-      <c r="O86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n"/>
@@ -2050,7 +1940,6 @@
       <c r="L87" s="3" t="n"/>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
-      <c r="O87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -2067,7 +1956,6 @@
       <c r="L88" s="3" t="n"/>
       <c r="M88" s="3" t="n"/>
       <c r="N88" s="3" t="n"/>
-      <c r="O88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
@@ -2084,7 +1972,6 @@
       <c r="L89" s="3" t="n"/>
       <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
-      <c r="O89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -2101,7 +1988,6 @@
       <c r="L90" s="3" t="n"/>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
-      <c r="O90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -2118,7 +2004,6 @@
       <c r="L91" s="3" t="n"/>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
-      <c r="O91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -2135,7 +2020,6 @@
       <c r="L92" s="3" t="n"/>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
-      <c r="O92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n"/>
@@ -2152,7 +2036,6 @@
       <c r="L93" s="3" t="n"/>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>
-      <c r="O93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -2169,7 +2052,6 @@
       <c r="L94" s="3" t="n"/>
       <c r="M94" s="3" t="n"/>
       <c r="N94" s="3" t="n"/>
-      <c r="O94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -2186,7 +2068,6 @@
       <c r="L95" s="3" t="n"/>
       <c r="M95" s="3" t="n"/>
       <c r="N95" s="3" t="n"/>
-      <c r="O95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -2203,7 +2084,6 @@
       <c r="L96" s="3" t="n"/>
       <c r="M96" s="3" t="n"/>
       <c r="N96" s="3" t="n"/>
-      <c r="O96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
@@ -2220,7 +2100,6 @@
       <c r="L97" s="3" t="n"/>
       <c r="M97" s="3" t="n"/>
       <c r="N97" s="3" t="n"/>
-      <c r="O97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
@@ -2237,7 +2116,6 @@
       <c r="L98" s="3" t="n"/>
       <c r="M98" s="3" t="n"/>
       <c r="N98" s="3" t="n"/>
-      <c r="O98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
@@ -2254,7 +2132,6 @@
       <c r="L99" s="3" t="n"/>
       <c r="M99" s="3" t="n"/>
       <c r="N99" s="3" t="n"/>
-      <c r="O99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -2271,7 +2148,6 @@
       <c r="L100" s="3" t="n"/>
       <c r="M100" s="3" t="n"/>
       <c r="N100" s="3" t="n"/>
-      <c r="O100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
@@ -2288,7 +2164,6 @@
       <c r="L101" s="3" t="n"/>
       <c r="M101" s="3" t="n"/>
       <c r="N101" s="3" t="n"/>
-      <c r="O101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -2305,7 +2180,6 @@
       <c r="L102" s="3" t="n"/>
       <c r="M102" s="3" t="n"/>
       <c r="N102" s="3" t="n"/>
-      <c r="O102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
@@ -2322,7 +2196,6 @@
       <c r="L103" s="3" t="n"/>
       <c r="M103" s="3" t="n"/>
       <c r="N103" s="3" t="n"/>
-      <c r="O103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -2339,7 +2212,6 @@
       <c r="L104" s="3" t="n"/>
       <c r="M104" s="3" t="n"/>
       <c r="N104" s="3" t="n"/>
-      <c r="O104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
@@ -2356,7 +2228,6 @@
       <c r="L105" s="3" t="n"/>
       <c r="M105" s="3" t="n"/>
       <c r="N105" s="3" t="n"/>
-      <c r="O105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -2373,7 +2244,6 @@
       <c r="L106" s="3" t="n"/>
       <c r="M106" s="3" t="n"/>
       <c r="N106" s="3" t="n"/>
-      <c r="O106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
@@ -2390,7 +2260,6 @@
       <c r="L107" s="3" t="n"/>
       <c r="M107" s="3" t="n"/>
       <c r="N107" s="3" t="n"/>
-      <c r="O107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -2407,7 +2276,6 @@
       <c r="L108" s="3" t="n"/>
       <c r="M108" s="3" t="n"/>
       <c r="N108" s="3" t="n"/>
-      <c r="O108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
@@ -2424,7 +2292,6 @@
       <c r="L109" s="3" t="n"/>
       <c r="M109" s="3" t="n"/>
       <c r="N109" s="3" t="n"/>
-      <c r="O109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
@@ -2441,7 +2308,6 @@
       <c r="L110" s="3" t="n"/>
       <c r="M110" s="3" t="n"/>
       <c r="N110" s="3" t="n"/>
-      <c r="O110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
@@ -2458,7 +2324,6 @@
       <c r="L111" s="3" t="n"/>
       <c r="M111" s="3" t="n"/>
       <c r="N111" s="3" t="n"/>
-      <c r="O111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -2475,7 +2340,6 @@
       <c r="L112" s="3" t="n"/>
       <c r="M112" s="3" t="n"/>
       <c r="N112" s="3" t="n"/>
-      <c r="O112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
@@ -2492,7 +2356,6 @@
       <c r="L113" s="3" t="n"/>
       <c r="M113" s="3" t="n"/>
       <c r="N113" s="3" t="n"/>
-      <c r="O113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -2509,7 +2372,6 @@
       <c r="L114" s="3" t="n"/>
       <c r="M114" s="3" t="n"/>
       <c r="N114" s="3" t="n"/>
-      <c r="O114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
@@ -2526,7 +2388,6 @@
       <c r="L115" s="3" t="n"/>
       <c r="M115" s="3" t="n"/>
       <c r="N115" s="3" t="n"/>
-      <c r="O115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -2543,7 +2404,6 @@
       <c r="L116" s="3" t="n"/>
       <c r="M116" s="3" t="n"/>
       <c r="N116" s="3" t="n"/>
-      <c r="O116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
@@ -2560,7 +2420,6 @@
       <c r="L117" s="3" t="n"/>
       <c r="M117" s="3" t="n"/>
       <c r="N117" s="3" t="n"/>
-      <c r="O117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -2577,7 +2436,6 @@
       <c r="L118" s="3" t="n"/>
       <c r="M118" s="3" t="n"/>
       <c r="N118" s="3" t="n"/>
-      <c r="O118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
@@ -2594,7 +2452,6 @@
       <c r="L119" s="3" t="n"/>
       <c r="M119" s="3" t="n"/>
       <c r="N119" s="3" t="n"/>
-      <c r="O119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -2611,7 +2468,6 @@
       <c r="L120" s="3" t="n"/>
       <c r="M120" s="3" t="n"/>
       <c r="N120" s="3" t="n"/>
-      <c r="O120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
@@ -2628,7 +2484,6 @@
       <c r="L121" s="3" t="n"/>
       <c r="M121" s="3" t="n"/>
       <c r="N121" s="3" t="n"/>
-      <c r="O121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -2645,7 +2500,6 @@
       <c r="L122" s="3" t="n"/>
       <c r="M122" s="3" t="n"/>
       <c r="N122" s="3" t="n"/>
-      <c r="O122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
@@ -2662,7 +2516,6 @@
       <c r="L123" s="3" t="n"/>
       <c r="M123" s="3" t="n"/>
       <c r="N123" s="3" t="n"/>
-      <c r="O123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -2679,7 +2532,6 @@
       <c r="L124" s="3" t="n"/>
       <c r="M124" s="3" t="n"/>
       <c r="N124" s="3" t="n"/>
-      <c r="O124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
@@ -2696,7 +2548,6 @@
       <c r="L125" s="3" t="n"/>
       <c r="M125" s="3" t="n"/>
       <c r="N125" s="3" t="n"/>
-      <c r="O125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -2713,7 +2564,6 @@
       <c r="L126" s="3" t="n"/>
       <c r="M126" s="3" t="n"/>
       <c r="N126" s="3" t="n"/>
-      <c r="O126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -2730,7 +2580,6 @@
       <c r="L127" s="3" t="n"/>
       <c r="M127" s="3" t="n"/>
       <c r="N127" s="3" t="n"/>
-      <c r="O127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -2747,7 +2596,6 @@
       <c r="L128" s="3" t="n"/>
       <c r="M128" s="3" t="n"/>
       <c r="N128" s="3" t="n"/>
-      <c r="O128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
@@ -2764,7 +2612,6 @@
       <c r="L129" s="3" t="n"/>
       <c r="M129" s="3" t="n"/>
       <c r="N129" s="3" t="n"/>
-      <c r="O129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -2781,7 +2628,6 @@
       <c r="L130" s="3" t="n"/>
       <c r="M130" s="3" t="n"/>
       <c r="N130" s="3" t="n"/>
-      <c r="O130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
@@ -2798,7 +2644,6 @@
       <c r="L131" s="3" t="n"/>
       <c r="M131" s="3" t="n"/>
       <c r="N131" s="3" t="n"/>
-      <c r="O131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -2815,7 +2660,6 @@
       <c r="L132" s="3" t="n"/>
       <c r="M132" s="3" t="n"/>
       <c r="N132" s="3" t="n"/>
-      <c r="O132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
@@ -2832,7 +2676,6 @@
       <c r="L133" s="3" t="n"/>
       <c r="M133" s="3" t="n"/>
       <c r="N133" s="3" t="n"/>
-      <c r="O133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -2849,7 +2692,6 @@
       <c r="L134" s="3" t="n"/>
       <c r="M134" s="3" t="n"/>
       <c r="N134" s="3" t="n"/>
-      <c r="O134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
@@ -2866,7 +2708,6 @@
       <c r="L135" s="3" t="n"/>
       <c r="M135" s="3" t="n"/>
       <c r="N135" s="3" t="n"/>
-      <c r="O135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
@@ -2883,7 +2724,6 @@
       <c r="L136" s="3" t="n"/>
       <c r="M136" s="3" t="n"/>
       <c r="N136" s="3" t="n"/>
-      <c r="O136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
@@ -2900,7 +2740,6 @@
       <c r="L137" s="3" t="n"/>
       <c r="M137" s="3" t="n"/>
       <c r="N137" s="3" t="n"/>
-      <c r="O137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
@@ -2917,7 +2756,6 @@
       <c r="L138" s="3" t="n"/>
       <c r="M138" s="3" t="n"/>
       <c r="N138" s="3" t="n"/>
-      <c r="O138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
@@ -2934,7 +2772,6 @@
       <c r="L139" s="3" t="n"/>
       <c r="M139" s="3" t="n"/>
       <c r="N139" s="3" t="n"/>
-      <c r="O139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -2951,7 +2788,6 @@
       <c r="L140" s="3" t="n"/>
       <c r="M140" s="3" t="n"/>
       <c r="N140" s="3" t="n"/>
-      <c r="O140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
@@ -2968,7 +2804,6 @@
       <c r="L141" s="3" t="n"/>
       <c r="M141" s="3" t="n"/>
       <c r="N141" s="3" t="n"/>
-      <c r="O141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -2985,7 +2820,6 @@
       <c r="L142" s="3" t="n"/>
       <c r="M142" s="3" t="n"/>
       <c r="N142" s="3" t="n"/>
-      <c r="O142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
@@ -3002,7 +2836,6 @@
       <c r="L143" s="3" t="n"/>
       <c r="M143" s="3" t="n"/>
       <c r="N143" s="3" t="n"/>
-      <c r="O143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -3019,7 +2852,6 @@
       <c r="L144" s="3" t="n"/>
       <c r="M144" s="3" t="n"/>
       <c r="N144" s="3" t="n"/>
-      <c r="O144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
@@ -3036,7 +2868,6 @@
       <c r="L145" s="3" t="n"/>
       <c r="M145" s="3" t="n"/>
       <c r="N145" s="3" t="n"/>
-      <c r="O145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -3053,7 +2884,6 @@
       <c r="L146" s="3" t="n"/>
       <c r="M146" s="3" t="n"/>
       <c r="N146" s="3" t="n"/>
-      <c r="O146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
@@ -3070,7 +2900,6 @@
       <c r="L147" s="3" t="n"/>
       <c r="M147" s="3" t="n"/>
       <c r="N147" s="3" t="n"/>
-      <c r="O147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -3087,7 +2916,6 @@
       <c r="L148" s="3" t="n"/>
       <c r="M148" s="3" t="n"/>
       <c r="N148" s="3" t="n"/>
-      <c r="O148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
@@ -3104,7 +2932,6 @@
       <c r="L149" s="3" t="n"/>
       <c r="M149" s="3" t="n"/>
       <c r="N149" s="3" t="n"/>
-      <c r="O149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -3121,7 +2948,6 @@
       <c r="L150" s="3" t="n"/>
       <c r="M150" s="3" t="n"/>
       <c r="N150" s="3" t="n"/>
-      <c r="O150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
@@ -3138,7 +2964,6 @@
       <c r="L151" s="3" t="n"/>
       <c r="M151" s="3" t="n"/>
       <c r="N151" s="3" t="n"/>
-      <c r="O151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -3155,7 +2980,6 @@
       <c r="L152" s="3" t="n"/>
       <c r="M152" s="3" t="n"/>
       <c r="N152" s="3" t="n"/>
-      <c r="O152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n"/>
@@ -3172,7 +2996,6 @@
       <c r="L153" s="3" t="n"/>
       <c r="M153" s="3" t="n"/>
       <c r="N153" s="3" t="n"/>
-      <c r="O153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -3189,7 +3012,6 @@
       <c r="L154" s="3" t="n"/>
       <c r="M154" s="3" t="n"/>
       <c r="N154" s="3" t="n"/>
-      <c r="O154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
@@ -3206,7 +3028,6 @@
       <c r="L155" s="3" t="n"/>
       <c r="M155" s="3" t="n"/>
       <c r="N155" s="3" t="n"/>
-      <c r="O155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -3223,7 +3044,6 @@
       <c r="L156" s="3" t="n"/>
       <c r="M156" s="3" t="n"/>
       <c r="N156" s="3" t="n"/>
-      <c r="O156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n"/>
@@ -3240,7 +3060,6 @@
       <c r="L157" s="3" t="n"/>
       <c r="M157" s="3" t="n"/>
       <c r="N157" s="3" t="n"/>
-      <c r="O157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
@@ -3257,7 +3076,6 @@
       <c r="L158" s="3" t="n"/>
       <c r="M158" s="3" t="n"/>
       <c r="N158" s="3" t="n"/>
-      <c r="O158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n"/>
@@ -3274,7 +3092,6 @@
       <c r="L159" s="3" t="n"/>
       <c r="M159" s="3" t="n"/>
       <c r="N159" s="3" t="n"/>
-      <c r="O159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
@@ -3291,7 +3108,6 @@
       <c r="L160" s="3" t="n"/>
       <c r="M160" s="3" t="n"/>
       <c r="N160" s="3" t="n"/>
-      <c r="O160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n"/>
@@ -3308,7 +3124,6 @@
       <c r="L161" s="3" t="n"/>
       <c r="M161" s="3" t="n"/>
       <c r="N161" s="3" t="n"/>
-      <c r="O161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
@@ -3325,7 +3140,6 @@
       <c r="L162" s="3" t="n"/>
       <c r="M162" s="3" t="n"/>
       <c r="N162" s="3" t="n"/>
-      <c r="O162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n"/>
@@ -3342,7 +3156,6 @@
       <c r="L163" s="3" t="n"/>
       <c r="M163" s="3" t="n"/>
       <c r="N163" s="3" t="n"/>
-      <c r="O163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
@@ -3359,7 +3172,6 @@
       <c r="L164" s="3" t="n"/>
       <c r="M164" s="3" t="n"/>
       <c r="N164" s="3" t="n"/>
-      <c r="O164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n"/>
@@ -3376,7 +3188,6 @@
       <c r="L165" s="3" t="n"/>
       <c r="M165" s="3" t="n"/>
       <c r="N165" s="3" t="n"/>
-      <c r="O165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
@@ -3393,7 +3204,6 @@
       <c r="L166" s="3" t="n"/>
       <c r="M166" s="3" t="n"/>
       <c r="N166" s="3" t="n"/>
-      <c r="O166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n"/>
@@ -3410,7 +3220,6 @@
       <c r="L167" s="3" t="n"/>
       <c r="M167" s="3" t="n"/>
       <c r="N167" s="3" t="n"/>
-      <c r="O167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
@@ -3427,7 +3236,6 @@
       <c r="L168" s="3" t="n"/>
       <c r="M168" s="3" t="n"/>
       <c r="N168" s="3" t="n"/>
-      <c r="O168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n"/>
@@ -3444,7 +3252,6 @@
       <c r="L169" s="3" t="n"/>
       <c r="M169" s="3" t="n"/>
       <c r="N169" s="3" t="n"/>
-      <c r="O169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n"/>
@@ -3461,7 +3268,6 @@
       <c r="L170" s="3" t="n"/>
       <c r="M170" s="3" t="n"/>
       <c r="N170" s="3" t="n"/>
-      <c r="O170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n"/>
@@ -3478,7 +3284,6 @@
       <c r="L171" s="3" t="n"/>
       <c r="M171" s="3" t="n"/>
       <c r="N171" s="3" t="n"/>
-      <c r="O171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n"/>
@@ -3495,7 +3300,6 @@
       <c r="L172" s="3" t="n"/>
       <c r="M172" s="3" t="n"/>
       <c r="N172" s="3" t="n"/>
-      <c r="O172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n"/>
@@ -3512,7 +3316,6 @@
       <c r="L173" s="3" t="n"/>
       <c r="M173" s="3" t="n"/>
       <c r="N173" s="3" t="n"/>
-      <c r="O173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n"/>
@@ -3529,7 +3332,6 @@
       <c r="L174" s="3" t="n"/>
       <c r="M174" s="3" t="n"/>
       <c r="N174" s="3" t="n"/>
-      <c r="O174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n"/>
@@ -3546,7 +3348,6 @@
       <c r="L175" s="3" t="n"/>
       <c r="M175" s="3" t="n"/>
       <c r="N175" s="3" t="n"/>
-      <c r="O175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n"/>
@@ -3563,7 +3364,6 @@
       <c r="L176" s="3" t="n"/>
       <c r="M176" s="3" t="n"/>
       <c r="N176" s="3" t="n"/>
-      <c r="O176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n"/>
@@ -3580,7 +3380,6 @@
       <c r="L177" s="3" t="n"/>
       <c r="M177" s="3" t="n"/>
       <c r="N177" s="3" t="n"/>
-      <c r="O177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n"/>
@@ -3597,7 +3396,6 @@
       <c r="L178" s="3" t="n"/>
       <c r="M178" s="3" t="n"/>
       <c r="N178" s="3" t="n"/>
-      <c r="O178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n"/>
@@ -3614,7 +3412,6 @@
       <c r="L179" s="3" t="n"/>
       <c r="M179" s="3" t="n"/>
       <c r="N179" s="3" t="n"/>
-      <c r="O179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n"/>
@@ -3631,7 +3428,6 @@
       <c r="L180" s="3" t="n"/>
       <c r="M180" s="3" t="n"/>
       <c r="N180" s="3" t="n"/>
-      <c r="O180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n"/>
@@ -3648,7 +3444,6 @@
       <c r="L181" s="3" t="n"/>
       <c r="M181" s="3" t="n"/>
       <c r="N181" s="3" t="n"/>
-      <c r="O181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n"/>
@@ -3665,7 +3460,6 @@
       <c r="L182" s="3" t="n"/>
       <c r="M182" s="3" t="n"/>
       <c r="N182" s="3" t="n"/>
-      <c r="O182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n"/>
@@ -3682,7 +3476,6 @@
       <c r="L183" s="3" t="n"/>
       <c r="M183" s="3" t="n"/>
       <c r="N183" s="3" t="n"/>
-      <c r="O183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n"/>
@@ -3699,7 +3492,6 @@
       <c r="L184" s="3" t="n"/>
       <c r="M184" s="3" t="n"/>
       <c r="N184" s="3" t="n"/>
-      <c r="O184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n"/>
@@ -3716,7 +3508,6 @@
       <c r="L185" s="3" t="n"/>
       <c r="M185" s="3" t="n"/>
       <c r="N185" s="3" t="n"/>
-      <c r="O185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n"/>
@@ -3733,7 +3524,6 @@
       <c r="L186" s="3" t="n"/>
       <c r="M186" s="3" t="n"/>
       <c r="N186" s="3" t="n"/>
-      <c r="O186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n"/>
@@ -3750,7 +3540,6 @@
       <c r="L187" s="3" t="n"/>
       <c r="M187" s="3" t="n"/>
       <c r="N187" s="3" t="n"/>
-      <c r="O187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n"/>
@@ -3767,7 +3556,6 @@
       <c r="L188" s="3" t="n"/>
       <c r="M188" s="3" t="n"/>
       <c r="N188" s="3" t="n"/>
-      <c r="O188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n"/>
@@ -3784,7 +3572,6 @@
       <c r="L189" s="3" t="n"/>
       <c r="M189" s="3" t="n"/>
       <c r="N189" s="3" t="n"/>
-      <c r="O189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n"/>
@@ -3801,7 +3588,6 @@
       <c r="L190" s="3" t="n"/>
       <c r="M190" s="3" t="n"/>
       <c r="N190" s="3" t="n"/>
-      <c r="O190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n"/>
@@ -3818,7 +3604,6 @@
       <c r="L191" s="3" t="n"/>
       <c r="M191" s="3" t="n"/>
       <c r="N191" s="3" t="n"/>
-      <c r="O191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n"/>
@@ -3835,7 +3620,6 @@
       <c r="L192" s="3" t="n"/>
       <c r="M192" s="3" t="n"/>
       <c r="N192" s="3" t="n"/>
-      <c r="O192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n"/>
@@ -3852,7 +3636,6 @@
       <c r="L193" s="3" t="n"/>
       <c r="M193" s="3" t="n"/>
       <c r="N193" s="3" t="n"/>
-      <c r="O193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n"/>
@@ -3869,7 +3652,6 @@
       <c r="L194" s="3" t="n"/>
       <c r="M194" s="3" t="n"/>
       <c r="N194" s="3" t="n"/>
-      <c r="O194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n"/>
@@ -3886,7 +3668,6 @@
       <c r="L195" s="3" t="n"/>
       <c r="M195" s="3" t="n"/>
       <c r="N195" s="3" t="n"/>
-      <c r="O195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n"/>
@@ -3903,7 +3684,6 @@
       <c r="L196" s="3" t="n"/>
       <c r="M196" s="3" t="n"/>
       <c r="N196" s="3" t="n"/>
-      <c r="O196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n"/>
@@ -3920,7 +3700,6 @@
       <c r="L197" s="3" t="n"/>
       <c r="M197" s="3" t="n"/>
       <c r="N197" s="3" t="n"/>
-      <c r="O197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n"/>
@@ -3937,7 +3716,6 @@
       <c r="L198" s="3" t="n"/>
       <c r="M198" s="3" t="n"/>
       <c r="N198" s="3" t="n"/>
-      <c r="O198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n"/>
@@ -3954,7 +3732,6 @@
       <c r="L199" s="3" t="n"/>
       <c r="M199" s="3" t="n"/>
       <c r="N199" s="3" t="n"/>
-      <c r="O199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n"/>
@@ -3971,7 +3748,6 @@
       <c r="L200" s="3" t="n"/>
       <c r="M200" s="3" t="n"/>
       <c r="N200" s="3" t="n"/>
-      <c r="O200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n"/>
@@ -3988,7 +3764,6 @@
       <c r="L201" s="3" t="n"/>
       <c r="M201" s="3" t="n"/>
       <c r="N201" s="3" t="n"/>
-      <c r="O201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n"/>
@@ -4005,7 +3780,6 @@
       <c r="L202" s="3" t="n"/>
       <c r="M202" s="3" t="n"/>
       <c r="N202" s="3" t="n"/>
-      <c r="O202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n"/>
@@ -4022,7 +3796,6 @@
       <c r="L203" s="3" t="n"/>
       <c r="M203" s="3" t="n"/>
       <c r="N203" s="3" t="n"/>
-      <c r="O203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n"/>
@@ -4039,7 +3812,6 @@
       <c r="L204" s="3" t="n"/>
       <c r="M204" s="3" t="n"/>
       <c r="N204" s="3" t="n"/>
-      <c r="O204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n"/>
@@ -4056,7 +3828,6 @@
       <c r="L205" s="3" t="n"/>
       <c r="M205" s="3" t="n"/>
       <c r="N205" s="3" t="n"/>
-      <c r="O205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n"/>
@@ -4073,7 +3844,6 @@
       <c r="L206" s="3" t="n"/>
       <c r="M206" s="3" t="n"/>
       <c r="N206" s="3" t="n"/>
-      <c r="O206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n"/>
@@ -4090,7 +3860,6 @@
       <c r="L207" s="3" t="n"/>
       <c r="M207" s="3" t="n"/>
       <c r="N207" s="3" t="n"/>
-      <c r="O207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n"/>
@@ -4107,7 +3876,6 @@
       <c r="L208" s="3" t="n"/>
       <c r="M208" s="3" t="n"/>
       <c r="N208" s="3" t="n"/>
-      <c r="O208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n"/>
@@ -4124,7 +3892,6 @@
       <c r="L209" s="3" t="n"/>
       <c r="M209" s="3" t="n"/>
       <c r="N209" s="3" t="n"/>
-      <c r="O209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n"/>
@@ -4141,7 +3908,6 @@
       <c r="L210" s="3" t="n"/>
       <c r="M210" s="3" t="n"/>
       <c r="N210" s="3" t="n"/>
-      <c r="O210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n"/>
@@ -4158,7 +3924,6 @@
       <c r="L211" s="3" t="n"/>
       <c r="M211" s="3" t="n"/>
       <c r="N211" s="3" t="n"/>
-      <c r="O211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n"/>
@@ -4175,7 +3940,6 @@
       <c r="L212" s="3" t="n"/>
       <c r="M212" s="3" t="n"/>
       <c r="N212" s="3" t="n"/>
-      <c r="O212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n"/>
@@ -4192,7 +3956,6 @@
       <c r="L213" s="3" t="n"/>
       <c r="M213" s="3" t="n"/>
       <c r="N213" s="3" t="n"/>
-      <c r="O213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n"/>
@@ -4209,7 +3972,6 @@
       <c r="L214" s="3" t="n"/>
       <c r="M214" s="3" t="n"/>
       <c r="N214" s="3" t="n"/>
-      <c r="O214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n"/>
@@ -4226,7 +3988,6 @@
       <c r="L215" s="3" t="n"/>
       <c r="M215" s="3" t="n"/>
       <c r="N215" s="3" t="n"/>
-      <c r="O215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n"/>
@@ -4243,7 +4004,6 @@
       <c r="L216" s="3" t="n"/>
       <c r="M216" s="3" t="n"/>
       <c r="N216" s="3" t="n"/>
-      <c r="O216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="n"/>
@@ -4260,7 +4020,6 @@
       <c r="L217" s="3" t="n"/>
       <c r="M217" s="3" t="n"/>
       <c r="N217" s="3" t="n"/>
-      <c r="O217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n"/>
@@ -4277,7 +4036,6 @@
       <c r="L218" s="3" t="n"/>
       <c r="M218" s="3" t="n"/>
       <c r="N218" s="3" t="n"/>
-      <c r="O218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n"/>
@@ -4294,7 +4052,6 @@
       <c r="L219" s="3" t="n"/>
       <c r="M219" s="3" t="n"/>
       <c r="N219" s="3" t="n"/>
-      <c r="O219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n"/>
@@ -4311,7 +4068,6 @@
       <c r="L220" s="3" t="n"/>
       <c r="M220" s="3" t="n"/>
       <c r="N220" s="3" t="n"/>
-      <c r="O220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n"/>
@@ -4328,7 +4084,6 @@
       <c r="L221" s="3" t="n"/>
       <c r="M221" s="3" t="n"/>
       <c r="N221" s="3" t="n"/>
-      <c r="O221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n"/>
@@ -4345,7 +4100,6 @@
       <c r="L222" s="3" t="n"/>
       <c r="M222" s="3" t="n"/>
       <c r="N222" s="3" t="n"/>
-      <c r="O222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="n"/>
@@ -4362,7 +4116,6 @@
       <c r="L223" s="3" t="n"/>
       <c r="M223" s="3" t="n"/>
       <c r="N223" s="3" t="n"/>
-      <c r="O223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n"/>
@@ -4379,7 +4132,6 @@
       <c r="L224" s="3" t="n"/>
       <c r="M224" s="3" t="n"/>
       <c r="N224" s="3" t="n"/>
-      <c r="O224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n"/>
@@ -4396,7 +4148,6 @@
       <c r="L225" s="3" t="n"/>
       <c r="M225" s="3" t="n"/>
       <c r="N225" s="3" t="n"/>
-      <c r="O225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n"/>
@@ -4413,7 +4164,6 @@
       <c r="L226" s="3" t="n"/>
       <c r="M226" s="3" t="n"/>
       <c r="N226" s="3" t="n"/>
-      <c r="O226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n"/>
@@ -4430,7 +4180,6 @@
       <c r="L227" s="3" t="n"/>
       <c r="M227" s="3" t="n"/>
       <c r="N227" s="3" t="n"/>
-      <c r="O227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n"/>
@@ -4447,7 +4196,6 @@
       <c r="L228" s="3" t="n"/>
       <c r="M228" s="3" t="n"/>
       <c r="N228" s="3" t="n"/>
-      <c r="O228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n"/>
@@ -4464,7 +4212,6 @@
       <c r="L229" s="3" t="n"/>
       <c r="M229" s="3" t="n"/>
       <c r="N229" s="3" t="n"/>
-      <c r="O229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n"/>
@@ -4481,7 +4228,6 @@
       <c r="L230" s="3" t="n"/>
       <c r="M230" s="3" t="n"/>
       <c r="N230" s="3" t="n"/>
-      <c r="O230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n"/>
@@ -4498,7 +4244,6 @@
       <c r="L231" s="3" t="n"/>
       <c r="M231" s="3" t="n"/>
       <c r="N231" s="3" t="n"/>
-      <c r="O231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n"/>
@@ -4515,7 +4260,6 @@
       <c r="L232" s="3" t="n"/>
       <c r="M232" s="3" t="n"/>
       <c r="N232" s="3" t="n"/>
-      <c r="O232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="n"/>
@@ -4532,7 +4276,6 @@
       <c r="L233" s="3" t="n"/>
       <c r="M233" s="3" t="n"/>
       <c r="N233" s="3" t="n"/>
-      <c r="O233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n"/>
@@ -4549,7 +4292,6 @@
       <c r="L234" s="3" t="n"/>
       <c r="M234" s="3" t="n"/>
       <c r="N234" s="3" t="n"/>
-      <c r="O234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="n"/>
@@ -4566,7 +4308,6 @@
       <c r="L235" s="3" t="n"/>
       <c r="M235" s="3" t="n"/>
       <c r="N235" s="3" t="n"/>
-      <c r="O235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n"/>
@@ -4583,7 +4324,6 @@
       <c r="L236" s="3" t="n"/>
       <c r="M236" s="3" t="n"/>
       <c r="N236" s="3" t="n"/>
-      <c r="O236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n"/>
@@ -4600,7 +4340,6 @@
       <c r="L237" s="3" t="n"/>
       <c r="M237" s="3" t="n"/>
       <c r="N237" s="3" t="n"/>
-      <c r="O237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n"/>
@@ -4617,7 +4356,6 @@
       <c r="L238" s="3" t="n"/>
       <c r="M238" s="3" t="n"/>
       <c r="N238" s="3" t="n"/>
-      <c r="O238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n"/>
@@ -4634,7 +4372,6 @@
       <c r="L239" s="3" t="n"/>
       <c r="M239" s="3" t="n"/>
       <c r="N239" s="3" t="n"/>
-      <c r="O239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n"/>
@@ -4651,7 +4388,6 @@
       <c r="L240" s="3" t="n"/>
       <c r="M240" s="3" t="n"/>
       <c r="N240" s="3" t="n"/>
-      <c r="O240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="n"/>
@@ -4668,7 +4404,6 @@
       <c r="L241" s="3" t="n"/>
       <c r="M241" s="3" t="n"/>
       <c r="N241" s="3" t="n"/>
-      <c r="O241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="n"/>
@@ -4685,7 +4420,6 @@
       <c r="L242" s="3" t="n"/>
       <c r="M242" s="3" t="n"/>
       <c r="N242" s="3" t="n"/>
-      <c r="O242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="n"/>
@@ -4702,7 +4436,6 @@
       <c r="L243" s="3" t="n"/>
       <c r="M243" s="3" t="n"/>
       <c r="N243" s="3" t="n"/>
-      <c r="O243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="n"/>
@@ -4719,7 +4452,6 @@
       <c r="L244" s="3" t="n"/>
       <c r="M244" s="3" t="n"/>
       <c r="N244" s="3" t="n"/>
-      <c r="O244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="n"/>
@@ -4736,7 +4468,6 @@
       <c r="L245" s="3" t="n"/>
       <c r="M245" s="3" t="n"/>
       <c r="N245" s="3" t="n"/>
-      <c r="O245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="n"/>
@@ -4753,7 +4484,6 @@
       <c r="L246" s="3" t="n"/>
       <c r="M246" s="3" t="n"/>
       <c r="N246" s="3" t="n"/>
-      <c r="O246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="n"/>
@@ -4770,7 +4500,6 @@
       <c r="L247" s="3" t="n"/>
       <c r="M247" s="3" t="n"/>
       <c r="N247" s="3" t="n"/>
-      <c r="O247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="n"/>
@@ -4787,7 +4516,6 @@
       <c r="L248" s="3" t="n"/>
       <c r="M248" s="3" t="n"/>
       <c r="N248" s="3" t="n"/>
-      <c r="O248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="n"/>
@@ -4804,7 +4532,6 @@
       <c r="L249" s="3" t="n"/>
       <c r="M249" s="3" t="n"/>
       <c r="N249" s="3" t="n"/>
-      <c r="O249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="n"/>
@@ -4821,7 +4548,6 @@
       <c r="L250" s="3" t="n"/>
       <c r="M250" s="3" t="n"/>
       <c r="N250" s="3" t="n"/>
-      <c r="O250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="n"/>
@@ -4838,7 +4564,6 @@
       <c r="L251" s="3" t="n"/>
       <c r="M251" s="3" t="n"/>
       <c r="N251" s="3" t="n"/>
-      <c r="O251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="n"/>
@@ -4855,7 +4580,6 @@
       <c r="L252" s="3" t="n"/>
       <c r="M252" s="3" t="n"/>
       <c r="N252" s="3" t="n"/>
-      <c r="O252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="n"/>
@@ -4872,7 +4596,6 @@
       <c r="L253" s="3" t="n"/>
       <c r="M253" s="3" t="n"/>
       <c r="N253" s="3" t="n"/>
-      <c r="O253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n"/>
@@ -4889,7 +4612,6 @@
       <c r="L254" s="3" t="n"/>
       <c r="M254" s="3" t="n"/>
       <c r="N254" s="3" t="n"/>
-      <c r="O254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="n"/>
@@ -4906,7 +4628,6 @@
       <c r="L255" s="3" t="n"/>
       <c r="M255" s="3" t="n"/>
       <c r="N255" s="3" t="n"/>
-      <c r="O255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="n"/>
@@ -4923,7 +4644,6 @@
       <c r="L256" s="3" t="n"/>
       <c r="M256" s="3" t="n"/>
       <c r="N256" s="3" t="n"/>
-      <c r="O256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="n"/>
@@ -4940,7 +4660,6 @@
       <c r="L257" s="3" t="n"/>
       <c r="M257" s="3" t="n"/>
       <c r="N257" s="3" t="n"/>
-      <c r="O257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="n"/>
@@ -4957,7 +4676,6 @@
       <c r="L258" s="3" t="n"/>
       <c r="M258" s="3" t="n"/>
       <c r="N258" s="3" t="n"/>
-      <c r="O258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="n"/>
@@ -4974,7 +4692,6 @@
       <c r="L259" s="3" t="n"/>
       <c r="M259" s="3" t="n"/>
       <c r="N259" s="3" t="n"/>
-      <c r="O259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="n"/>
@@ -4991,7 +4708,6 @@
       <c r="L260" s="3" t="n"/>
       <c r="M260" s="3" t="n"/>
       <c r="N260" s="3" t="n"/>
-      <c r="O260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="n"/>
@@ -5008,7 +4724,6 @@
       <c r="L261" s="3" t="n"/>
       <c r="M261" s="3" t="n"/>
       <c r="N261" s="3" t="n"/>
-      <c r="O261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="n"/>
@@ -5025,7 +4740,6 @@
       <c r="L262" s="3" t="n"/>
       <c r="M262" s="3" t="n"/>
       <c r="N262" s="3" t="n"/>
-      <c r="O262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="n"/>
@@ -5042,7 +4756,6 @@
       <c r="L263" s="3" t="n"/>
       <c r="M263" s="3" t="n"/>
       <c r="N263" s="3" t="n"/>
-      <c r="O263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n"/>
@@ -5059,7 +4772,6 @@
       <c r="L264" s="3" t="n"/>
       <c r="M264" s="3" t="n"/>
       <c r="N264" s="3" t="n"/>
-      <c r="O264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="n"/>
@@ -5076,7 +4788,6 @@
       <c r="L265" s="3" t="n"/>
       <c r="M265" s="3" t="n"/>
       <c r="N265" s="3" t="n"/>
-      <c r="O265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="n"/>
@@ -5093,7 +4804,6 @@
       <c r="L266" s="3" t="n"/>
       <c r="M266" s="3" t="n"/>
       <c r="N266" s="3" t="n"/>
-      <c r="O266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="n"/>
@@ -5110,7 +4820,6 @@
       <c r="L267" s="3" t="n"/>
       <c r="M267" s="3" t="n"/>
       <c r="N267" s="3" t="n"/>
-      <c r="O267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="n"/>
@@ -5127,7 +4836,6 @@
       <c r="L268" s="3" t="n"/>
       <c r="M268" s="3" t="n"/>
       <c r="N268" s="3" t="n"/>
-      <c r="O268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="n"/>
@@ -5144,7 +4852,6 @@
       <c r="L269" s="3" t="n"/>
       <c r="M269" s="3" t="n"/>
       <c r="N269" s="3" t="n"/>
-      <c r="O269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="n"/>
@@ -5161,7 +4868,6 @@
       <c r="L270" s="3" t="n"/>
       <c r="M270" s="3" t="n"/>
       <c r="N270" s="3" t="n"/>
-      <c r="O270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="n"/>
@@ -5178,7 +4884,6 @@
       <c r="L271" s="3" t="n"/>
       <c r="M271" s="3" t="n"/>
       <c r="N271" s="3" t="n"/>
-      <c r="O271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="n"/>
@@ -5195,7 +4900,6 @@
       <c r="L272" s="3" t="n"/>
       <c r="M272" s="3" t="n"/>
       <c r="N272" s="3" t="n"/>
-      <c r="O272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="n"/>
@@ -5212,7 +4916,6 @@
       <c r="L273" s="3" t="n"/>
       <c r="M273" s="3" t="n"/>
       <c r="N273" s="3" t="n"/>
-      <c r="O273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="n"/>
@@ -5229,7 +4932,6 @@
       <c r="L274" s="3" t="n"/>
       <c r="M274" s="3" t="n"/>
       <c r="N274" s="3" t="n"/>
-      <c r="O274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="n"/>
@@ -5246,7 +4948,6 @@
       <c r="L275" s="3" t="n"/>
       <c r="M275" s="3" t="n"/>
       <c r="N275" s="3" t="n"/>
-      <c r="O275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n"/>
@@ -5263,7 +4964,6 @@
       <c r="L276" s="3" t="n"/>
       <c r="M276" s="3" t="n"/>
       <c r="N276" s="3" t="n"/>
-      <c r="O276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="n"/>
@@ -5280,7 +4980,6 @@
       <c r="L277" s="3" t="n"/>
       <c r="M277" s="3" t="n"/>
       <c r="N277" s="3" t="n"/>
-      <c r="O277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n"/>
@@ -5297,7 +4996,6 @@
       <c r="L278" s="3" t="n"/>
       <c r="M278" s="3" t="n"/>
       <c r="N278" s="3" t="n"/>
-      <c r="O278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="n"/>
@@ -5314,7 +5012,6 @@
       <c r="L279" s="3" t="n"/>
       <c r="M279" s="3" t="n"/>
       <c r="N279" s="3" t="n"/>
-      <c r="O279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="n"/>
@@ -5331,7 +5028,6 @@
       <c r="L280" s="3" t="n"/>
       <c r="M280" s="3" t="n"/>
       <c r="N280" s="3" t="n"/>
-      <c r="O280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="n"/>
@@ -5348,7 +5044,6 @@
       <c r="L281" s="3" t="n"/>
       <c r="M281" s="3" t="n"/>
       <c r="N281" s="3" t="n"/>
-      <c r="O281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="n"/>
@@ -5365,7 +5060,6 @@
       <c r="L282" s="3" t="n"/>
       <c r="M282" s="3" t="n"/>
       <c r="N282" s="3" t="n"/>
-      <c r="O282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="n"/>
@@ -5382,7 +5076,6 @@
       <c r="L283" s="3" t="n"/>
       <c r="M283" s="3" t="n"/>
       <c r="N283" s="3" t="n"/>
-      <c r="O283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="n"/>
@@ -5399,7 +5092,6 @@
       <c r="L284" s="3" t="n"/>
       <c r="M284" s="3" t="n"/>
       <c r="N284" s="3" t="n"/>
-      <c r="O284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="n"/>
@@ -5416,7 +5108,6 @@
       <c r="L285" s="3" t="n"/>
       <c r="M285" s="3" t="n"/>
       <c r="N285" s="3" t="n"/>
-      <c r="O285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="n"/>
@@ -5433,7 +5124,6 @@
       <c r="L286" s="3" t="n"/>
       <c r="M286" s="3" t="n"/>
       <c r="N286" s="3" t="n"/>
-      <c r="O286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="n"/>
@@ -5450,7 +5140,6 @@
       <c r="L287" s="3" t="n"/>
       <c r="M287" s="3" t="n"/>
       <c r="N287" s="3" t="n"/>
-      <c r="O287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="n"/>
@@ -5467,7 +5156,6 @@
       <c r="L288" s="3" t="n"/>
       <c r="M288" s="3" t="n"/>
       <c r="N288" s="3" t="n"/>
-      <c r="O288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="n"/>
@@ -5484,7 +5172,6 @@
       <c r="L289" s="3" t="n"/>
       <c r="M289" s="3" t="n"/>
       <c r="N289" s="3" t="n"/>
-      <c r="O289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="n"/>
@@ -5501,7 +5188,6 @@
       <c r="L290" s="3" t="n"/>
       <c r="M290" s="3" t="n"/>
       <c r="N290" s="3" t="n"/>
-      <c r="O290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="n"/>
@@ -5518,7 +5204,6 @@
       <c r="L291" s="3" t="n"/>
       <c r="M291" s="3" t="n"/>
       <c r="N291" s="3" t="n"/>
-      <c r="O291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="n"/>
@@ -5535,7 +5220,6 @@
       <c r="L292" s="3" t="n"/>
       <c r="M292" s="3" t="n"/>
       <c r="N292" s="3" t="n"/>
-      <c r="O292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n"/>
@@ -5552,7 +5236,6 @@
       <c r="L293" s="3" t="n"/>
       <c r="M293" s="3" t="n"/>
       <c r="N293" s="3" t="n"/>
-      <c r="O293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="n"/>
@@ -5569,7 +5252,6 @@
       <c r="L294" s="3" t="n"/>
       <c r="M294" s="3" t="n"/>
       <c r="N294" s="3" t="n"/>
-      <c r="O294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="n"/>
@@ -5586,7 +5268,6 @@
       <c r="L295" s="3" t="n"/>
       <c r="M295" s="3" t="n"/>
       <c r="N295" s="3" t="n"/>
-      <c r="O295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="n"/>
@@ -5603,7 +5284,6 @@
       <c r="L296" s="3" t="n"/>
       <c r="M296" s="3" t="n"/>
       <c r="N296" s="3" t="n"/>
-      <c r="O296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="n"/>
@@ -5620,7 +5300,6 @@
       <c r="L297" s="3" t="n"/>
       <c r="M297" s="3" t="n"/>
       <c r="N297" s="3" t="n"/>
-      <c r="O297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="n"/>
@@ -5637,7 +5316,6 @@
       <c r="L298" s="3" t="n"/>
       <c r="M298" s="3" t="n"/>
       <c r="N298" s="3" t="n"/>
-      <c r="O298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="n"/>
@@ -5654,7 +5332,6 @@
       <c r="L299" s="3" t="n"/>
       <c r="M299" s="3" t="n"/>
       <c r="N299" s="3" t="n"/>
-      <c r="O299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="n"/>
@@ -5671,7 +5348,6 @@
       <c r="L300" s="3" t="n"/>
       <c r="M300" s="3" t="n"/>
       <c r="N300" s="3" t="n"/>
-      <c r="O300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="n"/>
@@ -5688,7 +5364,6 @@
       <c r="L301" s="3" t="n"/>
       <c r="M301" s="3" t="n"/>
       <c r="N301" s="3" t="n"/>
-      <c r="O301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="n"/>
@@ -5705,7 +5380,6 @@
       <c r="L302" s="3" t="n"/>
       <c r="M302" s="3" t="n"/>
       <c r="N302" s="3" t="n"/>
-      <c r="O302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="n"/>
@@ -5722,7 +5396,6 @@
       <c r="L303" s="3" t="n"/>
       <c r="M303" s="3" t="n"/>
       <c r="N303" s="3" t="n"/>
-      <c r="O303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="n"/>
@@ -5739,7 +5412,6 @@
       <c r="L304" s="3" t="n"/>
       <c r="M304" s="3" t="n"/>
       <c r="N304" s="3" t="n"/>
-      <c r="O304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="n"/>
@@ -5756,7 +5428,6 @@
       <c r="L305" s="3" t="n"/>
       <c r="M305" s="3" t="n"/>
       <c r="N305" s="3" t="n"/>
-      <c r="O305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="n"/>
@@ -5773,7 +5444,6 @@
       <c r="L306" s="3" t="n"/>
       <c r="M306" s="3" t="n"/>
       <c r="N306" s="3" t="n"/>
-      <c r="O306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="n"/>
@@ -5790,7 +5460,6 @@
       <c r="L307" s="3" t="n"/>
       <c r="M307" s="3" t="n"/>
       <c r="N307" s="3" t="n"/>
-      <c r="O307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="n"/>
@@ -5807,7 +5476,6 @@
       <c r="L308" s="3" t="n"/>
       <c r="M308" s="3" t="n"/>
       <c r="N308" s="3" t="n"/>
-      <c r="O308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="n"/>
@@ -5824,7 +5492,6 @@
       <c r="L309" s="3" t="n"/>
       <c r="M309" s="3" t="n"/>
       <c r="N309" s="3" t="n"/>
-      <c r="O309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="n"/>
@@ -5841,7 +5508,6 @@
       <c r="L310" s="3" t="n"/>
       <c r="M310" s="3" t="n"/>
       <c r="N310" s="3" t="n"/>
-      <c r="O310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="n"/>
@@ -5858,7 +5524,6 @@
       <c r="L311" s="3" t="n"/>
       <c r="M311" s="3" t="n"/>
       <c r="N311" s="3" t="n"/>
-      <c r="O311" s="3" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="n"/>
@@ -5875,7 +5540,6 @@
       <c r="L312" s="3" t="n"/>
       <c r="M312" s="3" t="n"/>
       <c r="N312" s="3" t="n"/>
-      <c r="O312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="n"/>
@@ -5892,7 +5556,6 @@
       <c r="L313" s="3" t="n"/>
       <c r="M313" s="3" t="n"/>
       <c r="N313" s="3" t="n"/>
-      <c r="O313" s="3" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="n"/>
@@ -5909,7 +5572,6 @@
       <c r="L314" s="3" t="n"/>
       <c r="M314" s="3" t="n"/>
       <c r="N314" s="3" t="n"/>
-      <c r="O314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="n"/>
@@ -5926,7 +5588,6 @@
       <c r="L315" s="3" t="n"/>
       <c r="M315" s="3" t="n"/>
       <c r="N315" s="3" t="n"/>
-      <c r="O315" s="3" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="n"/>
@@ -5943,7 +5604,6 @@
       <c r="L316" s="3" t="n"/>
       <c r="M316" s="3" t="n"/>
       <c r="N316" s="3" t="n"/>
-      <c r="O316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="n"/>
@@ -5960,7 +5620,6 @@
       <c r="L317" s="3" t="n"/>
       <c r="M317" s="3" t="n"/>
       <c r="N317" s="3" t="n"/>
-      <c r="O317" s="3" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="n"/>
@@ -5977,7 +5636,6 @@
       <c r="L318" s="3" t="n"/>
       <c r="M318" s="3" t="n"/>
       <c r="N318" s="3" t="n"/>
-      <c r="O318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="n"/>
@@ -5994,7 +5652,6 @@
       <c r="L319" s="3" t="n"/>
       <c r="M319" s="3" t="n"/>
       <c r="N319" s="3" t="n"/>
-      <c r="O319" s="3" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="n"/>
@@ -6011,7 +5668,6 @@
       <c r="L320" s="3" t="n"/>
       <c r="M320" s="3" t="n"/>
       <c r="N320" s="3" t="n"/>
-      <c r="O320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="n"/>
@@ -6028,7 +5684,6 @@
       <c r="L321" s="3" t="n"/>
       <c r="M321" s="3" t="n"/>
       <c r="N321" s="3" t="n"/>
-      <c r="O321" s="3" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="n"/>
@@ -6045,7 +5700,6 @@
       <c r="L322" s="3" t="n"/>
       <c r="M322" s="3" t="n"/>
       <c r="N322" s="3" t="n"/>
-      <c r="O322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="n"/>
@@ -6062,7 +5716,6 @@
       <c r="L323" s="3" t="n"/>
       <c r="M323" s="3" t="n"/>
       <c r="N323" s="3" t="n"/>
-      <c r="O323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="n"/>
@@ -6079,7 +5732,6 @@
       <c r="L324" s="3" t="n"/>
       <c r="M324" s="3" t="n"/>
       <c r="N324" s="3" t="n"/>
-      <c r="O324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="n"/>
@@ -6096,7 +5748,6 @@
       <c r="L325" s="3" t="n"/>
       <c r="M325" s="3" t="n"/>
       <c r="N325" s="3" t="n"/>
-      <c r="O325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="n"/>
@@ -6113,7 +5764,6 @@
       <c r="L326" s="3" t="n"/>
       <c r="M326" s="3" t="n"/>
       <c r="N326" s="3" t="n"/>
-      <c r="O326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="n"/>
@@ -6130,7 +5780,6 @@
       <c r="L327" s="3" t="n"/>
       <c r="M327" s="3" t="n"/>
       <c r="N327" s="3" t="n"/>
-      <c r="O327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="n"/>
@@ -6147,7 +5796,6 @@
       <c r="L328" s="3" t="n"/>
       <c r="M328" s="3" t="n"/>
       <c r="N328" s="3" t="n"/>
-      <c r="O328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="n"/>
@@ -6164,7 +5812,6 @@
       <c r="L329" s="3" t="n"/>
       <c r="M329" s="3" t="n"/>
       <c r="N329" s="3" t="n"/>
-      <c r="O329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="n"/>
@@ -6181,7 +5828,6 @@
       <c r="L330" s="3" t="n"/>
       <c r="M330" s="3" t="n"/>
       <c r="N330" s="3" t="n"/>
-      <c r="O330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="n"/>
@@ -6198,7 +5844,6 @@
       <c r="L331" s="3" t="n"/>
       <c r="M331" s="3" t="n"/>
       <c r="N331" s="3" t="n"/>
-      <c r="O331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="n"/>
@@ -6215,7 +5860,6 @@
       <c r="L332" s="3" t="n"/>
       <c r="M332" s="3" t="n"/>
       <c r="N332" s="3" t="n"/>
-      <c r="O332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="n"/>
@@ -6232,7 +5876,6 @@
       <c r="L333" s="3" t="n"/>
       <c r="M333" s="3" t="n"/>
       <c r="N333" s="3" t="n"/>
-      <c r="O333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="n"/>
@@ -6249,7 +5892,6 @@
       <c r="L334" s="3" t="n"/>
       <c r="M334" s="3" t="n"/>
       <c r="N334" s="3" t="n"/>
-      <c r="O334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="n"/>
@@ -6266,7 +5908,6 @@
       <c r="L335" s="3" t="n"/>
       <c r="M335" s="3" t="n"/>
       <c r="N335" s="3" t="n"/>
-      <c r="O335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="n"/>
@@ -6283,7 +5924,6 @@
       <c r="L336" s="3" t="n"/>
       <c r="M336" s="3" t="n"/>
       <c r="N336" s="3" t="n"/>
-      <c r="O336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="n"/>
@@ -6300,7 +5940,6 @@
       <c r="L337" s="3" t="n"/>
       <c r="M337" s="3" t="n"/>
       <c r="N337" s="3" t="n"/>
-      <c r="O337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="n"/>
@@ -6317,7 +5956,6 @@
       <c r="L338" s="3" t="n"/>
       <c r="M338" s="3" t="n"/>
       <c r="N338" s="3" t="n"/>
-      <c r="O338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="n"/>
@@ -6334,7 +5972,6 @@
       <c r="L339" s="3" t="n"/>
       <c r="M339" s="3" t="n"/>
       <c r="N339" s="3" t="n"/>
-      <c r="O339" s="3" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="n"/>
@@ -6351,7 +5988,6 @@
       <c r="L340" s="3" t="n"/>
       <c r="M340" s="3" t="n"/>
       <c r="N340" s="3" t="n"/>
-      <c r="O340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="n"/>
@@ -6368,7 +6004,6 @@
       <c r="L341" s="3" t="n"/>
       <c r="M341" s="3" t="n"/>
       <c r="N341" s="3" t="n"/>
-      <c r="O341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="n"/>
@@ -6385,7 +6020,6 @@
       <c r="L342" s="3" t="n"/>
       <c r="M342" s="3" t="n"/>
       <c r="N342" s="3" t="n"/>
-      <c r="O342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="n"/>
@@ -6402,7 +6036,6 @@
       <c r="L343" s="3" t="n"/>
       <c r="M343" s="3" t="n"/>
       <c r="N343" s="3" t="n"/>
-      <c r="O343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="n"/>
@@ -6419,7 +6052,6 @@
       <c r="L344" s="3" t="n"/>
       <c r="M344" s="3" t="n"/>
       <c r="N344" s="3" t="n"/>
-      <c r="O344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="n"/>
@@ -6436,7 +6068,6 @@
       <c r="L345" s="3" t="n"/>
       <c r="M345" s="3" t="n"/>
       <c r="N345" s="3" t="n"/>
-      <c r="O345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="n"/>
@@ -6453,7 +6084,6 @@
       <c r="L346" s="3" t="n"/>
       <c r="M346" s="3" t="n"/>
       <c r="N346" s="3" t="n"/>
-      <c r="O346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="n"/>
@@ -6470,7 +6100,6 @@
       <c r="L347" s="3" t="n"/>
       <c r="M347" s="3" t="n"/>
       <c r="N347" s="3" t="n"/>
-      <c r="O347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="n"/>
@@ -6487,7 +6116,6 @@
       <c r="L348" s="3" t="n"/>
       <c r="M348" s="3" t="n"/>
       <c r="N348" s="3" t="n"/>
-      <c r="O348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="n"/>
@@ -6504,7 +6132,6 @@
       <c r="L349" s="3" t="n"/>
       <c r="M349" s="3" t="n"/>
       <c r="N349" s="3" t="n"/>
-      <c r="O349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="n"/>
@@ -6521,7 +6148,6 @@
       <c r="L350" s="3" t="n"/>
       <c r="M350" s="3" t="n"/>
       <c r="N350" s="3" t="n"/>
-      <c r="O350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="n"/>
@@ -6538,7 +6164,6 @@
       <c r="L351" s="3" t="n"/>
       <c r="M351" s="3" t="n"/>
       <c r="N351" s="3" t="n"/>
-      <c r="O351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="n"/>
@@ -6555,7 +6180,6 @@
       <c r="L352" s="3" t="n"/>
       <c r="M352" s="3" t="n"/>
       <c r="N352" s="3" t="n"/>
-      <c r="O352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="n"/>
@@ -6572,7 +6196,6 @@
       <c r="L353" s="3" t="n"/>
       <c r="M353" s="3" t="n"/>
       <c r="N353" s="3" t="n"/>
-      <c r="O353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="n"/>
@@ -6589,7 +6212,6 @@
       <c r="L354" s="3" t="n"/>
       <c r="M354" s="3" t="n"/>
       <c r="N354" s="3" t="n"/>
-      <c r="O354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="n"/>
@@ -6606,7 +6228,6 @@
       <c r="L355" s="3" t="n"/>
       <c r="M355" s="3" t="n"/>
       <c r="N355" s="3" t="n"/>
-      <c r="O355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="n"/>
@@ -6623,7 +6244,6 @@
       <c r="L356" s="3" t="n"/>
       <c r="M356" s="3" t="n"/>
       <c r="N356" s="3" t="n"/>
-      <c r="O356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="n"/>
@@ -6640,7 +6260,6 @@
       <c r="L357" s="3" t="n"/>
       <c r="M357" s="3" t="n"/>
       <c r="N357" s="3" t="n"/>
-      <c r="O357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="n"/>
@@ -6657,7 +6276,6 @@
       <c r="L358" s="3" t="n"/>
       <c r="M358" s="3" t="n"/>
       <c r="N358" s="3" t="n"/>
-      <c r="O358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="n"/>
@@ -6674,7 +6292,6 @@
       <c r="L359" s="3" t="n"/>
       <c r="M359" s="3" t="n"/>
       <c r="N359" s="3" t="n"/>
-      <c r="O359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="n"/>
@@ -6691,7 +6308,6 @@
       <c r="L360" s="3" t="n"/>
       <c r="M360" s="3" t="n"/>
       <c r="N360" s="3" t="n"/>
-      <c r="O360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="n"/>
@@ -6708,7 +6324,6 @@
       <c r="L361" s="3" t="n"/>
       <c r="M361" s="3" t="n"/>
       <c r="N361" s="3" t="n"/>
-      <c r="O361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="n"/>
@@ -6725,7 +6340,6 @@
       <c r="L362" s="3" t="n"/>
       <c r="M362" s="3" t="n"/>
       <c r="N362" s="3" t="n"/>
-      <c r="O362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="n"/>
@@ -6742,7 +6356,6 @@
       <c r="L363" s="3" t="n"/>
       <c r="M363" s="3" t="n"/>
       <c r="N363" s="3" t="n"/>
-      <c r="O363" s="3" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="n"/>
@@ -6759,7 +6372,6 @@
       <c r="L364" s="3" t="n"/>
       <c r="M364" s="3" t="n"/>
       <c r="N364" s="3" t="n"/>
-      <c r="O364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="n"/>
@@ -6776,7 +6388,6 @@
       <c r="L365" s="3" t="n"/>
       <c r="M365" s="3" t="n"/>
       <c r="N365" s="3" t="n"/>
-      <c r="O365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="n"/>
@@ -6793,7 +6404,6 @@
       <c r="L366" s="3" t="n"/>
       <c r="M366" s="3" t="n"/>
       <c r="N366" s="3" t="n"/>
-      <c r="O366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="n"/>
@@ -6810,7 +6420,6 @@
       <c r="L367" s="3" t="n"/>
       <c r="M367" s="3" t="n"/>
       <c r="N367" s="3" t="n"/>
-      <c r="O367" s="3" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="n"/>
@@ -6827,7 +6436,6 @@
       <c r="L368" s="3" t="n"/>
       <c r="M368" s="3" t="n"/>
       <c r="N368" s="3" t="n"/>
-      <c r="O368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="n"/>
@@ -6844,7 +6452,6 @@
       <c r="L369" s="3" t="n"/>
       <c r="M369" s="3" t="n"/>
       <c r="N369" s="3" t="n"/>
-      <c r="O369" s="3" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="n"/>
@@ -6861,7 +6468,6 @@
       <c r="L370" s="3" t="n"/>
       <c r="M370" s="3" t="n"/>
       <c r="N370" s="3" t="n"/>
-      <c r="O370" s="3" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="n"/>
@@ -6878,7 +6484,6 @@
       <c r="L371" s="3" t="n"/>
       <c r="M371" s="3" t="n"/>
       <c r="N371" s="3" t="n"/>
-      <c r="O371" s="3" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="3" t="n"/>
@@ -6895,7 +6500,6 @@
       <c r="L372" s="3" t="n"/>
       <c r="M372" s="3" t="n"/>
       <c r="N372" s="3" t="n"/>
-      <c r="O372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="n"/>
@@ -6912,7 +6516,6 @@
       <c r="L373" s="3" t="n"/>
       <c r="M373" s="3" t="n"/>
       <c r="N373" s="3" t="n"/>
-      <c r="O373" s="3" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="n"/>
@@ -6929,7 +6532,6 @@
       <c r="L374" s="3" t="n"/>
       <c r="M374" s="3" t="n"/>
       <c r="N374" s="3" t="n"/>
-      <c r="O374" s="3" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="n"/>
@@ -6946,7 +6548,6 @@
       <c r="L375" s="3" t="n"/>
       <c r="M375" s="3" t="n"/>
       <c r="N375" s="3" t="n"/>
-      <c r="O375" s="3" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="n"/>
@@ -6963,7 +6564,6 @@
       <c r="L376" s="3" t="n"/>
       <c r="M376" s="3" t="n"/>
       <c r="N376" s="3" t="n"/>
-      <c r="O376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="n"/>
@@ -6980,7 +6580,6 @@
       <c r="L377" s="3" t="n"/>
       <c r="M377" s="3" t="n"/>
       <c r="N377" s="3" t="n"/>
-      <c r="O377" s="3" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="n"/>
@@ -6997,7 +6596,6 @@
       <c r="L378" s="3" t="n"/>
       <c r="M378" s="3" t="n"/>
       <c r="N378" s="3" t="n"/>
-      <c r="O378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="3" t="n"/>
@@ -7014,7 +6612,6 @@
       <c r="L379" s="3" t="n"/>
       <c r="M379" s="3" t="n"/>
       <c r="N379" s="3" t="n"/>
-      <c r="O379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="n"/>
@@ -7031,7 +6628,6 @@
       <c r="L380" s="3" t="n"/>
       <c r="M380" s="3" t="n"/>
       <c r="N380" s="3" t="n"/>
-      <c r="O380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="n"/>
@@ -7048,7 +6644,6 @@
       <c r="L381" s="3" t="n"/>
       <c r="M381" s="3" t="n"/>
       <c r="N381" s="3" t="n"/>
-      <c r="O381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="n"/>
@@ -7065,7 +6660,6 @@
       <c r="L382" s="3" t="n"/>
       <c r="M382" s="3" t="n"/>
       <c r="N382" s="3" t="n"/>
-      <c r="O382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="n"/>
@@ -7082,7 +6676,6 @@
       <c r="L383" s="3" t="n"/>
       <c r="M383" s="3" t="n"/>
       <c r="N383" s="3" t="n"/>
-      <c r="O383" s="3" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="n"/>
@@ -7099,7 +6692,6 @@
       <c r="L384" s="3" t="n"/>
       <c r="M384" s="3" t="n"/>
       <c r="N384" s="3" t="n"/>
-      <c r="O384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="n"/>
@@ -7116,7 +6708,6 @@
       <c r="L385" s="3" t="n"/>
       <c r="M385" s="3" t="n"/>
       <c r="N385" s="3" t="n"/>
-      <c r="O385" s="3" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="n"/>
@@ -7133,7 +6724,6 @@
       <c r="L386" s="3" t="n"/>
       <c r="M386" s="3" t="n"/>
       <c r="N386" s="3" t="n"/>
-      <c r="O386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="n"/>
@@ -7150,7 +6740,6 @@
       <c r="L387" s="3" t="n"/>
       <c r="M387" s="3" t="n"/>
       <c r="N387" s="3" t="n"/>
-      <c r="O387" s="3" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="n"/>
@@ -7167,7 +6756,6 @@
       <c r="L388" s="3" t="n"/>
       <c r="M388" s="3" t="n"/>
       <c r="N388" s="3" t="n"/>
-      <c r="O388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="n"/>
@@ -7184,7 +6772,6 @@
       <c r="L389" s="3" t="n"/>
       <c r="M389" s="3" t="n"/>
       <c r="N389" s="3" t="n"/>
-      <c r="O389" s="3" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="n"/>
@@ -7201,7 +6788,6 @@
       <c r="L390" s="3" t="n"/>
       <c r="M390" s="3" t="n"/>
       <c r="N390" s="3" t="n"/>
-      <c r="O390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="n"/>
@@ -7218,7 +6804,6 @@
       <c r="L391" s="3" t="n"/>
       <c r="M391" s="3" t="n"/>
       <c r="N391" s="3" t="n"/>
-      <c r="O391" s="3" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="n"/>
@@ -7235,7 +6820,6 @@
       <c r="L392" s="3" t="n"/>
       <c r="M392" s="3" t="n"/>
       <c r="N392" s="3" t="n"/>
-      <c r="O392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="3" t="n"/>
@@ -7252,7 +6836,6 @@
       <c r="L393" s="3" t="n"/>
       <c r="M393" s="3" t="n"/>
       <c r="N393" s="3" t="n"/>
-      <c r="O393" s="3" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="n"/>
@@ -7269,7 +6852,6 @@
       <c r="L394" s="3" t="n"/>
       <c r="M394" s="3" t="n"/>
       <c r="N394" s="3" t="n"/>
-      <c r="O394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="n"/>
@@ -7286,7 +6868,6 @@
       <c r="L395" s="3" t="n"/>
       <c r="M395" s="3" t="n"/>
       <c r="N395" s="3" t="n"/>
-      <c r="O395" s="3" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="n"/>
@@ -7303,7 +6884,6 @@
       <c r="L396" s="3" t="n"/>
       <c r="M396" s="3" t="n"/>
       <c r="N396" s="3" t="n"/>
-      <c r="O396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="n"/>
@@ -7320,7 +6900,6 @@
       <c r="L397" s="3" t="n"/>
       <c r="M397" s="3" t="n"/>
       <c r="N397" s="3" t="n"/>
-      <c r="O397" s="3" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="n"/>
@@ -7337,7 +6916,6 @@
       <c r="L398" s="3" t="n"/>
       <c r="M398" s="3" t="n"/>
       <c r="N398" s="3" t="n"/>
-      <c r="O398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="n"/>
@@ -7354,7 +6932,6 @@
       <c r="L399" s="3" t="n"/>
       <c r="M399" s="3" t="n"/>
       <c r="N399" s="3" t="n"/>
-      <c r="O399" s="3" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="3" t="n"/>
@@ -7371,7 +6948,6 @@
       <c r="L400" s="3" t="n"/>
       <c r="M400" s="3" t="n"/>
       <c r="N400" s="3" t="n"/>
-      <c r="O400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="n"/>
@@ -7388,7 +6964,6 @@
       <c r="L401" s="3" t="n"/>
       <c r="M401" s="3" t="n"/>
       <c r="N401" s="3" t="n"/>
-      <c r="O401" s="3" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="n"/>
@@ -7405,7 +6980,6 @@
       <c r="L402" s="3" t="n"/>
       <c r="M402" s="3" t="n"/>
       <c r="N402" s="3" t="n"/>
-      <c r="O402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="n"/>
@@ -7422,7 +6996,6 @@
       <c r="L403" s="3" t="n"/>
       <c r="M403" s="3" t="n"/>
       <c r="N403" s="3" t="n"/>
-      <c r="O403" s="3" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="n"/>
@@ -7439,7 +7012,6 @@
       <c r="L404" s="3" t="n"/>
       <c r="M404" s="3" t="n"/>
       <c r="N404" s="3" t="n"/>
-      <c r="O404" s="3" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="n"/>
@@ -7456,7 +7028,6 @@
       <c r="L405" s="3" t="n"/>
       <c r="M405" s="3" t="n"/>
       <c r="N405" s="3" t="n"/>
-      <c r="O405" s="3" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="n"/>
@@ -7473,7 +7044,6 @@
       <c r="L406" s="3" t="n"/>
       <c r="M406" s="3" t="n"/>
       <c r="N406" s="3" t="n"/>
-      <c r="O406" s="3" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="3" t="n"/>
@@ -7490,7 +7060,6 @@
       <c r="L407" s="3" t="n"/>
       <c r="M407" s="3" t="n"/>
       <c r="N407" s="3" t="n"/>
-      <c r="O407" s="3" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="n"/>
@@ -7507,7 +7076,6 @@
       <c r="L408" s="3" t="n"/>
       <c r="M408" s="3" t="n"/>
       <c r="N408" s="3" t="n"/>
-      <c r="O408" s="3" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="n"/>
@@ -7524,7 +7092,6 @@
       <c r="L409" s="3" t="n"/>
       <c r="M409" s="3" t="n"/>
       <c r="N409" s="3" t="n"/>
-      <c r="O409" s="3" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="n"/>
@@ -7541,7 +7108,6 @@
       <c r="L410" s="3" t="n"/>
       <c r="M410" s="3" t="n"/>
       <c r="N410" s="3" t="n"/>
-      <c r="O410" s="3" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="n"/>
@@ -7558,7 +7124,6 @@
       <c r="L411" s="3" t="n"/>
       <c r="M411" s="3" t="n"/>
       <c r="N411" s="3" t="n"/>
-      <c r="O411" s="3" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="n"/>
@@ -7575,7 +7140,6 @@
       <c r="L412" s="3" t="n"/>
       <c r="M412" s="3" t="n"/>
       <c r="N412" s="3" t="n"/>
-      <c r="O412" s="3" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="n"/>
@@ -7592,7 +7156,6 @@
       <c r="L413" s="3" t="n"/>
       <c r="M413" s="3" t="n"/>
       <c r="N413" s="3" t="n"/>
-      <c r="O413" s="3" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="3" t="n"/>
@@ -7609,7 +7172,6 @@
       <c r="L414" s="3" t="n"/>
       <c r="M414" s="3" t="n"/>
       <c r="N414" s="3" t="n"/>
-      <c r="O414" s="3" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="n"/>
@@ -7626,7 +7188,6 @@
       <c r="L415" s="3" t="n"/>
       <c r="M415" s="3" t="n"/>
       <c r="N415" s="3" t="n"/>
-      <c r="O415" s="3" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="n"/>
@@ -7643,7 +7204,6 @@
       <c r="L416" s="3" t="n"/>
       <c r="M416" s="3" t="n"/>
       <c r="N416" s="3" t="n"/>
-      <c r="O416" s="3" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="n"/>
@@ -7660,7 +7220,6 @@
       <c r="L417" s="3" t="n"/>
       <c r="M417" s="3" t="n"/>
       <c r="N417" s="3" t="n"/>
-      <c r="O417" s="3" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="n"/>
@@ -7677,7 +7236,6 @@
       <c r="L418" s="3" t="n"/>
       <c r="M418" s="3" t="n"/>
       <c r="N418" s="3" t="n"/>
-      <c r="O418" s="3" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="n"/>
@@ -7694,7 +7252,6 @@
       <c r="L419" s="3" t="n"/>
       <c r="M419" s="3" t="n"/>
       <c r="N419" s="3" t="n"/>
-      <c r="O419" s="3" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="n"/>
@@ -7711,7 +7268,6 @@
       <c r="L420" s="3" t="n"/>
       <c r="M420" s="3" t="n"/>
       <c r="N420" s="3" t="n"/>
-      <c r="O420" s="3" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="3" t="n"/>
@@ -7728,7 +7284,6 @@
       <c r="L421" s="3" t="n"/>
       <c r="M421" s="3" t="n"/>
       <c r="N421" s="3" t="n"/>
-      <c r="O421" s="3" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="n"/>
@@ -7745,7 +7300,6 @@
       <c r="L422" s="3" t="n"/>
       <c r="M422" s="3" t="n"/>
       <c r="N422" s="3" t="n"/>
-      <c r="O422" s="3" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="n"/>
@@ -7762,7 +7316,6 @@
       <c r="L423" s="3" t="n"/>
       <c r="M423" s="3" t="n"/>
       <c r="N423" s="3" t="n"/>
-      <c r="O423" s="3" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="n"/>
@@ -7779,7 +7332,6 @@
       <c r="L424" s="3" t="n"/>
       <c r="M424" s="3" t="n"/>
       <c r="N424" s="3" t="n"/>
-      <c r="O424" s="3" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="n"/>
@@ -7796,7 +7348,6 @@
       <c r="L425" s="3" t="n"/>
       <c r="M425" s="3" t="n"/>
       <c r="N425" s="3" t="n"/>
-      <c r="O425" s="3" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="n"/>
@@ -7813,7 +7364,6 @@
       <c r="L426" s="3" t="n"/>
       <c r="M426" s="3" t="n"/>
       <c r="N426" s="3" t="n"/>
-      <c r="O426" s="3" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="3" t="n"/>
@@ -7830,7 +7380,6 @@
       <c r="L427" s="3" t="n"/>
       <c r="M427" s="3" t="n"/>
       <c r="N427" s="3" t="n"/>
-      <c r="O427" s="3" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="3" t="n"/>
@@ -7847,7 +7396,6 @@
       <c r="L428" s="3" t="n"/>
       <c r="M428" s="3" t="n"/>
       <c r="N428" s="3" t="n"/>
-      <c r="O428" s="3" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="n"/>
@@ -7864,7 +7412,6 @@
       <c r="L429" s="3" t="n"/>
       <c r="M429" s="3" t="n"/>
       <c r="N429" s="3" t="n"/>
-      <c r="O429" s="3" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="n"/>
@@ -7881,7 +7428,6 @@
       <c r="L430" s="3" t="n"/>
       <c r="M430" s="3" t="n"/>
       <c r="N430" s="3" t="n"/>
-      <c r="O430" s="3" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="3" t="n"/>
@@ -7898,7 +7444,6 @@
       <c r="L431" s="3" t="n"/>
       <c r="M431" s="3" t="n"/>
       <c r="N431" s="3" t="n"/>
-      <c r="O431" s="3" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="n"/>
@@ -7915,7 +7460,6 @@
       <c r="L432" s="3" t="n"/>
       <c r="M432" s="3" t="n"/>
       <c r="N432" s="3" t="n"/>
-      <c r="O432" s="3" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="n"/>
@@ -7932,7 +7476,6 @@
       <c r="L433" s="3" t="n"/>
       <c r="M433" s="3" t="n"/>
       <c r="N433" s="3" t="n"/>
-      <c r="O433" s="3" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="n"/>
@@ -7949,7 +7492,6 @@
       <c r="L434" s="3" t="n"/>
       <c r="M434" s="3" t="n"/>
       <c r="N434" s="3" t="n"/>
-      <c r="O434" s="3" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="3" t="n"/>
@@ -7966,7 +7508,6 @@
       <c r="L435" s="3" t="n"/>
       <c r="M435" s="3" t="n"/>
       <c r="N435" s="3" t="n"/>
-      <c r="O435" s="3" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="n"/>
@@ -7983,7 +7524,6 @@
       <c r="L436" s="3" t="n"/>
       <c r="M436" s="3" t="n"/>
       <c r="N436" s="3" t="n"/>
-      <c r="O436" s="3" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="n"/>
@@ -8000,7 +7540,6 @@
       <c r="L437" s="3" t="n"/>
       <c r="M437" s="3" t="n"/>
       <c r="N437" s="3" t="n"/>
-      <c r="O437" s="3" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="n"/>
@@ -8017,7 +7556,6 @@
       <c r="L438" s="3" t="n"/>
       <c r="M438" s="3" t="n"/>
       <c r="N438" s="3" t="n"/>
-      <c r="O438" s="3" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="n"/>
@@ -8034,7 +7572,6 @@
       <c r="L439" s="3" t="n"/>
       <c r="M439" s="3" t="n"/>
       <c r="N439" s="3" t="n"/>
-      <c r="O439" s="3" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="n"/>
@@ -8051,7 +7588,6 @@
       <c r="L440" s="3" t="n"/>
       <c r="M440" s="3" t="n"/>
       <c r="N440" s="3" t="n"/>
-      <c r="O440" s="3" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="3" t="n"/>
@@ -8068,7 +7604,6 @@
       <c r="L441" s="3" t="n"/>
       <c r="M441" s="3" t="n"/>
       <c r="N441" s="3" t="n"/>
-      <c r="O441" s="3" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="3" t="n"/>
@@ -8085,7 +7620,6 @@
       <c r="L442" s="3" t="n"/>
       <c r="M442" s="3" t="n"/>
       <c r="N442" s="3" t="n"/>
-      <c r="O442" s="3" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="n"/>
@@ -8102,7 +7636,6 @@
       <c r="L443" s="3" t="n"/>
       <c r="M443" s="3" t="n"/>
       <c r="N443" s="3" t="n"/>
-      <c r="O443" s="3" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="n"/>
@@ -8119,7 +7652,6 @@
       <c r="L444" s="3" t="n"/>
       <c r="M444" s="3" t="n"/>
       <c r="N444" s="3" t="n"/>
-      <c r="O444" s="3" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="n"/>
@@ -8136,7 +7668,6 @@
       <c r="L445" s="3" t="n"/>
       <c r="M445" s="3" t="n"/>
       <c r="N445" s="3" t="n"/>
-      <c r="O445" s="3" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="n"/>
@@ -8153,7 +7684,6 @@
       <c r="L446" s="3" t="n"/>
       <c r="M446" s="3" t="n"/>
       <c r="N446" s="3" t="n"/>
-      <c r="O446" s="3" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="n"/>
@@ -8170,7 +7700,6 @@
       <c r="L447" s="3" t="n"/>
       <c r="M447" s="3" t="n"/>
       <c r="N447" s="3" t="n"/>
-      <c r="O447" s="3" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="n"/>
@@ -8187,7 +7716,6 @@
       <c r="L448" s="3" t="n"/>
       <c r="M448" s="3" t="n"/>
       <c r="N448" s="3" t="n"/>
-      <c r="O448" s="3" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="3" t="n"/>
@@ -8204,7 +7732,6 @@
       <c r="L449" s="3" t="n"/>
       <c r="M449" s="3" t="n"/>
       <c r="N449" s="3" t="n"/>
-      <c r="O449" s="3" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="n"/>
@@ -8221,7 +7748,6 @@
       <c r="L450" s="3" t="n"/>
       <c r="M450" s="3" t="n"/>
       <c r="N450" s="3" t="n"/>
-      <c r="O450" s="3" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="n"/>
@@ -8238,7 +7764,6 @@
       <c r="L451" s="3" t="n"/>
       <c r="M451" s="3" t="n"/>
       <c r="N451" s="3" t="n"/>
-      <c r="O451" s="3" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="n"/>
@@ -8255,7 +7780,6 @@
       <c r="L452" s="3" t="n"/>
       <c r="M452" s="3" t="n"/>
       <c r="N452" s="3" t="n"/>
-      <c r="O452" s="3" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="n"/>
@@ -8272,7 +7796,6 @@
       <c r="L453" s="3" t="n"/>
       <c r="M453" s="3" t="n"/>
       <c r="N453" s="3" t="n"/>
-      <c r="O453" s="3" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="n"/>
@@ -8289,7 +7812,6 @@
       <c r="L454" s="3" t="n"/>
       <c r="M454" s="3" t="n"/>
       <c r="N454" s="3" t="n"/>
-      <c r="O454" s="3" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="n"/>
@@ -8306,7 +7828,6 @@
       <c r="L455" s="3" t="n"/>
       <c r="M455" s="3" t="n"/>
       <c r="N455" s="3" t="n"/>
-      <c r="O455" s="3" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="3" t="n"/>
@@ -8323,7 +7844,6 @@
       <c r="L456" s="3" t="n"/>
       <c r="M456" s="3" t="n"/>
       <c r="N456" s="3" t="n"/>
-      <c r="O456" s="3" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="n"/>
@@ -8340,7 +7860,6 @@
       <c r="L457" s="3" t="n"/>
       <c r="M457" s="3" t="n"/>
       <c r="N457" s="3" t="n"/>
-      <c r="O457" s="3" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="n"/>
@@ -8357,7 +7876,6 @@
       <c r="L458" s="3" t="n"/>
       <c r="M458" s="3" t="n"/>
       <c r="N458" s="3" t="n"/>
-      <c r="O458" s="3" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="n"/>
@@ -8374,7 +7892,6 @@
       <c r="L459" s="3" t="n"/>
       <c r="M459" s="3" t="n"/>
       <c r="N459" s="3" t="n"/>
-      <c r="O459" s="3" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="n"/>
@@ -8391,7 +7908,6 @@
       <c r="L460" s="3" t="n"/>
       <c r="M460" s="3" t="n"/>
       <c r="N460" s="3" t="n"/>
-      <c r="O460" s="3" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="n"/>
@@ -8408,7 +7924,6 @@
       <c r="L461" s="3" t="n"/>
       <c r="M461" s="3" t="n"/>
       <c r="N461" s="3" t="n"/>
-      <c r="O461" s="3" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="n"/>
@@ -8425,7 +7940,6 @@
       <c r="L462" s="3" t="n"/>
       <c r="M462" s="3" t="n"/>
       <c r="N462" s="3" t="n"/>
-      <c r="O462" s="3" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="3" t="n"/>
@@ -8442,7 +7956,6 @@
       <c r="L463" s="3" t="n"/>
       <c r="M463" s="3" t="n"/>
       <c r="N463" s="3" t="n"/>
-      <c r="O463" s="3" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="n"/>
@@ -8459,7 +7972,6 @@
       <c r="L464" s="3" t="n"/>
       <c r="M464" s="3" t="n"/>
       <c r="N464" s="3" t="n"/>
-      <c r="O464" s="3" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="n"/>
@@ -8476,7 +7988,6 @@
       <c r="L465" s="3" t="n"/>
       <c r="M465" s="3" t="n"/>
       <c r="N465" s="3" t="n"/>
-      <c r="O465" s="3" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="n"/>
@@ -8493,7 +8004,6 @@
       <c r="L466" s="3" t="n"/>
       <c r="M466" s="3" t="n"/>
       <c r="N466" s="3" t="n"/>
-      <c r="O466" s="3" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="n"/>
@@ -8510,7 +8020,6 @@
       <c r="L467" s="3" t="n"/>
       <c r="M467" s="3" t="n"/>
       <c r="N467" s="3" t="n"/>
-      <c r="O467" s="3" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="n"/>
@@ -8527,7 +8036,6 @@
       <c r="L468" s="3" t="n"/>
       <c r="M468" s="3" t="n"/>
       <c r="N468" s="3" t="n"/>
-      <c r="O468" s="3" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="n"/>
@@ -8544,7 +8052,6 @@
       <c r="L469" s="3" t="n"/>
       <c r="M469" s="3" t="n"/>
       <c r="N469" s="3" t="n"/>
-      <c r="O469" s="3" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="3" t="n"/>
@@ -8561,7 +8068,6 @@
       <c r="L470" s="3" t="n"/>
       <c r="M470" s="3" t="n"/>
       <c r="N470" s="3" t="n"/>
-      <c r="O470" s="3" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="n"/>
@@ -8578,7 +8084,6 @@
       <c r="L471" s="3" t="n"/>
       <c r="M471" s="3" t="n"/>
       <c r="N471" s="3" t="n"/>
-      <c r="O471" s="3" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="n"/>
@@ -8595,7 +8100,6 @@
       <c r="L472" s="3" t="n"/>
       <c r="M472" s="3" t="n"/>
       <c r="N472" s="3" t="n"/>
-      <c r="O472" s="3" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="n"/>
@@ -8612,7 +8116,6 @@
       <c r="L473" s="3" t="n"/>
       <c r="M473" s="3" t="n"/>
       <c r="N473" s="3" t="n"/>
-      <c r="O473" s="3" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="n"/>
@@ -8629,7 +8132,6 @@
       <c r="L474" s="3" t="n"/>
       <c r="M474" s="3" t="n"/>
       <c r="N474" s="3" t="n"/>
-      <c r="O474" s="3" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="n"/>
@@ -8646,7 +8148,6 @@
       <c r="L475" s="3" t="n"/>
       <c r="M475" s="3" t="n"/>
       <c r="N475" s="3" t="n"/>
-      <c r="O475" s="3" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="n"/>
@@ -8663,7 +8164,6 @@
       <c r="L476" s="3" t="n"/>
       <c r="M476" s="3" t="n"/>
       <c r="N476" s="3" t="n"/>
-      <c r="O476" s="3" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="3" t="n"/>
@@ -8680,7 +8180,6 @@
       <c r="L477" s="3" t="n"/>
       <c r="M477" s="3" t="n"/>
       <c r="N477" s="3" t="n"/>
-      <c r="O477" s="3" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="n"/>
@@ -8697,7 +8196,6 @@
       <c r="L478" s="3" t="n"/>
       <c r="M478" s="3" t="n"/>
       <c r="N478" s="3" t="n"/>
-      <c r="O478" s="3" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="n"/>
@@ -8714,7 +8212,6 @@
       <c r="L479" s="3" t="n"/>
       <c r="M479" s="3" t="n"/>
       <c r="N479" s="3" t="n"/>
-      <c r="O479" s="3" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="n"/>
@@ -8731,7 +8228,6 @@
       <c r="L480" s="3" t="n"/>
       <c r="M480" s="3" t="n"/>
       <c r="N480" s="3" t="n"/>
-      <c r="O480" s="3" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="n"/>
@@ -8748,7 +8244,6 @@
       <c r="L481" s="3" t="n"/>
       <c r="M481" s="3" t="n"/>
       <c r="N481" s="3" t="n"/>
-      <c r="O481" s="3" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="n"/>
@@ -8765,7 +8260,6 @@
       <c r="L482" s="3" t="n"/>
       <c r="M482" s="3" t="n"/>
       <c r="N482" s="3" t="n"/>
-      <c r="O482" s="3" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="3" t="n"/>
@@ -8782,7 +8276,6 @@
       <c r="L483" s="3" t="n"/>
       <c r="M483" s="3" t="n"/>
       <c r="N483" s="3" t="n"/>
-      <c r="O483" s="3" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="3" t="n"/>
@@ -8799,7 +8292,6 @@
       <c r="L484" s="3" t="n"/>
       <c r="M484" s="3" t="n"/>
       <c r="N484" s="3" t="n"/>
-      <c r="O484" s="3" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="n"/>
@@ -8816,7 +8308,6 @@
       <c r="L485" s="3" t="n"/>
       <c r="M485" s="3" t="n"/>
       <c r="N485" s="3" t="n"/>
-      <c r="O485" s="3" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="n"/>
@@ -8833,7 +8324,6 @@
       <c r="L486" s="3" t="n"/>
       <c r="M486" s="3" t="n"/>
       <c r="N486" s="3" t="n"/>
-      <c r="O486" s="3" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="n"/>
@@ -8850,7 +8340,6 @@
       <c r="L487" s="3" t="n"/>
       <c r="M487" s="3" t="n"/>
       <c r="N487" s="3" t="n"/>
-      <c r="O487" s="3" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="n"/>
@@ -8867,7 +8356,6 @@
       <c r="L488" s="3" t="n"/>
       <c r="M488" s="3" t="n"/>
       <c r="N488" s="3" t="n"/>
-      <c r="O488" s="3" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="n"/>
@@ -8884,7 +8372,6 @@
       <c r="L489" s="3" t="n"/>
       <c r="M489" s="3" t="n"/>
       <c r="N489" s="3" t="n"/>
-      <c r="O489" s="3" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="n"/>
@@ -8901,7 +8388,6 @@
       <c r="L490" s="3" t="n"/>
       <c r="M490" s="3" t="n"/>
       <c r="N490" s="3" t="n"/>
-      <c r="O490" s="3" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="3" t="n"/>
@@ -8918,7 +8404,6 @@
       <c r="L491" s="3" t="n"/>
       <c r="M491" s="3" t="n"/>
       <c r="N491" s="3" t="n"/>
-      <c r="O491" s="3" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="n"/>
@@ -8935,7 +8420,6 @@
       <c r="L492" s="3" t="n"/>
       <c r="M492" s="3" t="n"/>
       <c r="N492" s="3" t="n"/>
-      <c r="O492" s="3" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="n"/>
@@ -8952,7 +8436,6 @@
       <c r="L493" s="3" t="n"/>
       <c r="M493" s="3" t="n"/>
       <c r="N493" s="3" t="n"/>
-      <c r="O493" s="3" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="n"/>
@@ -8969,7 +8452,6 @@
       <c r="L494" s="3" t="n"/>
       <c r="M494" s="3" t="n"/>
       <c r="N494" s="3" t="n"/>
-      <c r="O494" s="3" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="n"/>
@@ -8986,7 +8468,6 @@
       <c r="L495" s="3" t="n"/>
       <c r="M495" s="3" t="n"/>
       <c r="N495" s="3" t="n"/>
-      <c r="O495" s="3" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="n"/>
@@ -9003,7 +8484,6 @@
       <c r="L496" s="3" t="n"/>
       <c r="M496" s="3" t="n"/>
       <c r="N496" s="3" t="n"/>
-      <c r="O496" s="3" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="3" t="n"/>
@@ -9020,7 +8500,6 @@
       <c r="L497" s="3" t="n"/>
       <c r="M497" s="3" t="n"/>
       <c r="N497" s="3" t="n"/>
-      <c r="O497" s="3" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="3" t="n"/>
@@ -9037,7 +8516,6 @@
       <c r="L498" s="3" t="n"/>
       <c r="M498" s="3" t="n"/>
       <c r="N498" s="3" t="n"/>
-      <c r="O498" s="3" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="n"/>
@@ -9054,7 +8532,6 @@
       <c r="L499" s="3" t="n"/>
       <c r="M499" s="3" t="n"/>
       <c r="N499" s="3" t="n"/>
-      <c r="O499" s="3" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="n"/>
@@ -9071,7 +8548,6 @@
       <c r="L500" s="3" t="n"/>
       <c r="M500" s="3" t="n"/>
       <c r="N500" s="3" t="n"/>
-      <c r="O500" s="3" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="n"/>
@@ -9088,7 +8564,6 @@
       <c r="L501" s="3" t="n"/>
       <c r="M501" s="3" t="n"/>
       <c r="N501" s="3" t="n"/>
-      <c r="O501" s="3" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="3" t="n"/>
@@ -9105,7 +8580,6 @@
       <c r="L502" s="3" t="n"/>
       <c r="M502" s="3" t="n"/>
       <c r="N502" s="3" t="n"/>
-      <c r="O502" s="3" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="3" t="n"/>
@@ -9122,7 +8596,6 @@
       <c r="L503" s="3" t="n"/>
       <c r="M503" s="3" t="n"/>
       <c r="N503" s="3" t="n"/>
-      <c r="O503" s="3" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="3" t="n"/>
@@ -9139,7 +8612,6 @@
       <c r="L504" s="3" t="n"/>
       <c r="M504" s="3" t="n"/>
       <c r="N504" s="3" t="n"/>
-      <c r="O504" s="3" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="3" t="n"/>
@@ -9156,7 +8628,6 @@
       <c r="L505" s="3" t="n"/>
       <c r="M505" s="3" t="n"/>
       <c r="N505" s="3" t="n"/>
-      <c r="O505" s="3" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="3" t="n"/>
@@ -9173,7 +8644,6 @@
       <c r="L506" s="3" t="n"/>
       <c r="M506" s="3" t="n"/>
       <c r="N506" s="3" t="n"/>
-      <c r="O506" s="3" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="3" t="n"/>
@@ -9190,7 +8660,6 @@
       <c r="L507" s="3" t="n"/>
       <c r="M507" s="3" t="n"/>
       <c r="N507" s="3" t="n"/>
-      <c r="O507" s="3" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="3" t="n"/>
@@ -9207,7 +8676,6 @@
       <c r="L508" s="3" t="n"/>
       <c r="M508" s="3" t="n"/>
       <c r="N508" s="3" t="n"/>
-      <c r="O508" s="3" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="3" t="n"/>
@@ -9224,7 +8692,6 @@
       <c r="L509" s="3" t="n"/>
       <c r="M509" s="3" t="n"/>
       <c r="N509" s="3" t="n"/>
-      <c r="O509" s="3" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="3" t="n"/>
@@ -9241,7 +8708,6 @@
       <c r="L510" s="3" t="n"/>
       <c r="M510" s="3" t="n"/>
       <c r="N510" s="3" t="n"/>
-      <c r="O510" s="3" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="3" t="n"/>
@@ -9258,7 +8724,6 @@
       <c r="L511" s="3" t="n"/>
       <c r="M511" s="3" t="n"/>
       <c r="N511" s="3" t="n"/>
-      <c r="O511" s="3" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="3" t="n"/>
@@ -9275,7 +8740,6 @@
       <c r="L512" s="3" t="n"/>
       <c r="M512" s="3" t="n"/>
       <c r="N512" s="3" t="n"/>
-      <c r="O512" s="3" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="3" t="n"/>
@@ -9292,7 +8756,6 @@
       <c r="L513" s="3" t="n"/>
       <c r="M513" s="3" t="n"/>
       <c r="N513" s="3" t="n"/>
-      <c r="O513" s="3" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="3" t="n"/>
@@ -9309,7 +8772,6 @@
       <c r="L514" s="3" t="n"/>
       <c r="M514" s="3" t="n"/>
       <c r="N514" s="3" t="n"/>
-      <c r="O514" s="3" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="3" t="n"/>
@@ -9326,7 +8788,6 @@
       <c r="L515" s="3" t="n"/>
       <c r="M515" s="3" t="n"/>
       <c r="N515" s="3" t="n"/>
-      <c r="O515" s="3" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="3" t="n"/>
@@ -9343,7 +8804,6 @@
       <c r="L516" s="3" t="n"/>
       <c r="M516" s="3" t="n"/>
       <c r="N516" s="3" t="n"/>
-      <c r="O516" s="3" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="3" t="n"/>
@@ -9360,7 +8820,6 @@
       <c r="L517" s="3" t="n"/>
       <c r="M517" s="3" t="n"/>
       <c r="N517" s="3" t="n"/>
-      <c r="O517" s="3" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="3" t="n"/>
@@ -9377,7 +8836,6 @@
       <c r="L518" s="3" t="n"/>
       <c r="M518" s="3" t="n"/>
       <c r="N518" s="3" t="n"/>
-      <c r="O518" s="3" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="3" t="n"/>
@@ -9394,7 +8852,6 @@
       <c r="L519" s="3" t="n"/>
       <c r="M519" s="3" t="n"/>
       <c r="N519" s="3" t="n"/>
-      <c r="O519" s="3" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="3" t="n"/>
@@ -9411,7 +8868,6 @@
       <c r="L520" s="3" t="n"/>
       <c r="M520" s="3" t="n"/>
       <c r="N520" s="3" t="n"/>
-      <c r="O520" s="3" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="3" t="n"/>
@@ -9428,7 +8884,6 @@
       <c r="L521" s="3" t="n"/>
       <c r="M521" s="3" t="n"/>
       <c r="N521" s="3" t="n"/>
-      <c r="O521" s="3" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="3" t="n"/>
@@ -9445,7 +8900,6 @@
       <c r="L522" s="3" t="n"/>
       <c r="M522" s="3" t="n"/>
       <c r="N522" s="3" t="n"/>
-      <c r="O522" s="3" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="3" t="n"/>
@@ -9462,7 +8916,6 @@
       <c r="L523" s="3" t="n"/>
       <c r="M523" s="3" t="n"/>
       <c r="N523" s="3" t="n"/>
-      <c r="O523" s="3" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="3" t="n"/>
@@ -9479,7 +8932,6 @@
       <c r="L524" s="3" t="n"/>
       <c r="M524" s="3" t="n"/>
       <c r="N524" s="3" t="n"/>
-      <c r="O524" s="3" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="3" t="n"/>
@@ -9496,7 +8948,6 @@
       <c r="L525" s="3" t="n"/>
       <c r="M525" s="3" t="n"/>
       <c r="N525" s="3" t="n"/>
-      <c r="O525" s="3" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="3" t="n"/>
@@ -9513,7 +8964,6 @@
       <c r="L526" s="3" t="n"/>
       <c r="M526" s="3" t="n"/>
       <c r="N526" s="3" t="n"/>
-      <c r="O526" s="3" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="3" t="n"/>
@@ -9530,7 +8980,6 @@
       <c r="L527" s="3" t="n"/>
       <c r="M527" s="3" t="n"/>
       <c r="N527" s="3" t="n"/>
-      <c r="O527" s="3" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="3" t="n"/>
@@ -9547,7 +8996,6 @@
       <c r="L528" s="3" t="n"/>
       <c r="M528" s="3" t="n"/>
       <c r="N528" s="3" t="n"/>
-      <c r="O528" s="3" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="3" t="n"/>
@@ -9564,7 +9012,6 @@
       <c r="L529" s="3" t="n"/>
       <c r="M529" s="3" t="n"/>
       <c r="N529" s="3" t="n"/>
-      <c r="O529" s="3" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="3" t="n"/>
@@ -9581,7 +9028,6 @@
       <c r="L530" s="3" t="n"/>
       <c r="M530" s="3" t="n"/>
       <c r="N530" s="3" t="n"/>
-      <c r="O530" s="3" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="3" t="n"/>
@@ -9598,7 +9044,6 @@
       <c r="L531" s="3" t="n"/>
       <c r="M531" s="3" t="n"/>
       <c r="N531" s="3" t="n"/>
-      <c r="O531" s="3" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="3" t="n"/>
@@ -9615,7 +9060,6 @@
       <c r="L532" s="3" t="n"/>
       <c r="M532" s="3" t="n"/>
       <c r="N532" s="3" t="n"/>
-      <c r="O532" s="3" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="3" t="n"/>
@@ -9632,7 +9076,6 @@
       <c r="L533" s="3" t="n"/>
       <c r="M533" s="3" t="n"/>
       <c r="N533" s="3" t="n"/>
-      <c r="O533" s="3" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="3" t="n"/>
@@ -9649,7 +9092,6 @@
       <c r="L534" s="3" t="n"/>
       <c r="M534" s="3" t="n"/>
       <c r="N534" s="3" t="n"/>
-      <c r="O534" s="3" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="3" t="n"/>
@@ -9666,7 +9108,6 @@
       <c r="L535" s="3" t="n"/>
       <c r="M535" s="3" t="n"/>
       <c r="N535" s="3" t="n"/>
-      <c r="O535" s="3" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="3" t="n"/>
@@ -9683,7 +9124,6 @@
       <c r="L536" s="3" t="n"/>
       <c r="M536" s="3" t="n"/>
       <c r="N536" s="3" t="n"/>
-      <c r="O536" s="3" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="3" t="n"/>
@@ -9700,7 +9140,6 @@
       <c r="L537" s="3" t="n"/>
       <c r="M537" s="3" t="n"/>
       <c r="N537" s="3" t="n"/>
-      <c r="O537" s="3" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="3" t="n"/>
@@ -9717,7 +9156,6 @@
       <c r="L538" s="3" t="n"/>
       <c r="M538" s="3" t="n"/>
       <c r="N538" s="3" t="n"/>
-      <c r="O538" s="3" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="3" t="n"/>
@@ -9734,7 +9172,6 @@
       <c r="L539" s="3" t="n"/>
       <c r="M539" s="3" t="n"/>
       <c r="N539" s="3" t="n"/>
-      <c r="O539" s="3" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="3" t="n"/>
@@ -9751,7 +9188,6 @@
       <c r="L540" s="3" t="n"/>
       <c r="M540" s="3" t="n"/>
       <c r="N540" s="3" t="n"/>
-      <c r="O540" s="3" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="3" t="n"/>
@@ -9768,7 +9204,6 @@
       <c r="L541" s="3" t="n"/>
       <c r="M541" s="3" t="n"/>
       <c r="N541" s="3" t="n"/>
-      <c r="O541" s="3" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="3" t="n"/>
@@ -9785,7 +9220,6 @@
       <c r="L542" s="3" t="n"/>
       <c r="M542" s="3" t="n"/>
       <c r="N542" s="3" t="n"/>
-      <c r="O542" s="3" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="3" t="n"/>
@@ -9802,7 +9236,6 @@
       <c r="L543" s="3" t="n"/>
       <c r="M543" s="3" t="n"/>
       <c r="N543" s="3" t="n"/>
-      <c r="O543" s="3" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="3" t="n"/>
@@ -9819,7 +9252,6 @@
       <c r="L544" s="3" t="n"/>
       <c r="M544" s="3" t="n"/>
       <c r="N544" s="3" t="n"/>
-      <c r="O544" s="3" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="3" t="n"/>
@@ -9836,7 +9268,6 @@
       <c r="L545" s="3" t="n"/>
       <c r="M545" s="3" t="n"/>
       <c r="N545" s="3" t="n"/>
-      <c r="O545" s="3" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="3" t="n"/>
@@ -9853,7 +9284,6 @@
       <c r="L546" s="3" t="n"/>
       <c r="M546" s="3" t="n"/>
       <c r="N546" s="3" t="n"/>
-      <c r="O546" s="3" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="3" t="n"/>
@@ -9870,7 +9300,6 @@
       <c r="L547" s="3" t="n"/>
       <c r="M547" s="3" t="n"/>
       <c r="N547" s="3" t="n"/>
-      <c r="O547" s="3" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="3" t="n"/>
@@ -9887,7 +9316,6 @@
       <c r="L548" s="3" t="n"/>
       <c r="M548" s="3" t="n"/>
       <c r="N548" s="3" t="n"/>
-      <c r="O548" s="3" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="3" t="n"/>
@@ -9904,7 +9332,6 @@
       <c r="L549" s="3" t="n"/>
       <c r="M549" s="3" t="n"/>
       <c r="N549" s="3" t="n"/>
-      <c r="O549" s="3" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="3" t="n"/>
@@ -9921,7 +9348,6 @@
       <c r="L550" s="3" t="n"/>
       <c r="M550" s="3" t="n"/>
       <c r="N550" s="3" t="n"/>
-      <c r="O550" s="3" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="3" t="n"/>
@@ -9938,7 +9364,6 @@
       <c r="L551" s="3" t="n"/>
       <c r="M551" s="3" t="n"/>
       <c r="N551" s="3" t="n"/>
-      <c r="O551" s="3" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="3" t="n"/>
@@ -9955,7 +9380,6 @@
       <c r="L552" s="3" t="n"/>
       <c r="M552" s="3" t="n"/>
       <c r="N552" s="3" t="n"/>
-      <c r="O552" s="3" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="3" t="n"/>
@@ -9972,7 +9396,6 @@
       <c r="L553" s="3" t="n"/>
       <c r="M553" s="3" t="n"/>
       <c r="N553" s="3" t="n"/>
-      <c r="O553" s="3" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="3" t="n"/>
@@ -9989,7 +9412,6 @@
       <c r="L554" s="3" t="n"/>
       <c r="M554" s="3" t="n"/>
       <c r="N554" s="3" t="n"/>
-      <c r="O554" s="3" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="3" t="n"/>
@@ -10006,7 +9428,6 @@
       <c r="L555" s="3" t="n"/>
       <c r="M555" s="3" t="n"/>
       <c r="N555" s="3" t="n"/>
-      <c r="O555" s="3" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="3" t="n"/>
@@ -10023,7 +9444,6 @@
       <c r="L556" s="3" t="n"/>
       <c r="M556" s="3" t="n"/>
       <c r="N556" s="3" t="n"/>
-      <c r="O556" s="3" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="3" t="n"/>
@@ -10040,7 +9460,6 @@
       <c r="L557" s="3" t="n"/>
       <c r="M557" s="3" t="n"/>
       <c r="N557" s="3" t="n"/>
-      <c r="O557" s="3" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="3" t="n"/>
@@ -10057,7 +9476,6 @@
       <c r="L558" s="3" t="n"/>
       <c r="M558" s="3" t="n"/>
       <c r="N558" s="3" t="n"/>
-      <c r="O558" s="3" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="3" t="n"/>
@@ -10074,7 +9492,6 @@
       <c r="L559" s="3" t="n"/>
       <c r="M559" s="3" t="n"/>
       <c r="N559" s="3" t="n"/>
-      <c r="O559" s="3" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="3" t="n"/>
@@ -10091,7 +9508,6 @@
       <c r="L560" s="3" t="n"/>
       <c r="M560" s="3" t="n"/>
       <c r="N560" s="3" t="n"/>
-      <c r="O560" s="3" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="3" t="n"/>
@@ -10108,7 +9524,6 @@
       <c r="L561" s="3" t="n"/>
       <c r="M561" s="3" t="n"/>
       <c r="N561" s="3" t="n"/>
-      <c r="O561" s="3" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="3" t="n"/>
@@ -10125,7 +9540,6 @@
       <c r="L562" s="3" t="n"/>
       <c r="M562" s="3" t="n"/>
       <c r="N562" s="3" t="n"/>
-      <c r="O562" s="3" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="3" t="n"/>
@@ -10142,7 +9556,6 @@
       <c r="L563" s="3" t="n"/>
       <c r="M563" s="3" t="n"/>
       <c r="N563" s="3" t="n"/>
-      <c r="O563" s="3" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="3" t="n"/>
@@ -10159,7 +9572,6 @@
       <c r="L564" s="3" t="n"/>
       <c r="M564" s="3" t="n"/>
       <c r="N564" s="3" t="n"/>
-      <c r="O564" s="3" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="3" t="n"/>
@@ -10176,7 +9588,6 @@
       <c r="L565" s="3" t="n"/>
       <c r="M565" s="3" t="n"/>
       <c r="N565" s="3" t="n"/>
-      <c r="O565" s="3" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="3" t="n"/>
@@ -10193,7 +9604,6 @@
       <c r="L566" s="3" t="n"/>
       <c r="M566" s="3" t="n"/>
       <c r="N566" s="3" t="n"/>
-      <c r="O566" s="3" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="3" t="n"/>
@@ -10210,7 +9620,6 @@
       <c r="L567" s="3" t="n"/>
       <c r="M567" s="3" t="n"/>
       <c r="N567" s="3" t="n"/>
-      <c r="O567" s="3" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="3" t="n"/>
@@ -10227,7 +9636,6 @@
       <c r="L568" s="3" t="n"/>
       <c r="M568" s="3" t="n"/>
       <c r="N568" s="3" t="n"/>
-      <c r="O568" s="3" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="3" t="n"/>
@@ -10244,7 +9652,6 @@
       <c r="L569" s="3" t="n"/>
       <c r="M569" s="3" t="n"/>
       <c r="N569" s="3" t="n"/>
-      <c r="O569" s="3" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="3" t="n"/>
@@ -10261,7 +9668,6 @@
       <c r="L570" s="3" t="n"/>
       <c r="M570" s="3" t="n"/>
       <c r="N570" s="3" t="n"/>
-      <c r="O570" s="3" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="3" t="n"/>
@@ -10278,7 +9684,6 @@
       <c r="L571" s="3" t="n"/>
       <c r="M571" s="3" t="n"/>
       <c r="N571" s="3" t="n"/>
-      <c r="O571" s="3" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="3" t="n"/>
@@ -10295,7 +9700,6 @@
       <c r="L572" s="3" t="n"/>
       <c r="M572" s="3" t="n"/>
       <c r="N572" s="3" t="n"/>
-      <c r="O572" s="3" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="3" t="n"/>
@@ -10312,7 +9716,6 @@
       <c r="L573" s="3" t="n"/>
       <c r="M573" s="3" t="n"/>
       <c r="N573" s="3" t="n"/>
-      <c r="O573" s="3" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="3" t="n"/>
@@ -10329,7 +9732,6 @@
       <c r="L574" s="3" t="n"/>
       <c r="M574" s="3" t="n"/>
       <c r="N574" s="3" t="n"/>
-      <c r="O574" s="3" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="3" t="n"/>
@@ -10346,7 +9748,6 @@
       <c r="L575" s="3" t="n"/>
       <c r="M575" s="3" t="n"/>
       <c r="N575" s="3" t="n"/>
-      <c r="O575" s="3" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="3" t="n"/>
@@ -10363,7 +9764,6 @@
       <c r="L576" s="3" t="n"/>
       <c r="M576" s="3" t="n"/>
       <c r="N576" s="3" t="n"/>
-      <c r="O576" s="3" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="3" t="n"/>
@@ -10380,7 +9780,6 @@
       <c r="L577" s="3" t="n"/>
       <c r="M577" s="3" t="n"/>
       <c r="N577" s="3" t="n"/>
-      <c r="O577" s="3" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="3" t="n"/>
@@ -10397,7 +9796,6 @@
       <c r="L578" s="3" t="n"/>
       <c r="M578" s="3" t="n"/>
       <c r="N578" s="3" t="n"/>
-      <c r="O578" s="3" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="3" t="n"/>
@@ -10414,7 +9812,6 @@
       <c r="L579" s="3" t="n"/>
       <c r="M579" s="3" t="n"/>
       <c r="N579" s="3" t="n"/>
-      <c r="O579" s="3" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="3" t="n"/>
@@ -10431,7 +9828,6 @@
       <c r="L580" s="3" t="n"/>
       <c r="M580" s="3" t="n"/>
       <c r="N580" s="3" t="n"/>
-      <c r="O580" s="3" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="3" t="n"/>
@@ -10448,7 +9844,6 @@
       <c r="L581" s="3" t="n"/>
       <c r="M581" s="3" t="n"/>
       <c r="N581" s="3" t="n"/>
-      <c r="O581" s="3" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="3" t="n"/>
@@ -10465,7 +9860,6 @@
       <c r="L582" s="3" t="n"/>
       <c r="M582" s="3" t="n"/>
       <c r="N582" s="3" t="n"/>
-      <c r="O582" s="3" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="3" t="n"/>
@@ -10482,7 +9876,6 @@
       <c r="L583" s="3" t="n"/>
       <c r="M583" s="3" t="n"/>
       <c r="N583" s="3" t="n"/>
-      <c r="O583" s="3" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="3" t="n"/>
@@ -10499,7 +9892,6 @@
       <c r="L584" s="3" t="n"/>
       <c r="M584" s="3" t="n"/>
       <c r="N584" s="3" t="n"/>
-      <c r="O584" s="3" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="3" t="n"/>
@@ -10516,7 +9908,6 @@
       <c r="L585" s="3" t="n"/>
       <c r="M585" s="3" t="n"/>
       <c r="N585" s="3" t="n"/>
-      <c r="O585" s="3" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="3" t="n"/>
@@ -10533,7 +9924,6 @@
       <c r="L586" s="3" t="n"/>
       <c r="M586" s="3" t="n"/>
       <c r="N586" s="3" t="n"/>
-      <c r="O586" s="3" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="3" t="n"/>
@@ -10550,7 +9940,6 @@
       <c r="L587" s="3" t="n"/>
       <c r="M587" s="3" t="n"/>
       <c r="N587" s="3" t="n"/>
-      <c r="O587" s="3" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="3" t="n"/>
@@ -10567,7 +9956,6 @@
       <c r="L588" s="3" t="n"/>
       <c r="M588" s="3" t="n"/>
       <c r="N588" s="3" t="n"/>
-      <c r="O588" s="3" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="3" t="n"/>
@@ -10584,7 +9972,6 @@
       <c r="L589" s="3" t="n"/>
       <c r="M589" s="3" t="n"/>
       <c r="N589" s="3" t="n"/>
-      <c r="O589" s="3" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="3" t="n"/>
@@ -10601,7 +9988,6 @@
       <c r="L590" s="3" t="n"/>
       <c r="M590" s="3" t="n"/>
       <c r="N590" s="3" t="n"/>
-      <c r="O590" s="3" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="3" t="n"/>
@@ -10618,7 +10004,6 @@
       <c r="L591" s="3" t="n"/>
       <c r="M591" s="3" t="n"/>
       <c r="N591" s="3" t="n"/>
-      <c r="O591" s="3" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="3" t="n"/>
@@ -10635,7 +10020,6 @@
       <c r="L592" s="3" t="n"/>
       <c r="M592" s="3" t="n"/>
       <c r="N592" s="3" t="n"/>
-      <c r="O592" s="3" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="3" t="n"/>
@@ -10652,7 +10036,6 @@
       <c r="L593" s="3" t="n"/>
       <c r="M593" s="3" t="n"/>
       <c r="N593" s="3" t="n"/>
-      <c r="O593" s="3" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="3" t="n"/>
@@ -10669,7 +10052,6 @@
       <c r="L594" s="3" t="n"/>
       <c r="M594" s="3" t="n"/>
       <c r="N594" s="3" t="n"/>
-      <c r="O594" s="3" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="3" t="n"/>
@@ -10686,7 +10068,6 @@
       <c r="L595" s="3" t="n"/>
       <c r="M595" s="3" t="n"/>
       <c r="N595" s="3" t="n"/>
-      <c r="O595" s="3" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="3" t="n"/>
@@ -10703,7 +10084,6 @@
       <c r="L596" s="3" t="n"/>
       <c r="M596" s="3" t="n"/>
       <c r="N596" s="3" t="n"/>
-      <c r="O596" s="3" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="3" t="n"/>
@@ -10720,7 +10100,6 @@
       <c r="L597" s="3" t="n"/>
       <c r="M597" s="3" t="n"/>
       <c r="N597" s="3" t="n"/>
-      <c r="O597" s="3" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="3" t="n"/>
@@ -10737,7 +10116,6 @@
       <c r="L598" s="3" t="n"/>
       <c r="M598" s="3" t="n"/>
       <c r="N598" s="3" t="n"/>
-      <c r="O598" s="3" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="3" t="n"/>
@@ -10754,7 +10132,6 @@
       <c r="L599" s="3" t="n"/>
       <c r="M599" s="3" t="n"/>
       <c r="N599" s="3" t="n"/>
-      <c r="O599" s="3" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="3" t="n"/>
@@ -10771,7 +10148,6 @@
       <c r="L600" s="3" t="n"/>
       <c r="M600" s="3" t="n"/>
       <c r="N600" s="3" t="n"/>
-      <c r="O600" s="3" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="3" t="n"/>
@@ -10788,7 +10164,6 @@
       <c r="L601" s="3" t="n"/>
       <c r="M601" s="3" t="n"/>
       <c r="N601" s="3" t="n"/>
-      <c r="O601" s="3" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="3" t="n"/>
@@ -10805,7 +10180,6 @@
       <c r="L602" s="3" t="n"/>
       <c r="M602" s="3" t="n"/>
       <c r="N602" s="3" t="n"/>
-      <c r="O602" s="3" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="3" t="n"/>
@@ -10822,7 +10196,6 @@
       <c r="L603" s="3" t="n"/>
       <c r="M603" s="3" t="n"/>
       <c r="N603" s="3" t="n"/>
-      <c r="O603" s="3" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="3" t="n"/>
@@ -10839,7 +10212,6 @@
       <c r="L604" s="3" t="n"/>
       <c r="M604" s="3" t="n"/>
       <c r="N604" s="3" t="n"/>
-      <c r="O604" s="3" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="3" t="n"/>
@@ -10856,7 +10228,6 @@
       <c r="L605" s="3" t="n"/>
       <c r="M605" s="3" t="n"/>
       <c r="N605" s="3" t="n"/>
-      <c r="O605" s="3" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="3" t="n"/>
@@ -10873,7 +10244,6 @@
       <c r="L606" s="3" t="n"/>
       <c r="M606" s="3" t="n"/>
       <c r="N606" s="3" t="n"/>
-      <c r="O606" s="3" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="3" t="n"/>
@@ -10890,7 +10260,6 @@
       <c r="L607" s="3" t="n"/>
       <c r="M607" s="3" t="n"/>
       <c r="N607" s="3" t="n"/>
-      <c r="O607" s="3" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="3" t="n"/>
@@ -10907,7 +10276,6 @@
       <c r="L608" s="3" t="n"/>
       <c r="M608" s="3" t="n"/>
       <c r="N608" s="3" t="n"/>
-      <c r="O608" s="3" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="3" t="n"/>
@@ -10924,7 +10292,6 @@
       <c r="L609" s="3" t="n"/>
       <c r="M609" s="3" t="n"/>
       <c r="N609" s="3" t="n"/>
-      <c r="O609" s="3" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="3" t="n"/>
@@ -10941,7 +10308,6 @@
       <c r="L610" s="3" t="n"/>
       <c r="M610" s="3" t="n"/>
       <c r="N610" s="3" t="n"/>
-      <c r="O610" s="3" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="3" t="n"/>
@@ -10958,7 +10324,6 @@
       <c r="L611" s="3" t="n"/>
       <c r="M611" s="3" t="n"/>
       <c r="N611" s="3" t="n"/>
-      <c r="O611" s="3" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="3" t="n"/>
@@ -10975,7 +10340,6 @@
       <c r="L612" s="3" t="n"/>
       <c r="M612" s="3" t="n"/>
       <c r="N612" s="3" t="n"/>
-      <c r="O612" s="3" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="3" t="n"/>
@@ -10992,7 +10356,6 @@
       <c r="L613" s="3" t="n"/>
       <c r="M613" s="3" t="n"/>
       <c r="N613" s="3" t="n"/>
-      <c r="O613" s="3" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="3" t="n"/>
@@ -11009,7 +10372,6 @@
       <c r="L614" s="3" t="n"/>
       <c r="M614" s="3" t="n"/>
       <c r="N614" s="3" t="n"/>
-      <c r="O614" s="3" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="3" t="n"/>
@@ -11026,7 +10388,6 @@
       <c r="L615" s="3" t="n"/>
       <c r="M615" s="3" t="n"/>
       <c r="N615" s="3" t="n"/>
-      <c r="O615" s="3" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="3" t="n"/>
@@ -11043,7 +10404,6 @@
       <c r="L616" s="3" t="n"/>
       <c r="M616" s="3" t="n"/>
       <c r="N616" s="3" t="n"/>
-      <c r="O616" s="3" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="3" t="n"/>
@@ -11060,7 +10420,6 @@
       <c r="L617" s="3" t="n"/>
       <c r="M617" s="3" t="n"/>
       <c r="N617" s="3" t="n"/>
-      <c r="O617" s="3" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="3" t="n"/>
@@ -11077,7 +10436,6 @@
       <c r="L618" s="3" t="n"/>
       <c r="M618" s="3" t="n"/>
       <c r="N618" s="3" t="n"/>
-      <c r="O618" s="3" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="3" t="n"/>
@@ -11094,7 +10452,6 @@
       <c r="L619" s="3" t="n"/>
       <c r="M619" s="3" t="n"/>
       <c r="N619" s="3" t="n"/>
-      <c r="O619" s="3" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="3" t="n"/>
@@ -11111,7 +10468,6 @@
       <c r="L620" s="3" t="n"/>
       <c r="M620" s="3" t="n"/>
       <c r="N620" s="3" t="n"/>
-      <c r="O620" s="3" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="3" t="n"/>
@@ -11128,7 +10484,6 @@
       <c r="L621" s="3" t="n"/>
       <c r="M621" s="3" t="n"/>
       <c r="N621" s="3" t="n"/>
-      <c r="O621" s="3" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="3" t="n"/>
@@ -11145,7 +10500,6 @@
       <c r="L622" s="3" t="n"/>
       <c r="M622" s="3" t="n"/>
       <c r="N622" s="3" t="n"/>
-      <c r="O622" s="3" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="3" t="n"/>
@@ -11162,7 +10516,6 @@
       <c r="L623" s="3" t="n"/>
       <c r="M623" s="3" t="n"/>
       <c r="N623" s="3" t="n"/>
-      <c r="O623" s="3" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="3" t="n"/>
@@ -11179,7 +10532,6 @@
       <c r="L624" s="3" t="n"/>
       <c r="M624" s="3" t="n"/>
       <c r="N624" s="3" t="n"/>
-      <c r="O624" s="3" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="3" t="n"/>
@@ -11196,7 +10548,6 @@
       <c r="L625" s="3" t="n"/>
       <c r="M625" s="3" t="n"/>
       <c r="N625" s="3" t="n"/>
-      <c r="O625" s="3" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="3" t="n"/>
@@ -11213,7 +10564,6 @@
       <c r="L626" s="3" t="n"/>
       <c r="M626" s="3" t="n"/>
       <c r="N626" s="3" t="n"/>
-      <c r="O626" s="3" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="3" t="n"/>
@@ -11230,7 +10580,6 @@
       <c r="L627" s="3" t="n"/>
       <c r="M627" s="3" t="n"/>
       <c r="N627" s="3" t="n"/>
-      <c r="O627" s="3" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="3" t="n"/>
@@ -11247,7 +10596,6 @@
       <c r="L628" s="3" t="n"/>
       <c r="M628" s="3" t="n"/>
       <c r="N628" s="3" t="n"/>
-      <c r="O628" s="3" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="3" t="n"/>
@@ -11264,7 +10612,6 @@
       <c r="L629" s="3" t="n"/>
       <c r="M629" s="3" t="n"/>
       <c r="N629" s="3" t="n"/>
-      <c r="O629" s="3" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="3" t="n"/>
@@ -11281,7 +10628,6 @@
       <c r="L630" s="3" t="n"/>
       <c r="M630" s="3" t="n"/>
       <c r="N630" s="3" t="n"/>
-      <c r="O630" s="3" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="3" t="n"/>
@@ -11298,7 +10644,6 @@
       <c r="L631" s="3" t="n"/>
       <c r="M631" s="3" t="n"/>
       <c r="N631" s="3" t="n"/>
-      <c r="O631" s="3" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="3" t="n"/>
@@ -11315,7 +10660,6 @@
       <c r="L632" s="3" t="n"/>
       <c r="M632" s="3" t="n"/>
       <c r="N632" s="3" t="n"/>
-      <c r="O632" s="3" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="3" t="n"/>
@@ -11332,7 +10676,6 @@
       <c r="L633" s="3" t="n"/>
       <c r="M633" s="3" t="n"/>
       <c r="N633" s="3" t="n"/>
-      <c r="O633" s="3" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="3" t="n"/>
@@ -11349,7 +10692,6 @@
       <c r="L634" s="3" t="n"/>
       <c r="M634" s="3" t="n"/>
       <c r="N634" s="3" t="n"/>
-      <c r="O634" s="3" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="3" t="n"/>
@@ -11366,7 +10708,6 @@
       <c r="L635" s="3" t="n"/>
       <c r="M635" s="3" t="n"/>
       <c r="N635" s="3" t="n"/>
-      <c r="O635" s="3" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="3" t="n"/>
@@ -11383,7 +10724,6 @@
       <c r="L636" s="3" t="n"/>
       <c r="M636" s="3" t="n"/>
       <c r="N636" s="3" t="n"/>
-      <c r="O636" s="3" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="3" t="n"/>
@@ -11400,7 +10740,6 @@
       <c r="L637" s="3" t="n"/>
       <c r="M637" s="3" t="n"/>
       <c r="N637" s="3" t="n"/>
-      <c r="O637" s="3" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="3" t="n"/>
@@ -11417,7 +10756,6 @@
       <c r="L638" s="3" t="n"/>
       <c r="M638" s="3" t="n"/>
       <c r="N638" s="3" t="n"/>
-      <c r="O638" s="3" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="3" t="n"/>
@@ -11434,7 +10772,6 @@
       <c r="L639" s="3" t="n"/>
       <c r="M639" s="3" t="n"/>
       <c r="N639" s="3" t="n"/>
-      <c r="O639" s="3" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="3" t="n"/>
@@ -11451,7 +10788,6 @@
       <c r="L640" s="3" t="n"/>
       <c r="M640" s="3" t="n"/>
       <c r="N640" s="3" t="n"/>
-      <c r="O640" s="3" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="3" t="n"/>
@@ -11468,7 +10804,6 @@
       <c r="L641" s="3" t="n"/>
       <c r="M641" s="3" t="n"/>
       <c r="N641" s="3" t="n"/>
-      <c r="O641" s="3" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="3" t="n"/>
@@ -11485,7 +10820,6 @@
       <c r="L642" s="3" t="n"/>
       <c r="M642" s="3" t="n"/>
       <c r="N642" s="3" t="n"/>
-      <c r="O642" s="3" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="3" t="n"/>
@@ -11502,7 +10836,6 @@
       <c r="L643" s="3" t="n"/>
       <c r="M643" s="3" t="n"/>
       <c r="N643" s="3" t="n"/>
-      <c r="O643" s="3" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="3" t="n"/>
@@ -11519,7 +10852,6 @@
       <c r="L644" s="3" t="n"/>
       <c r="M644" s="3" t="n"/>
       <c r="N644" s="3" t="n"/>
-      <c r="O644" s="3" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="3" t="n"/>
@@ -11536,7 +10868,6 @@
       <c r="L645" s="3" t="n"/>
       <c r="M645" s="3" t="n"/>
       <c r="N645" s="3" t="n"/>
-      <c r="O645" s="3" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="3" t="n"/>
@@ -11553,7 +10884,6 @@
       <c r="L646" s="3" t="n"/>
       <c r="M646" s="3" t="n"/>
       <c r="N646" s="3" t="n"/>
-      <c r="O646" s="3" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="3" t="n"/>
@@ -11570,7 +10900,6 @@
       <c r="L647" s="3" t="n"/>
       <c r="M647" s="3" t="n"/>
       <c r="N647" s="3" t="n"/>
-      <c r="O647" s="3" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="3" t="n"/>
@@ -11587,7 +10916,6 @@
       <c r="L648" s="3" t="n"/>
       <c r="M648" s="3" t="n"/>
       <c r="N648" s="3" t="n"/>
-      <c r="O648" s="3" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="3" t="n"/>
@@ -11604,7 +10932,6 @@
       <c r="L649" s="3" t="n"/>
       <c r="M649" s="3" t="n"/>
       <c r="N649" s="3" t="n"/>
-      <c r="O649" s="3" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="3" t="n"/>
@@ -11621,7 +10948,6 @@
       <c r="L650" s="3" t="n"/>
       <c r="M650" s="3" t="n"/>
       <c r="N650" s="3" t="n"/>
-      <c r="O650" s="3" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="3" t="n"/>
@@ -11638,7 +10964,6 @@
       <c r="L651" s="3" t="n"/>
       <c r="M651" s="3" t="n"/>
       <c r="N651" s="3" t="n"/>
-      <c r="O651" s="3" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="3" t="n"/>
@@ -11655,7 +10980,6 @@
       <c r="L652" s="3" t="n"/>
       <c r="M652" s="3" t="n"/>
       <c r="N652" s="3" t="n"/>
-      <c r="O652" s="3" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="3" t="n"/>
@@ -11672,7 +10996,6 @@
       <c r="L653" s="3" t="n"/>
       <c r="M653" s="3" t="n"/>
       <c r="N653" s="3" t="n"/>
-      <c r="O653" s="3" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="3" t="n"/>
@@ -11689,7 +11012,6 @@
       <c r="L654" s="3" t="n"/>
       <c r="M654" s="3" t="n"/>
       <c r="N654" s="3" t="n"/>
-      <c r="O654" s="3" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="3" t="n"/>
@@ -11706,7 +11028,6 @@
       <c r="L655" s="3" t="n"/>
       <c r="M655" s="3" t="n"/>
       <c r="N655" s="3" t="n"/>
-      <c r="O655" s="3" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="3" t="n"/>
@@ -11723,7 +11044,6 @@
       <c r="L656" s="3" t="n"/>
       <c r="M656" s="3" t="n"/>
       <c r="N656" s="3" t="n"/>
-      <c r="O656" s="3" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="3" t="n"/>
@@ -11740,7 +11060,6 @@
       <c r="L657" s="3" t="n"/>
       <c r="M657" s="3" t="n"/>
       <c r="N657" s="3" t="n"/>
-      <c r="O657" s="3" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="3" t="n"/>
@@ -11757,7 +11076,6 @@
       <c r="L658" s="3" t="n"/>
       <c r="M658" s="3" t="n"/>
       <c r="N658" s="3" t="n"/>
-      <c r="O658" s="3" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="3" t="n"/>
@@ -11774,7 +11092,6 @@
       <c r="L659" s="3" t="n"/>
       <c r="M659" s="3" t="n"/>
       <c r="N659" s="3" t="n"/>
-      <c r="O659" s="3" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="3" t="n"/>
@@ -11791,7 +11108,6 @@
       <c r="L660" s="3" t="n"/>
       <c r="M660" s="3" t="n"/>
       <c r="N660" s="3" t="n"/>
-      <c r="O660" s="3" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="3" t="n"/>
@@ -11808,7 +11124,6 @@
       <c r="L661" s="3" t="n"/>
       <c r="M661" s="3" t="n"/>
       <c r="N661" s="3" t="n"/>
-      <c r="O661" s="3" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="3" t="n"/>
@@ -11825,7 +11140,6 @@
       <c r="L662" s="3" t="n"/>
       <c r="M662" s="3" t="n"/>
       <c r="N662" s="3" t="n"/>
-      <c r="O662" s="3" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="3" t="n"/>
@@ -11842,7 +11156,6 @@
       <c r="L663" s="3" t="n"/>
       <c r="M663" s="3" t="n"/>
       <c r="N663" s="3" t="n"/>
-      <c r="O663" s="3" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="3" t="n"/>
@@ -11859,7 +11172,6 @@
       <c r="L664" s="3" t="n"/>
       <c r="M664" s="3" t="n"/>
       <c r="N664" s="3" t="n"/>
-      <c r="O664" s="3" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="3" t="n"/>
@@ -11876,7 +11188,6 @@
       <c r="L665" s="3" t="n"/>
       <c r="M665" s="3" t="n"/>
       <c r="N665" s="3" t="n"/>
-      <c r="O665" s="3" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="3" t="n"/>
@@ -11893,7 +11204,6 @@
       <c r="L666" s="3" t="n"/>
       <c r="M666" s="3" t="n"/>
       <c r="N666" s="3" t="n"/>
-      <c r="O666" s="3" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="3" t="n"/>
@@ -11910,7 +11220,6 @@
       <c r="L667" s="3" t="n"/>
       <c r="M667" s="3" t="n"/>
       <c r="N667" s="3" t="n"/>
-      <c r="O667" s="3" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="3" t="n"/>
@@ -11927,7 +11236,6 @@
       <c r="L668" s="3" t="n"/>
       <c r="M668" s="3" t="n"/>
       <c r="N668" s="3" t="n"/>
-      <c r="O668" s="3" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="3" t="n"/>
@@ -11944,7 +11252,6 @@
       <c r="L669" s="3" t="n"/>
       <c r="M669" s="3" t="n"/>
       <c r="N669" s="3" t="n"/>
-      <c r="O669" s="3" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="3" t="n"/>
@@ -11961,7 +11268,6 @@
       <c r="L670" s="3" t="n"/>
       <c r="M670" s="3" t="n"/>
       <c r="N670" s="3" t="n"/>
-      <c r="O670" s="3" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="3" t="n"/>
@@ -11978,7 +11284,6 @@
       <c r="L671" s="3" t="n"/>
       <c r="M671" s="3" t="n"/>
       <c r="N671" s="3" t="n"/>
-      <c r="O671" s="3" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="3" t="n"/>
@@ -11995,7 +11300,6 @@
       <c r="L672" s="3" t="n"/>
       <c r="M672" s="3" t="n"/>
       <c r="N672" s="3" t="n"/>
-      <c r="O672" s="3" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="3" t="n"/>
@@ -12012,7 +11316,6 @@
       <c r="L673" s="3" t="n"/>
       <c r="M673" s="3" t="n"/>
       <c r="N673" s="3" t="n"/>
-      <c r="O673" s="3" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="3" t="n"/>
@@ -12029,7 +11332,6 @@
       <c r="L674" s="3" t="n"/>
       <c r="M674" s="3" t="n"/>
       <c r="N674" s="3" t="n"/>
-      <c r="O674" s="3" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="3" t="n"/>
@@ -12046,7 +11348,6 @@
       <c r="L675" s="3" t="n"/>
       <c r="M675" s="3" t="n"/>
       <c r="N675" s="3" t="n"/>
-      <c r="O675" s="3" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="3" t="n"/>
@@ -12063,7 +11364,6 @@
       <c r="L676" s="3" t="n"/>
       <c r="M676" s="3" t="n"/>
       <c r="N676" s="3" t="n"/>
-      <c r="O676" s="3" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="3" t="n"/>
@@ -12080,7 +11380,6 @@
       <c r="L677" s="3" t="n"/>
       <c r="M677" s="3" t="n"/>
       <c r="N677" s="3" t="n"/>
-      <c r="O677" s="3" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="3" t="n"/>
@@ -12097,7 +11396,6 @@
       <c r="L678" s="3" t="n"/>
       <c r="M678" s="3" t="n"/>
       <c r="N678" s="3" t="n"/>
-      <c r="O678" s="3" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="3" t="n"/>
@@ -12114,7 +11412,6 @@
       <c r="L679" s="3" t="n"/>
       <c r="M679" s="3" t="n"/>
       <c r="N679" s="3" t="n"/>
-      <c r="O679" s="3" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="3" t="n"/>
@@ -12131,7 +11428,6 @@
       <c r="L680" s="3" t="n"/>
       <c r="M680" s="3" t="n"/>
       <c r="N680" s="3" t="n"/>
-      <c r="O680" s="3" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="3" t="n"/>
@@ -12148,7 +11444,6 @@
       <c r="L681" s="3" t="n"/>
       <c r="M681" s="3" t="n"/>
       <c r="N681" s="3" t="n"/>
-      <c r="O681" s="3" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="3" t="n"/>
@@ -12165,7 +11460,6 @@
       <c r="L682" s="3" t="n"/>
       <c r="M682" s="3" t="n"/>
       <c r="N682" s="3" t="n"/>
-      <c r="O682" s="3" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="3" t="n"/>
@@ -12182,7 +11476,6 @@
       <c r="L683" s="3" t="n"/>
       <c r="M683" s="3" t="n"/>
       <c r="N683" s="3" t="n"/>
-      <c r="O683" s="3" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="3" t="n"/>
@@ -12199,7 +11492,6 @@
       <c r="L684" s="3" t="n"/>
       <c r="M684" s="3" t="n"/>
       <c r="N684" s="3" t="n"/>
-      <c r="O684" s="3" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="3" t="n"/>
@@ -12216,7 +11508,6 @@
       <c r="L685" s="3" t="n"/>
       <c r="M685" s="3" t="n"/>
       <c r="N685" s="3" t="n"/>
-      <c r="O685" s="3" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="3" t="n"/>
@@ -12233,7 +11524,6 @@
       <c r="L686" s="3" t="n"/>
       <c r="M686" s="3" t="n"/>
       <c r="N686" s="3" t="n"/>
-      <c r="O686" s="3" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="3" t="n"/>
@@ -12250,7 +11540,6 @@
       <c r="L687" s="3" t="n"/>
       <c r="M687" s="3" t="n"/>
       <c r="N687" s="3" t="n"/>
-      <c r="O687" s="3" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="3" t="n"/>
@@ -12267,7 +11556,6 @@
       <c r="L688" s="3" t="n"/>
       <c r="M688" s="3" t="n"/>
       <c r="N688" s="3" t="n"/>
-      <c r="O688" s="3" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="3" t="n"/>
@@ -12284,7 +11572,6 @@
       <c r="L689" s="3" t="n"/>
       <c r="M689" s="3" t="n"/>
       <c r="N689" s="3" t="n"/>
-      <c r="O689" s="3" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="3" t="n"/>
@@ -12301,7 +11588,6 @@
       <c r="L690" s="3" t="n"/>
       <c r="M690" s="3" t="n"/>
       <c r="N690" s="3" t="n"/>
-      <c r="O690" s="3" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="3" t="n"/>
@@ -12318,7 +11604,6 @@
       <c r="L691" s="3" t="n"/>
       <c r="M691" s="3" t="n"/>
       <c r="N691" s="3" t="n"/>
-      <c r="O691" s="3" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="3" t="n"/>
@@ -12335,7 +11620,6 @@
       <c r="L692" s="3" t="n"/>
       <c r="M692" s="3" t="n"/>
       <c r="N692" s="3" t="n"/>
-      <c r="O692" s="3" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="3" t="n"/>
@@ -12352,7 +11636,6 @@
       <c r="L693" s="3" t="n"/>
       <c r="M693" s="3" t="n"/>
       <c r="N693" s="3" t="n"/>
-      <c r="O693" s="3" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="3" t="n"/>
@@ -12369,7 +11652,6 @@
       <c r="L694" s="3" t="n"/>
       <c r="M694" s="3" t="n"/>
       <c r="N694" s="3" t="n"/>
-      <c r="O694" s="3" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="3" t="n"/>
@@ -12386,7 +11668,6 @@
       <c r="L695" s="3" t="n"/>
       <c r="M695" s="3" t="n"/>
       <c r="N695" s="3" t="n"/>
-      <c r="O695" s="3" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="3" t="n"/>
@@ -12403,7 +11684,6 @@
       <c r="L696" s="3" t="n"/>
       <c r="M696" s="3" t="n"/>
       <c r="N696" s="3" t="n"/>
-      <c r="O696" s="3" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="3" t="n"/>
@@ -12420,7 +11700,6 @@
       <c r="L697" s="3" t="n"/>
       <c r="M697" s="3" t="n"/>
       <c r="N697" s="3" t="n"/>
-      <c r="O697" s="3" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="3" t="n"/>
@@ -12437,7 +11716,6 @@
       <c r="L698" s="3" t="n"/>
       <c r="M698" s="3" t="n"/>
       <c r="N698" s="3" t="n"/>
-      <c r="O698" s="3" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="3" t="n"/>
@@ -12454,7 +11732,6 @@
       <c r="L699" s="3" t="n"/>
       <c r="M699" s="3" t="n"/>
       <c r="N699" s="3" t="n"/>
-      <c r="O699" s="3" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="3" t="n"/>
@@ -12471,7 +11748,6 @@
       <c r="L700" s="3" t="n"/>
       <c r="M700" s="3" t="n"/>
       <c r="N700" s="3" t="n"/>
-      <c r="O700" s="3" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="3" t="n"/>
@@ -12488,7 +11764,6 @@
       <c r="L701" s="3" t="n"/>
       <c r="M701" s="3" t="n"/>
       <c r="N701" s="3" t="n"/>
-      <c r="O701" s="3" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="3" t="n"/>
@@ -12505,7 +11780,6 @@
       <c r="L702" s="3" t="n"/>
       <c r="M702" s="3" t="n"/>
       <c r="N702" s="3" t="n"/>
-      <c r="O702" s="3" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="3" t="n"/>
@@ -12522,7 +11796,6 @@
       <c r="L703" s="3" t="n"/>
       <c r="M703" s="3" t="n"/>
       <c r="N703" s="3" t="n"/>
-      <c r="O703" s="3" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="3" t="n"/>
@@ -12539,7 +11812,6 @@
       <c r="L704" s="3" t="n"/>
       <c r="M704" s="3" t="n"/>
       <c r="N704" s="3" t="n"/>
-      <c r="O704" s="3" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="3" t="n"/>
@@ -12556,7 +11828,6 @@
       <c r="L705" s="3" t="n"/>
       <c r="M705" s="3" t="n"/>
       <c r="N705" s="3" t="n"/>
-      <c r="O705" s="3" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="3" t="n"/>
@@ -12573,7 +11844,6 @@
       <c r="L706" s="3" t="n"/>
       <c r="M706" s="3" t="n"/>
       <c r="N706" s="3" t="n"/>
-      <c r="O706" s="3" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="3" t="n"/>
@@ -12590,7 +11860,6 @@
       <c r="L707" s="3" t="n"/>
       <c r="M707" s="3" t="n"/>
       <c r="N707" s="3" t="n"/>
-      <c r="O707" s="3" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="3" t="n"/>
@@ -12607,7 +11876,6 @@
       <c r="L708" s="3" t="n"/>
       <c r="M708" s="3" t="n"/>
       <c r="N708" s="3" t="n"/>
-      <c r="O708" s="3" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="3" t="n"/>
@@ -12624,7 +11892,6 @@
       <c r="L709" s="3" t="n"/>
       <c r="M709" s="3" t="n"/>
       <c r="N709" s="3" t="n"/>
-      <c r="O709" s="3" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="3" t="n"/>
@@ -12641,7 +11908,6 @@
       <c r="L710" s="3" t="n"/>
       <c r="M710" s="3" t="n"/>
       <c r="N710" s="3" t="n"/>
-      <c r="O710" s="3" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="3" t="n"/>
@@ -12658,7 +11924,6 @@
       <c r="L711" s="3" t="n"/>
       <c r="M711" s="3" t="n"/>
       <c r="N711" s="3" t="n"/>
-      <c r="O711" s="3" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="3" t="n"/>
@@ -12675,7 +11940,6 @@
       <c r="L712" s="3" t="n"/>
       <c r="M712" s="3" t="n"/>
       <c r="N712" s="3" t="n"/>
-      <c r="O712" s="3" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="3" t="n"/>
@@ -12692,7 +11956,6 @@
       <c r="L713" s="3" t="n"/>
       <c r="M713" s="3" t="n"/>
       <c r="N713" s="3" t="n"/>
-      <c r="O713" s="3" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="3" t="n"/>
@@ -12709,7 +11972,6 @@
       <c r="L714" s="3" t="n"/>
       <c r="M714" s="3" t="n"/>
       <c r="N714" s="3" t="n"/>
-      <c r="O714" s="3" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="3" t="n"/>
@@ -12726,7 +11988,6 @@
       <c r="L715" s="3" t="n"/>
       <c r="M715" s="3" t="n"/>
       <c r="N715" s="3" t="n"/>
-      <c r="O715" s="3" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="3" t="n"/>
@@ -12743,7 +12004,6 @@
       <c r="L716" s="3" t="n"/>
       <c r="M716" s="3" t="n"/>
       <c r="N716" s="3" t="n"/>
-      <c r="O716" s="3" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="3" t="n"/>
@@ -12760,7 +12020,6 @@
       <c r="L717" s="3" t="n"/>
       <c r="M717" s="3" t="n"/>
       <c r="N717" s="3" t="n"/>
-      <c r="O717" s="3" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="3" t="n"/>
@@ -12777,7 +12036,6 @@
       <c r="L718" s="3" t="n"/>
       <c r="M718" s="3" t="n"/>
       <c r="N718" s="3" t="n"/>
-      <c r="O718" s="3" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="3" t="n"/>
@@ -12794,7 +12052,6 @@
       <c r="L719" s="3" t="n"/>
       <c r="M719" s="3" t="n"/>
       <c r="N719" s="3" t="n"/>
-      <c r="O719" s="3" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="3" t="n"/>
@@ -12811,7 +12068,6 @@
       <c r="L720" s="3" t="n"/>
       <c r="M720" s="3" t="n"/>
       <c r="N720" s="3" t="n"/>
-      <c r="O720" s="3" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="3" t="n"/>
@@ -12828,7 +12084,6 @@
       <c r="L721" s="3" t="n"/>
       <c r="M721" s="3" t="n"/>
       <c r="N721" s="3" t="n"/>
-      <c r="O721" s="3" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="3" t="n"/>
@@ -12845,7 +12100,6 @@
       <c r="L722" s="3" t="n"/>
       <c r="M722" s="3" t="n"/>
       <c r="N722" s="3" t="n"/>
-      <c r="O722" s="3" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="3" t="n"/>
@@ -12862,7 +12116,6 @@
       <c r="L723" s="3" t="n"/>
       <c r="M723" s="3" t="n"/>
       <c r="N723" s="3" t="n"/>
-      <c r="O723" s="3" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="3" t="n"/>
@@ -12879,7 +12132,6 @@
       <c r="L724" s="3" t="n"/>
       <c r="M724" s="3" t="n"/>
       <c r="N724" s="3" t="n"/>
-      <c r="O724" s="3" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="3" t="n"/>
@@ -12896,7 +12148,6 @@
       <c r="L725" s="3" t="n"/>
       <c r="M725" s="3" t="n"/>
       <c r="N725" s="3" t="n"/>
-      <c r="O725" s="3" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="3" t="n"/>
@@ -12913,7 +12164,6 @@
       <c r="L726" s="3" t="n"/>
       <c r="M726" s="3" t="n"/>
       <c r="N726" s="3" t="n"/>
-      <c r="O726" s="3" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="3" t="n"/>
@@ -12930,7 +12180,6 @@
       <c r="L727" s="3" t="n"/>
       <c r="M727" s="3" t="n"/>
       <c r="N727" s="3" t="n"/>
-      <c r="O727" s="3" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="3" t="n"/>
@@ -12947,7 +12196,6 @@
       <c r="L728" s="3" t="n"/>
       <c r="M728" s="3" t="n"/>
       <c r="N728" s="3" t="n"/>
-      <c r="O728" s="3" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="3" t="n"/>
@@ -12964,7 +12212,6 @@
       <c r="L729" s="3" t="n"/>
       <c r="M729" s="3" t="n"/>
       <c r="N729" s="3" t="n"/>
-      <c r="O729" s="3" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="3" t="n"/>
@@ -12981,7 +12228,6 @@
       <c r="L730" s="3" t="n"/>
       <c r="M730" s="3" t="n"/>
       <c r="N730" s="3" t="n"/>
-      <c r="O730" s="3" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="3" t="n"/>
@@ -12998,7 +12244,6 @@
       <c r="L731" s="3" t="n"/>
       <c r="M731" s="3" t="n"/>
       <c r="N731" s="3" t="n"/>
-      <c r="O731" s="3" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="3" t="n"/>
@@ -13015,7 +12260,6 @@
       <c r="L732" s="3" t="n"/>
       <c r="M732" s="3" t="n"/>
       <c r="N732" s="3" t="n"/>
-      <c r="O732" s="3" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="3" t="n"/>
@@ -13032,7 +12276,6 @@
       <c r="L733" s="3" t="n"/>
       <c r="M733" s="3" t="n"/>
       <c r="N733" s="3" t="n"/>
-      <c r="O733" s="3" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="3" t="n"/>
@@ -13049,7 +12292,6 @@
       <c r="L734" s="3" t="n"/>
       <c r="M734" s="3" t="n"/>
       <c r="N734" s="3" t="n"/>
-      <c r="O734" s="3" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="3" t="n"/>
@@ -13066,7 +12308,6 @@
       <c r="L735" s="3" t="n"/>
       <c r="M735" s="3" t="n"/>
       <c r="N735" s="3" t="n"/>
-      <c r="O735" s="3" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="3" t="n"/>
@@ -13083,7 +12324,6 @@
       <c r="L736" s="3" t="n"/>
       <c r="M736" s="3" t="n"/>
       <c r="N736" s="3" t="n"/>
-      <c r="O736" s="3" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="3" t="n"/>
@@ -13100,7 +12340,6 @@
       <c r="L737" s="3" t="n"/>
       <c r="M737" s="3" t="n"/>
       <c r="N737" s="3" t="n"/>
-      <c r="O737" s="3" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="3" t="n"/>
@@ -13117,7 +12356,6 @@
       <c r="L738" s="3" t="n"/>
       <c r="M738" s="3" t="n"/>
       <c r="N738" s="3" t="n"/>
-      <c r="O738" s="3" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="3" t="n"/>
@@ -13134,7 +12372,6 @@
       <c r="L739" s="3" t="n"/>
       <c r="M739" s="3" t="n"/>
       <c r="N739" s="3" t="n"/>
-      <c r="O739" s="3" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="3" t="n"/>
@@ -13151,7 +12388,6 @@
       <c r="L740" s="3" t="n"/>
       <c r="M740" s="3" t="n"/>
       <c r="N740" s="3" t="n"/>
-      <c r="O740" s="3" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="3" t="n"/>
@@ -13168,7 +12404,6 @@
       <c r="L741" s="3" t="n"/>
       <c r="M741" s="3" t="n"/>
       <c r="N741" s="3" t="n"/>
-      <c r="O741" s="3" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="3" t="n"/>
@@ -13185,7 +12420,6 @@
       <c r="L742" s="3" t="n"/>
       <c r="M742" s="3" t="n"/>
       <c r="N742" s="3" t="n"/>
-      <c r="O742" s="3" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="3" t="n"/>
@@ -13202,7 +12436,6 @@
       <c r="L743" s="3" t="n"/>
       <c r="M743" s="3" t="n"/>
       <c r="N743" s="3" t="n"/>
-      <c r="O743" s="3" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="3" t="n"/>
@@ -13219,7 +12452,6 @@
       <c r="L744" s="3" t="n"/>
       <c r="M744" s="3" t="n"/>
       <c r="N744" s="3" t="n"/>
-      <c r="O744" s="3" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="3" t="n"/>
@@ -13236,7 +12468,6 @@
       <c r="L745" s="3" t="n"/>
       <c r="M745" s="3" t="n"/>
       <c r="N745" s="3" t="n"/>
-      <c r="O745" s="3" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="3" t="n"/>
@@ -13253,7 +12484,6 @@
       <c r="L746" s="3" t="n"/>
       <c r="M746" s="3" t="n"/>
       <c r="N746" s="3" t="n"/>
-      <c r="O746" s="3" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="3" t="n"/>
@@ -13270,7 +12500,6 @@
       <c r="L747" s="3" t="n"/>
       <c r="M747" s="3" t="n"/>
       <c r="N747" s="3" t="n"/>
-      <c r="O747" s="3" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="3" t="n"/>
@@ -13287,7 +12516,6 @@
       <c r="L748" s="3" t="n"/>
       <c r="M748" s="3" t="n"/>
       <c r="N748" s="3" t="n"/>
-      <c r="O748" s="3" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="3" t="n"/>
@@ -13304,7 +12532,6 @@
       <c r="L749" s="3" t="n"/>
       <c r="M749" s="3" t="n"/>
       <c r="N749" s="3" t="n"/>
-      <c r="O749" s="3" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="3" t="n"/>
@@ -13321,7 +12548,6 @@
       <c r="L750" s="3" t="n"/>
       <c r="M750" s="3" t="n"/>
       <c r="N750" s="3" t="n"/>
-      <c r="O750" s="3" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="3" t="n"/>
@@ -13338,7 +12564,6 @@
       <c r="L751" s="3" t="n"/>
       <c r="M751" s="3" t="n"/>
       <c r="N751" s="3" t="n"/>
-      <c r="O751" s="3" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="3" t="n"/>
@@ -13355,7 +12580,6 @@
       <c r="L752" s="3" t="n"/>
       <c r="M752" s="3" t="n"/>
       <c r="N752" s="3" t="n"/>
-      <c r="O752" s="3" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="3" t="n"/>
@@ -13372,7 +12596,6 @@
       <c r="L753" s="3" t="n"/>
       <c r="M753" s="3" t="n"/>
       <c r="N753" s="3" t="n"/>
-      <c r="O753" s="3" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="3" t="n"/>
@@ -13389,7 +12612,6 @@
       <c r="L754" s="3" t="n"/>
       <c r="M754" s="3" t="n"/>
       <c r="N754" s="3" t="n"/>
-      <c r="O754" s="3" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="3" t="n"/>
@@ -13406,7 +12628,6 @@
       <c r="L755" s="3" t="n"/>
       <c r="M755" s="3" t="n"/>
       <c r="N755" s="3" t="n"/>
-      <c r="O755" s="3" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="3" t="n"/>
@@ -13423,7 +12644,6 @@
       <c r="L756" s="3" t="n"/>
       <c r="M756" s="3" t="n"/>
       <c r="N756" s="3" t="n"/>
-      <c r="O756" s="3" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="3" t="n"/>
@@ -13440,7 +12660,6 @@
       <c r="L757" s="3" t="n"/>
       <c r="M757" s="3" t="n"/>
       <c r="N757" s="3" t="n"/>
-      <c r="O757" s="3" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="3" t="n"/>
@@ -13457,7 +12676,6 @@
       <c r="L758" s="3" t="n"/>
       <c r="M758" s="3" t="n"/>
       <c r="N758" s="3" t="n"/>
-      <c r="O758" s="3" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="3" t="n"/>
@@ -13474,7 +12692,6 @@
       <c r="L759" s="3" t="n"/>
       <c r="M759" s="3" t="n"/>
       <c r="N759" s="3" t="n"/>
-      <c r="O759" s="3" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="3" t="n"/>
@@ -13491,7 +12708,6 @@
       <c r="L760" s="3" t="n"/>
       <c r="M760" s="3" t="n"/>
       <c r="N760" s="3" t="n"/>
-      <c r="O760" s="3" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="3" t="n"/>
@@ -13508,7 +12724,6 @@
       <c r="L761" s="3" t="n"/>
       <c r="M761" s="3" t="n"/>
       <c r="N761" s="3" t="n"/>
-      <c r="O761" s="3" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="3" t="n"/>
@@ -13525,7 +12740,6 @@
       <c r="L762" s="3" t="n"/>
       <c r="M762" s="3" t="n"/>
       <c r="N762" s="3" t="n"/>
-      <c r="O762" s="3" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="3" t="n"/>
@@ -13542,7 +12756,6 @@
       <c r="L763" s="3" t="n"/>
       <c r="M763" s="3" t="n"/>
       <c r="N763" s="3" t="n"/>
-      <c r="O763" s="3" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="3" t="n"/>
@@ -13559,7 +12772,6 @@
       <c r="L764" s="3" t="n"/>
       <c r="M764" s="3" t="n"/>
       <c r="N764" s="3" t="n"/>
-      <c r="O764" s="3" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="3" t="n"/>
@@ -13576,7 +12788,6 @@
       <c r="L765" s="3" t="n"/>
       <c r="M765" s="3" t="n"/>
       <c r="N765" s="3" t="n"/>
-      <c r="O765" s="3" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="3" t="n"/>
@@ -13593,7 +12804,6 @@
       <c r="L766" s="3" t="n"/>
       <c r="M766" s="3" t="n"/>
       <c r="N766" s="3" t="n"/>
-      <c r="O766" s="3" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="3" t="n"/>
@@ -13610,7 +12820,6 @@
       <c r="L767" s="3" t="n"/>
       <c r="M767" s="3" t="n"/>
       <c r="N767" s="3" t="n"/>
-      <c r="O767" s="3" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="3" t="n"/>
@@ -13627,7 +12836,6 @@
       <c r="L768" s="3" t="n"/>
       <c r="M768" s="3" t="n"/>
       <c r="N768" s="3" t="n"/>
-      <c r="O768" s="3" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="3" t="n"/>
@@ -13644,7 +12852,6 @@
       <c r="L769" s="3" t="n"/>
       <c r="M769" s="3" t="n"/>
       <c r="N769" s="3" t="n"/>
-      <c r="O769" s="3" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="3" t="n"/>
@@ -13661,7 +12868,6 @@
       <c r="L770" s="3" t="n"/>
       <c r="M770" s="3" t="n"/>
       <c r="N770" s="3" t="n"/>
-      <c r="O770" s="3" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="3" t="n"/>
@@ -13678,7 +12884,6 @@
       <c r="L771" s="3" t="n"/>
       <c r="M771" s="3" t="n"/>
       <c r="N771" s="3" t="n"/>
-      <c r="O771" s="3" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="3" t="n"/>
@@ -13695,7 +12900,6 @@
       <c r="L772" s="3" t="n"/>
       <c r="M772" s="3" t="n"/>
       <c r="N772" s="3" t="n"/>
-      <c r="O772" s="3" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="3" t="n"/>
@@ -13712,7 +12916,6 @@
       <c r="L773" s="3" t="n"/>
       <c r="M773" s="3" t="n"/>
       <c r="N773" s="3" t="n"/>
-      <c r="O773" s="3" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="3" t="n"/>
@@ -13729,7 +12932,6 @@
       <c r="L774" s="3" t="n"/>
       <c r="M774" s="3" t="n"/>
       <c r="N774" s="3" t="n"/>
-      <c r="O774" s="3" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="3" t="n"/>
@@ -13746,7 +12948,6 @@
       <c r="L775" s="3" t="n"/>
       <c r="M775" s="3" t="n"/>
       <c r="N775" s="3" t="n"/>
-      <c r="O775" s="3" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="3" t="n"/>
@@ -13763,7 +12964,6 @@
       <c r="L776" s="3" t="n"/>
       <c r="M776" s="3" t="n"/>
       <c r="N776" s="3" t="n"/>
-      <c r="O776" s="3" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="3" t="n"/>
@@ -13780,7 +12980,6 @@
       <c r="L777" s="3" t="n"/>
       <c r="M777" s="3" t="n"/>
       <c r="N777" s="3" t="n"/>
-      <c r="O777" s="3" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="3" t="n"/>
@@ -13797,7 +12996,6 @@
       <c r="L778" s="3" t="n"/>
       <c r="M778" s="3" t="n"/>
       <c r="N778" s="3" t="n"/>
-      <c r="O778" s="3" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="3" t="n"/>
@@ -13814,7 +13012,6 @@
       <c r="L779" s="3" t="n"/>
       <c r="M779" s="3" t="n"/>
       <c r="N779" s="3" t="n"/>
-      <c r="O779" s="3" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="3" t="n"/>
@@ -13831,7 +13028,6 @@
       <c r="L780" s="3" t="n"/>
       <c r="M780" s="3" t="n"/>
       <c r="N780" s="3" t="n"/>
-      <c r="O780" s="3" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="3" t="n"/>
@@ -13848,7 +13044,6 @@
       <c r="L781" s="3" t="n"/>
       <c r="M781" s="3" t="n"/>
       <c r="N781" s="3" t="n"/>
-      <c r="O781" s="3" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="3" t="n"/>
@@ -13865,7 +13060,6 @@
       <c r="L782" s="3" t="n"/>
       <c r="M782" s="3" t="n"/>
       <c r="N782" s="3" t="n"/>
-      <c r="O782" s="3" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="3" t="n"/>
@@ -13882,7 +13076,6 @@
       <c r="L783" s="3" t="n"/>
       <c r="M783" s="3" t="n"/>
       <c r="N783" s="3" t="n"/>
-      <c r="O783" s="3" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="3" t="n"/>
@@ -13899,7 +13092,6 @@
       <c r="L784" s="3" t="n"/>
       <c r="M784" s="3" t="n"/>
       <c r="N784" s="3" t="n"/>
-      <c r="O784" s="3" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="3" t="n"/>
@@ -13916,7 +13108,6 @@
       <c r="L785" s="3" t="n"/>
       <c r="M785" s="3" t="n"/>
       <c r="N785" s="3" t="n"/>
-      <c r="O785" s="3" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="3" t="n"/>
@@ -13933,7 +13124,6 @@
       <c r="L786" s="3" t="n"/>
       <c r="M786" s="3" t="n"/>
       <c r="N786" s="3" t="n"/>
-      <c r="O786" s="3" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="3" t="n"/>
@@ -13950,7 +13140,6 @@
       <c r="L787" s="3" t="n"/>
       <c r="M787" s="3" t="n"/>
       <c r="N787" s="3" t="n"/>
-      <c r="O787" s="3" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="3" t="n"/>
@@ -13967,7 +13156,6 @@
       <c r="L788" s="3" t="n"/>
       <c r="M788" s="3" t="n"/>
       <c r="N788" s="3" t="n"/>
-      <c r="O788" s="3" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="3" t="n"/>
@@ -13984,7 +13172,6 @@
       <c r="L789" s="3" t="n"/>
       <c r="M789" s="3" t="n"/>
       <c r="N789" s="3" t="n"/>
-      <c r="O789" s="3" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="3" t="n"/>
@@ -14001,7 +13188,6 @@
       <c r="L790" s="3" t="n"/>
       <c r="M790" s="3" t="n"/>
       <c r="N790" s="3" t="n"/>
-      <c r="O790" s="3" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="3" t="n"/>
@@ -14018,7 +13204,6 @@
       <c r="L791" s="3" t="n"/>
       <c r="M791" s="3" t="n"/>
       <c r="N791" s="3" t="n"/>
-      <c r="O791" s="3" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="3" t="n"/>
@@ -14035,7 +13220,6 @@
       <c r="L792" s="3" t="n"/>
       <c r="M792" s="3" t="n"/>
       <c r="N792" s="3" t="n"/>
-      <c r="O792" s="3" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="3" t="n"/>
@@ -14052,7 +13236,6 @@
       <c r="L793" s="3" t="n"/>
       <c r="M793" s="3" t="n"/>
       <c r="N793" s="3" t="n"/>
-      <c r="O793" s="3" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="3" t="n"/>
@@ -14069,7 +13252,6 @@
       <c r="L794" s="3" t="n"/>
       <c r="M794" s="3" t="n"/>
       <c r="N794" s="3" t="n"/>
-      <c r="O794" s="3" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="3" t="n"/>
@@ -14086,7 +13268,6 @@
       <c r="L795" s="3" t="n"/>
       <c r="M795" s="3" t="n"/>
       <c r="N795" s="3" t="n"/>
-      <c r="O795" s="3" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="3" t="n"/>
@@ -14103,7 +13284,6 @@
       <c r="L796" s="3" t="n"/>
       <c r="M796" s="3" t="n"/>
       <c r="N796" s="3" t="n"/>
-      <c r="O796" s="3" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="3" t="n"/>
@@ -14120,7 +13300,6 @@
       <c r="L797" s="3" t="n"/>
       <c r="M797" s="3" t="n"/>
       <c r="N797" s="3" t="n"/>
-      <c r="O797" s="3" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="3" t="n"/>
@@ -14137,7 +13316,6 @@
       <c r="L798" s="3" t="n"/>
       <c r="M798" s="3" t="n"/>
       <c r="N798" s="3" t="n"/>
-      <c r="O798" s="3" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="3" t="n"/>
@@ -14154,7 +13332,6 @@
       <c r="L799" s="3" t="n"/>
       <c r="M799" s="3" t="n"/>
       <c r="N799" s="3" t="n"/>
-      <c r="O799" s="3" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="3" t="n"/>
@@ -14171,7 +13348,6 @@
       <c r="L800" s="3" t="n"/>
       <c r="M800" s="3" t="n"/>
       <c r="N800" s="3" t="n"/>
-      <c r="O800" s="3" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="3" t="n"/>
@@ -14188,7 +13364,6 @@
       <c r="L801" s="3" t="n"/>
       <c r="M801" s="3" t="n"/>
       <c r="N801" s="3" t="n"/>
-      <c r="O801" s="3" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="3" t="n"/>
@@ -14205,7 +13380,6 @@
       <c r="L802" s="3" t="n"/>
       <c r="M802" s="3" t="n"/>
       <c r="N802" s="3" t="n"/>
-      <c r="O802" s="3" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="3" t="n"/>
@@ -14222,7 +13396,6 @@
       <c r="L803" s="3" t="n"/>
       <c r="M803" s="3" t="n"/>
       <c r="N803" s="3" t="n"/>
-      <c r="O803" s="3" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="3" t="n"/>
@@ -14239,7 +13412,6 @@
       <c r="L804" s="3" t="n"/>
       <c r="M804" s="3" t="n"/>
       <c r="N804" s="3" t="n"/>
-      <c r="O804" s="3" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="3" t="n"/>
@@ -14256,7 +13428,6 @@
       <c r="L805" s="3" t="n"/>
       <c r="M805" s="3" t="n"/>
       <c r="N805" s="3" t="n"/>
-      <c r="O805" s="3" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="3" t="n"/>
@@ -14273,7 +13444,6 @@
       <c r="L806" s="3" t="n"/>
       <c r="M806" s="3" t="n"/>
       <c r="N806" s="3" t="n"/>
-      <c r="O806" s="3" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="3" t="n"/>
@@ -14290,7 +13460,6 @@
       <c r="L807" s="3" t="n"/>
       <c r="M807" s="3" t="n"/>
       <c r="N807" s="3" t="n"/>
-      <c r="O807" s="3" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="3" t="n"/>
@@ -14307,7 +13476,6 @@
       <c r="L808" s="3" t="n"/>
       <c r="M808" s="3" t="n"/>
       <c r="N808" s="3" t="n"/>
-      <c r="O808" s="3" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="3" t="n"/>
@@ -14324,7 +13492,6 @@
       <c r="L809" s="3" t="n"/>
       <c r="M809" s="3" t="n"/>
       <c r="N809" s="3" t="n"/>
-      <c r="O809" s="3" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="3" t="n"/>
@@ -14341,7 +13508,6 @@
       <c r="L810" s="3" t="n"/>
       <c r="M810" s="3" t="n"/>
       <c r="N810" s="3" t="n"/>
-      <c r="O810" s="3" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="3" t="n"/>
@@ -14358,7 +13524,6 @@
       <c r="L811" s="3" t="n"/>
       <c r="M811" s="3" t="n"/>
       <c r="N811" s="3" t="n"/>
-      <c r="O811" s="3" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="3" t="n"/>
@@ -14375,7 +13540,6 @@
       <c r="L812" s="3" t="n"/>
       <c r="M812" s="3" t="n"/>
       <c r="N812" s="3" t="n"/>
-      <c r="O812" s="3" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="3" t="n"/>
@@ -14392,7 +13556,6 @@
       <c r="L813" s="3" t="n"/>
       <c r="M813" s="3" t="n"/>
       <c r="N813" s="3" t="n"/>
-      <c r="O813" s="3" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="3" t="n"/>
@@ -14409,7 +13572,6 @@
       <c r="L814" s="3" t="n"/>
       <c r="M814" s="3" t="n"/>
       <c r="N814" s="3" t="n"/>
-      <c r="O814" s="3" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="3" t="n"/>
@@ -14426,7 +13588,6 @@
       <c r="L815" s="3" t="n"/>
       <c r="M815" s="3" t="n"/>
       <c r="N815" s="3" t="n"/>
-      <c r="O815" s="3" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="3" t="n"/>
@@ -14443,7 +13604,6 @@
       <c r="L816" s="3" t="n"/>
       <c r="M816" s="3" t="n"/>
       <c r="N816" s="3" t="n"/>
-      <c r="O816" s="3" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="3" t="n"/>
@@ -14460,7 +13620,6 @@
       <c r="L817" s="3" t="n"/>
       <c r="M817" s="3" t="n"/>
       <c r="N817" s="3" t="n"/>
-      <c r="O817" s="3" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="3" t="n"/>
@@ -14477,7 +13636,6 @@
       <c r="L818" s="3" t="n"/>
       <c r="M818" s="3" t="n"/>
       <c r="N818" s="3" t="n"/>
-      <c r="O818" s="3" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="3" t="n"/>
@@ -14494,7 +13652,6 @@
       <c r="L819" s="3" t="n"/>
       <c r="M819" s="3" t="n"/>
       <c r="N819" s="3" t="n"/>
-      <c r="O819" s="3" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="3" t="n"/>
@@ -14511,7 +13668,6 @@
       <c r="L820" s="3" t="n"/>
       <c r="M820" s="3" t="n"/>
       <c r="N820" s="3" t="n"/>
-      <c r="O820" s="3" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="3" t="n"/>
@@ -14528,7 +13684,6 @@
       <c r="L821" s="3" t="n"/>
       <c r="M821" s="3" t="n"/>
       <c r="N821" s="3" t="n"/>
-      <c r="O821" s="3" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="3" t="n"/>
@@ -14545,7 +13700,6 @@
       <c r="L822" s="3" t="n"/>
       <c r="M822" s="3" t="n"/>
       <c r="N822" s="3" t="n"/>
-      <c r="O822" s="3" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="3" t="n"/>
@@ -14562,7 +13716,6 @@
       <c r="L823" s="3" t="n"/>
       <c r="M823" s="3" t="n"/>
       <c r="N823" s="3" t="n"/>
-      <c r="O823" s="3" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="3" t="n"/>
@@ -14579,7 +13732,6 @@
       <c r="L824" s="3" t="n"/>
       <c r="M824" s="3" t="n"/>
       <c r="N824" s="3" t="n"/>
-      <c r="O824" s="3" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="3" t="n"/>
@@ -14596,7 +13748,6 @@
       <c r="L825" s="3" t="n"/>
       <c r="M825" s="3" t="n"/>
       <c r="N825" s="3" t="n"/>
-      <c r="O825" s="3" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="3" t="n"/>
@@ -14613,7 +13764,6 @@
       <c r="L826" s="3" t="n"/>
       <c r="M826" s="3" t="n"/>
       <c r="N826" s="3" t="n"/>
-      <c r="O826" s="3" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="3" t="n"/>
@@ -14630,7 +13780,6 @@
       <c r="L827" s="3" t="n"/>
       <c r="M827" s="3" t="n"/>
       <c r="N827" s="3" t="n"/>
-      <c r="O827" s="3" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="3" t="n"/>
@@ -14647,7 +13796,6 @@
       <c r="L828" s="3" t="n"/>
       <c r="M828" s="3" t="n"/>
       <c r="N828" s="3" t="n"/>
-      <c r="O828" s="3" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="3" t="n"/>
@@ -14664,7 +13812,6 @@
       <c r="L829" s="3" t="n"/>
       <c r="M829" s="3" t="n"/>
       <c r="N829" s="3" t="n"/>
-      <c r="O829" s="3" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="3" t="n"/>
@@ -14681,7 +13828,6 @@
       <c r="L830" s="3" t="n"/>
       <c r="M830" s="3" t="n"/>
       <c r="N830" s="3" t="n"/>
-      <c r="O830" s="3" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="3" t="n"/>
@@ -14698,7 +13844,6 @@
       <c r="L831" s="3" t="n"/>
       <c r="M831" s="3" t="n"/>
       <c r="N831" s="3" t="n"/>
-      <c r="O831" s="3" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="3" t="n"/>
@@ -14715,7 +13860,6 @@
       <c r="L832" s="3" t="n"/>
       <c r="M832" s="3" t="n"/>
       <c r="N832" s="3" t="n"/>
-      <c r="O832" s="3" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="3" t="n"/>
@@ -14732,7 +13876,6 @@
       <c r="L833" s="3" t="n"/>
       <c r="M833" s="3" t="n"/>
       <c r="N833" s="3" t="n"/>
-      <c r="O833" s="3" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="3" t="n"/>
@@ -14749,7 +13892,6 @@
       <c r="L834" s="3" t="n"/>
       <c r="M834" s="3" t="n"/>
       <c r="N834" s="3" t="n"/>
-      <c r="O834" s="3" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="3" t="n"/>
@@ -14766,7 +13908,6 @@
       <c r="L835" s="3" t="n"/>
       <c r="M835" s="3" t="n"/>
       <c r="N835" s="3" t="n"/>
-      <c r="O835" s="3" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="3" t="n"/>
@@ -14783,7 +13924,6 @@
       <c r="L836" s="3" t="n"/>
       <c r="M836" s="3" t="n"/>
       <c r="N836" s="3" t="n"/>
-      <c r="O836" s="3" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="3" t="n"/>
@@ -14800,7 +13940,6 @@
       <c r="L837" s="3" t="n"/>
       <c r="M837" s="3" t="n"/>
       <c r="N837" s="3" t="n"/>
-      <c r="O837" s="3" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="3" t="n"/>
@@ -14817,7 +13956,6 @@
       <c r="L838" s="3" t="n"/>
       <c r="M838" s="3" t="n"/>
       <c r="N838" s="3" t="n"/>
-      <c r="O838" s="3" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="3" t="n"/>
@@ -14834,7 +13972,6 @@
       <c r="L839" s="3" t="n"/>
       <c r="M839" s="3" t="n"/>
       <c r="N839" s="3" t="n"/>
-      <c r="O839" s="3" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="3" t="n"/>
@@ -14851,7 +13988,6 @@
       <c r="L840" s="3" t="n"/>
       <c r="M840" s="3" t="n"/>
       <c r="N840" s="3" t="n"/>
-      <c r="O840" s="3" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="3" t="n"/>
@@ -14868,7 +14004,6 @@
       <c r="L841" s="3" t="n"/>
       <c r="M841" s="3" t="n"/>
       <c r="N841" s="3" t="n"/>
-      <c r="O841" s="3" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="3" t="n"/>
@@ -14885,7 +14020,6 @@
       <c r="L842" s="3" t="n"/>
       <c r="M842" s="3" t="n"/>
       <c r="N842" s="3" t="n"/>
-      <c r="O842" s="3" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="3" t="n"/>
@@ -14902,7 +14036,6 @@
       <c r="L843" s="3" t="n"/>
       <c r="M843" s="3" t="n"/>
       <c r="N843" s="3" t="n"/>
-      <c r="O843" s="3" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="3" t="n"/>
@@ -14919,7 +14052,6 @@
       <c r="L844" s="3" t="n"/>
       <c r="M844" s="3" t="n"/>
       <c r="N844" s="3" t="n"/>
-      <c r="O844" s="3" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="3" t="n"/>
@@ -14936,7 +14068,6 @@
       <c r="L845" s="3" t="n"/>
       <c r="M845" s="3" t="n"/>
       <c r="N845" s="3" t="n"/>
-      <c r="O845" s="3" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="3" t="n"/>
@@ -14953,7 +14084,6 @@
       <c r="L846" s="3" t="n"/>
       <c r="M846" s="3" t="n"/>
       <c r="N846" s="3" t="n"/>
-      <c r="O846" s="3" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="3" t="n"/>
@@ -14970,7 +14100,6 @@
       <c r="L847" s="3" t="n"/>
       <c r="M847" s="3" t="n"/>
       <c r="N847" s="3" t="n"/>
-      <c r="O847" s="3" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="3" t="n"/>
@@ -14987,7 +14116,6 @@
       <c r="L848" s="3" t="n"/>
       <c r="M848" s="3" t="n"/>
       <c r="N848" s="3" t="n"/>
-      <c r="O848" s="3" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="3" t="n"/>
@@ -15004,7 +14132,6 @@
       <c r="L849" s="3" t="n"/>
       <c r="M849" s="3" t="n"/>
       <c r="N849" s="3" t="n"/>
-      <c r="O849" s="3" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="3" t="n"/>
@@ -15021,7 +14148,6 @@
       <c r="L850" s="3" t="n"/>
       <c r="M850" s="3" t="n"/>
       <c r="N850" s="3" t="n"/>
-      <c r="O850" s="3" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="3" t="n"/>
@@ -15038,7 +14164,6 @@
       <c r="L851" s="3" t="n"/>
       <c r="M851" s="3" t="n"/>
       <c r="N851" s="3" t="n"/>
-      <c r="O851" s="3" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="3" t="n"/>
@@ -15055,7 +14180,6 @@
       <c r="L852" s="3" t="n"/>
       <c r="M852" s="3" t="n"/>
       <c r="N852" s="3" t="n"/>
-      <c r="O852" s="3" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="3" t="n"/>
@@ -15072,7 +14196,6 @@
       <c r="L853" s="3" t="n"/>
       <c r="M853" s="3" t="n"/>
       <c r="N853" s="3" t="n"/>
-      <c r="O853" s="3" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="3" t="n"/>
@@ -15089,7 +14212,6 @@
       <c r="L854" s="3" t="n"/>
       <c r="M854" s="3" t="n"/>
       <c r="N854" s="3" t="n"/>
-      <c r="O854" s="3" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="3" t="n"/>
@@ -15106,7 +14228,6 @@
       <c r="L855" s="3" t="n"/>
       <c r="M855" s="3" t="n"/>
       <c r="N855" s="3" t="n"/>
-      <c r="O855" s="3" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="3" t="n"/>
@@ -15123,7 +14244,6 @@
       <c r="L856" s="3" t="n"/>
       <c r="M856" s="3" t="n"/>
       <c r="N856" s="3" t="n"/>
-      <c r="O856" s="3" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="3" t="n"/>
@@ -15140,7 +14260,6 @@
       <c r="L857" s="3" t="n"/>
       <c r="M857" s="3" t="n"/>
       <c r="N857" s="3" t="n"/>
-      <c r="O857" s="3" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="3" t="n"/>
@@ -15157,7 +14276,6 @@
       <c r="L858" s="3" t="n"/>
       <c r="M858" s="3" t="n"/>
       <c r="N858" s="3" t="n"/>
-      <c r="O858" s="3" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="3" t="n"/>
@@ -15174,7 +14292,6 @@
       <c r="L859" s="3" t="n"/>
       <c r="M859" s="3" t="n"/>
       <c r="N859" s="3" t="n"/>
-      <c r="O859" s="3" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="3" t="n"/>
@@ -15191,7 +14308,6 @@
       <c r="L860" s="3" t="n"/>
       <c r="M860" s="3" t="n"/>
       <c r="N860" s="3" t="n"/>
-      <c r="O860" s="3" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="3" t="n"/>
@@ -15208,7 +14324,6 @@
       <c r="L861" s="3" t="n"/>
       <c r="M861" s="3" t="n"/>
       <c r="N861" s="3" t="n"/>
-      <c r="O861" s="3" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="3" t="n"/>
@@ -15225,7 +14340,6 @@
       <c r="L862" s="3" t="n"/>
       <c r="M862" s="3" t="n"/>
       <c r="N862" s="3" t="n"/>
-      <c r="O862" s="3" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="3" t="n"/>
@@ -15242,7 +14356,6 @@
       <c r="L863" s="3" t="n"/>
       <c r="M863" s="3" t="n"/>
       <c r="N863" s="3" t="n"/>
-      <c r="O863" s="3" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="3" t="n"/>
@@ -15259,7 +14372,6 @@
       <c r="L864" s="3" t="n"/>
       <c r="M864" s="3" t="n"/>
       <c r="N864" s="3" t="n"/>
-      <c r="O864" s="3" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="3" t="n"/>
@@ -15276,7 +14388,6 @@
       <c r="L865" s="3" t="n"/>
       <c r="M865" s="3" t="n"/>
       <c r="N865" s="3" t="n"/>
-      <c r="O865" s="3" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="3" t="n"/>
@@ -15293,7 +14404,6 @@
       <c r="L866" s="3" t="n"/>
       <c r="M866" s="3" t="n"/>
       <c r="N866" s="3" t="n"/>
-      <c r="O866" s="3" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="3" t="n"/>
@@ -15310,7 +14420,6 @@
       <c r="L867" s="3" t="n"/>
       <c r="M867" s="3" t="n"/>
       <c r="N867" s="3" t="n"/>
-      <c r="O867" s="3" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="3" t="n"/>
@@ -15327,7 +14436,6 @@
       <c r="L868" s="3" t="n"/>
       <c r="M868" s="3" t="n"/>
       <c r="N868" s="3" t="n"/>
-      <c r="O868" s="3" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="3" t="n"/>
@@ -15344,7 +14452,6 @@
       <c r="L869" s="3" t="n"/>
       <c r="M869" s="3" t="n"/>
       <c r="N869" s="3" t="n"/>
-      <c r="O869" s="3" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="3" t="n"/>
@@ -15361,7 +14468,6 @@
       <c r="L870" s="3" t="n"/>
       <c r="M870" s="3" t="n"/>
       <c r="N870" s="3" t="n"/>
-      <c r="O870" s="3" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="3" t="n"/>
@@ -15378,7 +14484,6 @@
       <c r="L871" s="3" t="n"/>
       <c r="M871" s="3" t="n"/>
       <c r="N871" s="3" t="n"/>
-      <c r="O871" s="3" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="3" t="n"/>
@@ -15395,7 +14500,6 @@
       <c r="L872" s="3" t="n"/>
       <c r="M872" s="3" t="n"/>
       <c r="N872" s="3" t="n"/>
-      <c r="O872" s="3" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="3" t="n"/>
@@ -15412,7 +14516,6 @@
       <c r="L873" s="3" t="n"/>
       <c r="M873" s="3" t="n"/>
       <c r="N873" s="3" t="n"/>
-      <c r="O873" s="3" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="3" t="n"/>
@@ -15429,7 +14532,6 @@
       <c r="L874" s="3" t="n"/>
       <c r="M874" s="3" t="n"/>
       <c r="N874" s="3" t="n"/>
-      <c r="O874" s="3" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="3" t="n"/>
@@ -15446,7 +14548,6 @@
       <c r="L875" s="3" t="n"/>
       <c r="M875" s="3" t="n"/>
       <c r="N875" s="3" t="n"/>
-      <c r="O875" s="3" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="3" t="n"/>
@@ -15463,7 +14564,6 @@
       <c r="L876" s="3" t="n"/>
       <c r="M876" s="3" t="n"/>
       <c r="N876" s="3" t="n"/>
-      <c r="O876" s="3" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="3" t="n"/>
@@ -15480,7 +14580,6 @@
       <c r="L877" s="3" t="n"/>
       <c r="M877" s="3" t="n"/>
       <c r="N877" s="3" t="n"/>
-      <c r="O877" s="3" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="3" t="n"/>
@@ -15497,7 +14596,6 @@
       <c r="L878" s="3" t="n"/>
       <c r="M878" s="3" t="n"/>
       <c r="N878" s="3" t="n"/>
-      <c r="O878" s="3" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="3" t="n"/>
@@ -15514,7 +14612,6 @@
       <c r="L879" s="3" t="n"/>
       <c r="M879" s="3" t="n"/>
       <c r="N879" s="3" t="n"/>
-      <c r="O879" s="3" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="3" t="n"/>
@@ -15531,7 +14628,6 @@
       <c r="L880" s="3" t="n"/>
       <c r="M880" s="3" t="n"/>
       <c r="N880" s="3" t="n"/>
-      <c r="O880" s="3" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="3" t="n"/>
@@ -15548,7 +14644,6 @@
       <c r="L881" s="3" t="n"/>
       <c r="M881" s="3" t="n"/>
       <c r="N881" s="3" t="n"/>
-      <c r="O881" s="3" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="3" t="n"/>
@@ -15565,7 +14660,6 @@
       <c r="L882" s="3" t="n"/>
       <c r="M882" s="3" t="n"/>
       <c r="N882" s="3" t="n"/>
-      <c r="O882" s="3" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="3" t="n"/>
@@ -15582,7 +14676,6 @@
       <c r="L883" s="3" t="n"/>
       <c r="M883" s="3" t="n"/>
       <c r="N883" s="3" t="n"/>
-      <c r="O883" s="3" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="3" t="n"/>
@@ -15599,7 +14692,6 @@
       <c r="L884" s="3" t="n"/>
       <c r="M884" s="3" t="n"/>
       <c r="N884" s="3" t="n"/>
-      <c r="O884" s="3" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="3" t="n"/>
@@ -15616,7 +14708,6 @@
       <c r="L885" s="3" t="n"/>
       <c r="M885" s="3" t="n"/>
       <c r="N885" s="3" t="n"/>
-      <c r="O885" s="3" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="3" t="n"/>
@@ -15633,7 +14724,6 @@
       <c r="L886" s="3" t="n"/>
       <c r="M886" s="3" t="n"/>
       <c r="N886" s="3" t="n"/>
-      <c r="O886" s="3" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="3" t="n"/>
@@ -15650,7 +14740,6 @@
       <c r="L887" s="3" t="n"/>
       <c r="M887" s="3" t="n"/>
       <c r="N887" s="3" t="n"/>
-      <c r="O887" s="3" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="3" t="n"/>
@@ -15667,7 +14756,6 @@
       <c r="L888" s="3" t="n"/>
       <c r="M888" s="3" t="n"/>
       <c r="N888" s="3" t="n"/>
-      <c r="O888" s="3" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="3" t="n"/>
@@ -15684,7 +14772,6 @@
       <c r="L889" s="3" t="n"/>
       <c r="M889" s="3" t="n"/>
       <c r="N889" s="3" t="n"/>
-      <c r="O889" s="3" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="3" t="n"/>
@@ -15701,7 +14788,6 @@
       <c r="L890" s="3" t="n"/>
       <c r="M890" s="3" t="n"/>
       <c r="N890" s="3" t="n"/>
-      <c r="O890" s="3" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="3" t="n"/>
@@ -15718,7 +14804,6 @@
       <c r="L891" s="3" t="n"/>
       <c r="M891" s="3" t="n"/>
       <c r="N891" s="3" t="n"/>
-      <c r="O891" s="3" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="3" t="n"/>
@@ -15735,7 +14820,6 @@
       <c r="L892" s="3" t="n"/>
       <c r="M892" s="3" t="n"/>
       <c r="N892" s="3" t="n"/>
-      <c r="O892" s="3" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="3" t="n"/>
@@ -15752,7 +14836,6 @@
       <c r="L893" s="3" t="n"/>
       <c r="M893" s="3" t="n"/>
       <c r="N893" s="3" t="n"/>
-      <c r="O893" s="3" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="3" t="n"/>
@@ -15769,7 +14852,6 @@
       <c r="L894" s="3" t="n"/>
       <c r="M894" s="3" t="n"/>
       <c r="N894" s="3" t="n"/>
-      <c r="O894" s="3" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="3" t="n"/>
@@ -15786,7 +14868,6 @@
       <c r="L895" s="3" t="n"/>
       <c r="M895" s="3" t="n"/>
       <c r="N895" s="3" t="n"/>
-      <c r="O895" s="3" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="3" t="n"/>
@@ -15803,7 +14884,6 @@
       <c r="L896" s="3" t="n"/>
       <c r="M896" s="3" t="n"/>
       <c r="N896" s="3" t="n"/>
-      <c r="O896" s="3" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="3" t="n"/>
@@ -15820,7 +14900,6 @@
       <c r="L897" s="3" t="n"/>
       <c r="M897" s="3" t="n"/>
       <c r="N897" s="3" t="n"/>
-      <c r="O897" s="3" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="3" t="n"/>
@@ -15837,7 +14916,6 @@
       <c r="L898" s="3" t="n"/>
       <c r="M898" s="3" t="n"/>
       <c r="N898" s="3" t="n"/>
-      <c r="O898" s="3" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="3" t="n"/>
@@ -15854,7 +14932,6 @@
       <c r="L899" s="3" t="n"/>
       <c r="M899" s="3" t="n"/>
       <c r="N899" s="3" t="n"/>
-      <c r="O899" s="3" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="3" t="n"/>
@@ -15871,7 +14948,6 @@
       <c r="L900" s="3" t="n"/>
       <c r="M900" s="3" t="n"/>
       <c r="N900" s="3" t="n"/>
-      <c r="O900" s="3" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="3" t="n"/>
@@ -15888,7 +14964,6 @@
       <c r="L901" s="3" t="n"/>
       <c r="M901" s="3" t="n"/>
       <c r="N901" s="3" t="n"/>
-      <c r="O901" s="3" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="3" t="n"/>
@@ -15905,7 +14980,6 @@
       <c r="L902" s="3" t="n"/>
       <c r="M902" s="3" t="n"/>
       <c r="N902" s="3" t="n"/>
-      <c r="O902" s="3" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="3" t="n"/>
@@ -15922,7 +14996,6 @@
       <c r="L903" s="3" t="n"/>
       <c r="M903" s="3" t="n"/>
       <c r="N903" s="3" t="n"/>
-      <c r="O903" s="3" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="3" t="n"/>
@@ -15939,7 +15012,6 @@
       <c r="L904" s="3" t="n"/>
       <c r="M904" s="3" t="n"/>
       <c r="N904" s="3" t="n"/>
-      <c r="O904" s="3" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="3" t="n"/>
@@ -15956,7 +15028,6 @@
       <c r="L905" s="3" t="n"/>
       <c r="M905" s="3" t="n"/>
       <c r="N905" s="3" t="n"/>
-      <c r="O905" s="3" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="3" t="n"/>
@@ -15973,7 +15044,6 @@
       <c r="L906" s="3" t="n"/>
       <c r="M906" s="3" t="n"/>
       <c r="N906" s="3" t="n"/>
-      <c r="O906" s="3" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="3" t="n"/>
@@ -15990,7 +15060,6 @@
       <c r="L907" s="3" t="n"/>
       <c r="M907" s="3" t="n"/>
       <c r="N907" s="3" t="n"/>
-      <c r="O907" s="3" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="3" t="n"/>
@@ -16007,7 +15076,6 @@
       <c r="L908" s="3" t="n"/>
       <c r="M908" s="3" t="n"/>
       <c r="N908" s="3" t="n"/>
-      <c r="O908" s="3" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="3" t="n"/>
@@ -16024,7 +15092,6 @@
       <c r="L909" s="3" t="n"/>
       <c r="M909" s="3" t="n"/>
       <c r="N909" s="3" t="n"/>
-      <c r="O909" s="3" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="3" t="n"/>
@@ -16041,7 +15108,6 @@
       <c r="L910" s="3" t="n"/>
       <c r="M910" s="3" t="n"/>
       <c r="N910" s="3" t="n"/>
-      <c r="O910" s="3" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="3" t="n"/>
@@ -16058,7 +15124,6 @@
       <c r="L911" s="3" t="n"/>
       <c r="M911" s="3" t="n"/>
       <c r="N911" s="3" t="n"/>
-      <c r="O911" s="3" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="3" t="n"/>
@@ -16075,7 +15140,6 @@
       <c r="L912" s="3" t="n"/>
       <c r="M912" s="3" t="n"/>
       <c r="N912" s="3" t="n"/>
-      <c r="O912" s="3" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="3" t="n"/>
@@ -16092,7 +15156,6 @@
       <c r="L913" s="3" t="n"/>
       <c r="M913" s="3" t="n"/>
       <c r="N913" s="3" t="n"/>
-      <c r="O913" s="3" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="3" t="n"/>
@@ -16109,7 +15172,6 @@
       <c r="L914" s="3" t="n"/>
       <c r="M914" s="3" t="n"/>
       <c r="N914" s="3" t="n"/>
-      <c r="O914" s="3" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="3" t="n"/>
@@ -16126,7 +15188,6 @@
       <c r="L915" s="3" t="n"/>
       <c r="M915" s="3" t="n"/>
       <c r="N915" s="3" t="n"/>
-      <c r="O915" s="3" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="3" t="n"/>
@@ -16143,7 +15204,6 @@
       <c r="L916" s="3" t="n"/>
       <c r="M916" s="3" t="n"/>
       <c r="N916" s="3" t="n"/>
-      <c r="O916" s="3" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="3" t="n"/>
@@ -16160,7 +15220,6 @@
       <c r="L917" s="3" t="n"/>
       <c r="M917" s="3" t="n"/>
       <c r="N917" s="3" t="n"/>
-      <c r="O917" s="3" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="3" t="n"/>
@@ -16177,7 +15236,6 @@
       <c r="L918" s="3" t="n"/>
       <c r="M918" s="3" t="n"/>
       <c r="N918" s="3" t="n"/>
-      <c r="O918" s="3" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="3" t="n"/>
@@ -16194,7 +15252,6 @@
       <c r="L919" s="3" t="n"/>
       <c r="M919" s="3" t="n"/>
       <c r="N919" s="3" t="n"/>
-      <c r="O919" s="3" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="3" t="n"/>
@@ -16211,7 +15268,6 @@
       <c r="L920" s="3" t="n"/>
       <c r="M920" s="3" t="n"/>
       <c r="N920" s="3" t="n"/>
-      <c r="O920" s="3" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="3" t="n"/>
@@ -16228,7 +15284,6 @@
       <c r="L921" s="3" t="n"/>
       <c r="M921" s="3" t="n"/>
       <c r="N921" s="3" t="n"/>
-      <c r="O921" s="3" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="3" t="n"/>
@@ -16245,7 +15300,6 @@
       <c r="L922" s="3" t="n"/>
       <c r="M922" s="3" t="n"/>
       <c r="N922" s="3" t="n"/>
-      <c r="O922" s="3" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="3" t="n"/>
@@ -16262,7 +15316,6 @@
       <c r="L923" s="3" t="n"/>
       <c r="M923" s="3" t="n"/>
       <c r="N923" s="3" t="n"/>
-      <c r="O923" s="3" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="3" t="n"/>
@@ -16279,7 +15332,6 @@
       <c r="L924" s="3" t="n"/>
       <c r="M924" s="3" t="n"/>
       <c r="N924" s="3" t="n"/>
-      <c r="O924" s="3" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="3" t="n"/>
@@ -16296,7 +15348,6 @@
       <c r="L925" s="3" t="n"/>
       <c r="M925" s="3" t="n"/>
       <c r="N925" s="3" t="n"/>
-      <c r="O925" s="3" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="3" t="n"/>
@@ -16313,7 +15364,6 @@
       <c r="L926" s="3" t="n"/>
       <c r="M926" s="3" t="n"/>
       <c r="N926" s="3" t="n"/>
-      <c r="O926" s="3" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="3" t="n"/>
@@ -16330,7 +15380,6 @@
       <c r="L927" s="3" t="n"/>
       <c r="M927" s="3" t="n"/>
       <c r="N927" s="3" t="n"/>
-      <c r="O927" s="3" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="3" t="n"/>
@@ -16347,7 +15396,6 @@
       <c r="L928" s="3" t="n"/>
       <c r="M928" s="3" t="n"/>
       <c r="N928" s="3" t="n"/>
-      <c r="O928" s="3" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="3" t="n"/>
@@ -16364,7 +15412,6 @@
       <c r="L929" s="3" t="n"/>
       <c r="M929" s="3" t="n"/>
       <c r="N929" s="3" t="n"/>
-      <c r="O929" s="3" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="3" t="n"/>
@@ -16381,7 +15428,6 @@
       <c r="L930" s="3" t="n"/>
       <c r="M930" s="3" t="n"/>
       <c r="N930" s="3" t="n"/>
-      <c r="O930" s="3" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="3" t="n"/>
@@ -16398,7 +15444,6 @@
       <c r="L931" s="3" t="n"/>
       <c r="M931" s="3" t="n"/>
       <c r="N931" s="3" t="n"/>
-      <c r="O931" s="3" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="3" t="n"/>
@@ -16415,7 +15460,6 @@
       <c r="L932" s="3" t="n"/>
       <c r="M932" s="3" t="n"/>
       <c r="N932" s="3" t="n"/>
-      <c r="O932" s="3" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="3" t="n"/>
@@ -16432,7 +15476,6 @@
       <c r="L933" s="3" t="n"/>
       <c r="M933" s="3" t="n"/>
       <c r="N933" s="3" t="n"/>
-      <c r="O933" s="3" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="3" t="n"/>
@@ -16449,7 +15492,6 @@
       <c r="L934" s="3" t="n"/>
       <c r="M934" s="3" t="n"/>
       <c r="N934" s="3" t="n"/>
-      <c r="O934" s="3" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="3" t="n"/>
@@ -16466,7 +15508,6 @@
       <c r="L935" s="3" t="n"/>
       <c r="M935" s="3" t="n"/>
       <c r="N935" s="3" t="n"/>
-      <c r="O935" s="3" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="3" t="n"/>
@@ -16483,7 +15524,6 @@
       <c r="L936" s="3" t="n"/>
       <c r="M936" s="3" t="n"/>
       <c r="N936" s="3" t="n"/>
-      <c r="O936" s="3" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="3" t="n"/>
@@ -16500,7 +15540,6 @@
       <c r="L937" s="3" t="n"/>
       <c r="M937" s="3" t="n"/>
       <c r="N937" s="3" t="n"/>
-      <c r="O937" s="3" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="3" t="n"/>
@@ -16517,7 +15556,6 @@
       <c r="L938" s="3" t="n"/>
       <c r="M938" s="3" t="n"/>
       <c r="N938" s="3" t="n"/>
-      <c r="O938" s="3" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="3" t="n"/>
@@ -16534,7 +15572,6 @@
       <c r="L939" s="3" t="n"/>
       <c r="M939" s="3" t="n"/>
       <c r="N939" s="3" t="n"/>
-      <c r="O939" s="3" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="3" t="n"/>
@@ -16551,7 +15588,6 @@
       <c r="L940" s="3" t="n"/>
       <c r="M940" s="3" t="n"/>
       <c r="N940" s="3" t="n"/>
-      <c r="O940" s="3" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="3" t="n"/>
@@ -16568,7 +15604,6 @@
       <c r="L941" s="3" t="n"/>
       <c r="M941" s="3" t="n"/>
       <c r="N941" s="3" t="n"/>
-      <c r="O941" s="3" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="3" t="n"/>
@@ -16585,7 +15620,6 @@
       <c r="L942" s="3" t="n"/>
       <c r="M942" s="3" t="n"/>
       <c r="N942" s="3" t="n"/>
-      <c r="O942" s="3" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="3" t="n"/>
@@ -16602,7 +15636,6 @@
       <c r="L943" s="3" t="n"/>
       <c r="M943" s="3" t="n"/>
       <c r="N943" s="3" t="n"/>
-      <c r="O943" s="3" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="3" t="n"/>
@@ -16619,7 +15652,6 @@
       <c r="L944" s="3" t="n"/>
       <c r="M944" s="3" t="n"/>
       <c r="N944" s="3" t="n"/>
-      <c r="O944" s="3" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="3" t="n"/>
@@ -16636,7 +15668,6 @@
       <c r="L945" s="3" t="n"/>
       <c r="M945" s="3" t="n"/>
       <c r="N945" s="3" t="n"/>
-      <c r="O945" s="3" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="3" t="n"/>
@@ -16653,7 +15684,6 @@
       <c r="L946" s="3" t="n"/>
       <c r="M946" s="3" t="n"/>
       <c r="N946" s="3" t="n"/>
-      <c r="O946" s="3" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="3" t="n"/>
@@ -16670,7 +15700,6 @@
       <c r="L947" s="3" t="n"/>
       <c r="M947" s="3" t="n"/>
       <c r="N947" s="3" t="n"/>
-      <c r="O947" s="3" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="3" t="n"/>
@@ -16687,7 +15716,6 @@
       <c r="L948" s="3" t="n"/>
       <c r="M948" s="3" t="n"/>
       <c r="N948" s="3" t="n"/>
-      <c r="O948" s="3" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="3" t="n"/>
@@ -16704,7 +15732,6 @@
       <c r="L949" s="3" t="n"/>
       <c r="M949" s="3" t="n"/>
       <c r="N949" s="3" t="n"/>
-      <c r="O949" s="3" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="3" t="n"/>
@@ -16721,7 +15748,6 @@
       <c r="L950" s="3" t="n"/>
       <c r="M950" s="3" t="n"/>
       <c r="N950" s="3" t="n"/>
-      <c r="O950" s="3" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="3" t="n"/>
@@ -16738,7 +15764,6 @@
       <c r="L951" s="3" t="n"/>
       <c r="M951" s="3" t="n"/>
       <c r="N951" s="3" t="n"/>
-      <c r="O951" s="3" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="3" t="n"/>
@@ -16755,7 +15780,6 @@
       <c r="L952" s="3" t="n"/>
       <c r="M952" s="3" t="n"/>
       <c r="N952" s="3" t="n"/>
-      <c r="O952" s="3" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="3" t="n"/>
@@ -16772,7 +15796,6 @@
       <c r="L953" s="3" t="n"/>
       <c r="M953" s="3" t="n"/>
       <c r="N953" s="3" t="n"/>
-      <c r="O953" s="3" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="3" t="n"/>
@@ -16789,7 +15812,6 @@
       <c r="L954" s="3" t="n"/>
       <c r="M954" s="3" t="n"/>
       <c r="N954" s="3" t="n"/>
-      <c r="O954" s="3" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="3" t="n"/>
@@ -16806,7 +15828,6 @@
       <c r="L955" s="3" t="n"/>
       <c r="M955" s="3" t="n"/>
       <c r="N955" s="3" t="n"/>
-      <c r="O955" s="3" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="3" t="n"/>
@@ -16823,7 +15844,6 @@
       <c r="L956" s="3" t="n"/>
       <c r="M956" s="3" t="n"/>
       <c r="N956" s="3" t="n"/>
-      <c r="O956" s="3" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="3" t="n"/>
@@ -16840,7 +15860,6 @@
       <c r="L957" s="3" t="n"/>
       <c r="M957" s="3" t="n"/>
       <c r="N957" s="3" t="n"/>
-      <c r="O957" s="3" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="3" t="n"/>
@@ -16857,7 +15876,6 @@
       <c r="L958" s="3" t="n"/>
       <c r="M958" s="3" t="n"/>
       <c r="N958" s="3" t="n"/>
-      <c r="O958" s="3" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="3" t="n"/>
@@ -16874,7 +15892,6 @@
       <c r="L959" s="3" t="n"/>
       <c r="M959" s="3" t="n"/>
       <c r="N959" s="3" t="n"/>
-      <c r="O959" s="3" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="3" t="n"/>
@@ -16891,7 +15908,6 @@
       <c r="L960" s="3" t="n"/>
       <c r="M960" s="3" t="n"/>
       <c r="N960" s="3" t="n"/>
-      <c r="O960" s="3" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="3" t="n"/>
@@ -16908,7 +15924,6 @@
       <c r="L961" s="3" t="n"/>
       <c r="M961" s="3" t="n"/>
       <c r="N961" s="3" t="n"/>
-      <c r="O961" s="3" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="3" t="n"/>
@@ -16925,7 +15940,6 @@
       <c r="L962" s="3" t="n"/>
       <c r="M962" s="3" t="n"/>
       <c r="N962" s="3" t="n"/>
-      <c r="O962" s="3" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="3" t="n"/>
@@ -16942,7 +15956,6 @@
       <c r="L963" s="3" t="n"/>
       <c r="M963" s="3" t="n"/>
       <c r="N963" s="3" t="n"/>
-      <c r="O963" s="3" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="3" t="n"/>
@@ -16959,7 +15972,6 @@
       <c r="L964" s="3" t="n"/>
       <c r="M964" s="3" t="n"/>
       <c r="N964" s="3" t="n"/>
-      <c r="O964" s="3" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="3" t="n"/>
@@ -16976,7 +15988,6 @@
       <c r="L965" s="3" t="n"/>
       <c r="M965" s="3" t="n"/>
       <c r="N965" s="3" t="n"/>
-      <c r="O965" s="3" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="3" t="n"/>
@@ -16993,7 +16004,6 @@
       <c r="L966" s="3" t="n"/>
       <c r="M966" s="3" t="n"/>
       <c r="N966" s="3" t="n"/>
-      <c r="O966" s="3" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="3" t="n"/>
@@ -17010,7 +16020,6 @@
       <c r="L967" s="3" t="n"/>
       <c r="M967" s="3" t="n"/>
       <c r="N967" s="3" t="n"/>
-      <c r="O967" s="3" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="3" t="n"/>
@@ -17027,7 +16036,6 @@
       <c r="L968" s="3" t="n"/>
       <c r="M968" s="3" t="n"/>
       <c r="N968" s="3" t="n"/>
-      <c r="O968" s="3" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="3" t="n"/>
@@ -17044,7 +16052,6 @@
       <c r="L969" s="3" t="n"/>
       <c r="M969" s="3" t="n"/>
       <c r="N969" s="3" t="n"/>
-      <c r="O969" s="3" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="3" t="n"/>
@@ -17061,7 +16068,6 @@
       <c r="L970" s="3" t="n"/>
       <c r="M970" s="3" t="n"/>
       <c r="N970" s="3" t="n"/>
-      <c r="O970" s="3" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="3" t="n"/>
@@ -17078,7 +16084,6 @@
       <c r="L971" s="3" t="n"/>
       <c r="M971" s="3" t="n"/>
       <c r="N971" s="3" t="n"/>
-      <c r="O971" s="3" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="3" t="n"/>
@@ -17095,7 +16100,6 @@
       <c r="L972" s="3" t="n"/>
       <c r="M972" s="3" t="n"/>
       <c r="N972" s="3" t="n"/>
-      <c r="O972" s="3" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="3" t="n"/>
@@ -17112,7 +16116,6 @@
       <c r="L973" s="3" t="n"/>
       <c r="M973" s="3" t="n"/>
       <c r="N973" s="3" t="n"/>
-      <c r="O973" s="3" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="3" t="n"/>
@@ -17129,7 +16132,6 @@
       <c r="L974" s="3" t="n"/>
       <c r="M974" s="3" t="n"/>
       <c r="N974" s="3" t="n"/>
-      <c r="O974" s="3" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="3" t="n"/>
@@ -17146,7 +16148,6 @@
       <c r="L975" s="3" t="n"/>
       <c r="M975" s="3" t="n"/>
       <c r="N975" s="3" t="n"/>
-      <c r="O975" s="3" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="3" t="n"/>
@@ -17163,7 +16164,6 @@
       <c r="L976" s="3" t="n"/>
       <c r="M976" s="3" t="n"/>
       <c r="N976" s="3" t="n"/>
-      <c r="O976" s="3" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="3" t="n"/>
@@ -17180,7 +16180,6 @@
       <c r="L977" s="3" t="n"/>
       <c r="M977" s="3" t="n"/>
       <c r="N977" s="3" t="n"/>
-      <c r="O977" s="3" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="3" t="n"/>
@@ -17197,7 +16196,6 @@
       <c r="L978" s="3" t="n"/>
       <c r="M978" s="3" t="n"/>
       <c r="N978" s="3" t="n"/>
-      <c r="O978" s="3" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="3" t="n"/>
@@ -17214,7 +16212,6 @@
       <c r="L979" s="3" t="n"/>
       <c r="M979" s="3" t="n"/>
       <c r="N979" s="3" t="n"/>
-      <c r="O979" s="3" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="3" t="n"/>
@@ -17231,7 +16228,6 @@
       <c r="L980" s="3" t="n"/>
       <c r="M980" s="3" t="n"/>
       <c r="N980" s="3" t="n"/>
-      <c r="O980" s="3" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="3" t="n"/>
@@ -17248,7 +16244,6 @@
       <c r="L981" s="3" t="n"/>
       <c r="M981" s="3" t="n"/>
       <c r="N981" s="3" t="n"/>
-      <c r="O981" s="3" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="3" t="n"/>
@@ -17265,7 +16260,6 @@
       <c r="L982" s="3" t="n"/>
       <c r="M982" s="3" t="n"/>
       <c r="N982" s="3" t="n"/>
-      <c r="O982" s="3" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="3" t="n"/>
@@ -17282,7 +16276,6 @@
       <c r="L983" s="3" t="n"/>
       <c r="M983" s="3" t="n"/>
       <c r="N983" s="3" t="n"/>
-      <c r="O983" s="3" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="3" t="n"/>
@@ -17299,7 +16292,6 @@
       <c r="L984" s="3" t="n"/>
       <c r="M984" s="3" t="n"/>
       <c r="N984" s="3" t="n"/>
-      <c r="O984" s="3" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="3" t="n"/>
@@ -17316,7 +16308,6 @@
       <c r="L985" s="3" t="n"/>
       <c r="M985" s="3" t="n"/>
       <c r="N985" s="3" t="n"/>
-      <c r="O985" s="3" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="3" t="n"/>
@@ -17333,7 +16324,6 @@
       <c r="L986" s="3" t="n"/>
       <c r="M986" s="3" t="n"/>
       <c r="N986" s="3" t="n"/>
-      <c r="O986" s="3" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="3" t="n"/>
@@ -17350,7 +16340,6 @@
       <c r="L987" s="3" t="n"/>
       <c r="M987" s="3" t="n"/>
       <c r="N987" s="3" t="n"/>
-      <c r="O987" s="3" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="3" t="n"/>
@@ -17367,7 +16356,6 @@
       <c r="L988" s="3" t="n"/>
       <c r="M988" s="3" t="n"/>
       <c r="N988" s="3" t="n"/>
-      <c r="O988" s="3" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="3" t="n"/>
@@ -17384,7 +16372,6 @@
       <c r="L989" s="3" t="n"/>
       <c r="M989" s="3" t="n"/>
       <c r="N989" s="3" t="n"/>
-      <c r="O989" s="3" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="3" t="n"/>
@@ -17401,7 +16388,6 @@
       <c r="L990" s="3" t="n"/>
       <c r="M990" s="3" t="n"/>
       <c r="N990" s="3" t="n"/>
-      <c r="O990" s="3" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="3" t="n"/>
@@ -17418,7 +16404,6 @@
       <c r="L991" s="3" t="n"/>
       <c r="M991" s="3" t="n"/>
       <c r="N991" s="3" t="n"/>
-      <c r="O991" s="3" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="3" t="n"/>
@@ -17435,7 +16420,6 @@
       <c r="L992" s="3" t="n"/>
       <c r="M992" s="3" t="n"/>
       <c r="N992" s="3" t="n"/>
-      <c r="O992" s="3" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="3" t="n"/>
@@ -17452,7 +16436,6 @@
       <c r="L993" s="3" t="n"/>
       <c r="M993" s="3" t="n"/>
       <c r="N993" s="3" t="n"/>
-      <c r="O993" s="3" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="3" t="n"/>
@@ -17469,7 +16452,6 @@
       <c r="L994" s="3" t="n"/>
       <c r="M994" s="3" t="n"/>
       <c r="N994" s="3" t="n"/>
-      <c r="O994" s="3" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="3" t="n"/>
@@ -17486,7 +16468,6 @@
       <c r="L995" s="3" t="n"/>
       <c r="M995" s="3" t="n"/>
       <c r="N995" s="3" t="n"/>
-      <c r="O995" s="3" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="3" t="n"/>
@@ -17503,7 +16484,6 @@
       <c r="L996" s="3" t="n"/>
       <c r="M996" s="3" t="n"/>
       <c r="N996" s="3" t="n"/>
-      <c r="O996" s="3" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="3" t="n"/>
@@ -17520,7 +16500,6 @@
       <c r="L997" s="3" t="n"/>
       <c r="M997" s="3" t="n"/>
       <c r="N997" s="3" t="n"/>
-      <c r="O997" s="3" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="3" t="n"/>
@@ -17537,7 +16516,6 @@
       <c r="L998" s="3" t="n"/>
       <c r="M998" s="3" t="n"/>
       <c r="N998" s="3" t="n"/>
-      <c r="O998" s="3" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="3" t="n"/>
@@ -17554,7 +16532,6 @@
       <c r="L999" s="3" t="n"/>
       <c r="M999" s="3" t="n"/>
       <c r="N999" s="3" t="n"/>
-      <c r="O999" s="3" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="3" t="n"/>
@@ -17571,7 +16548,6 @@
       <c r="L1000" s="3" t="n"/>
       <c r="M1000" s="3" t="n"/>
       <c r="N1000" s="3" t="n"/>
-      <c r="O1000" s="3" t="n"/>
     </row>
     <row r="1001">
       <c r="A1001" s="3" t="n"/>
@@ -17588,10 +16564,9 @@
       <c r="L1001" s="3" t="n"/>
       <c r="M1001" s="3" t="n"/>
       <c r="N1001" s="3" t="n"/>
-      <c r="O1001" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:N1"/>
   <dataValidations count="1">
     <dataValidation sqref="I2:I1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick one" error="Use male, female or other (or leave blank)." type="list">
       <formula1>"male,female,other"</formula1>
@@ -17607,7 +16582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B33"/>
+  <dimension ref="B2:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -17765,21 +16740,21 @@
     <row r="26">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>first_name  last_name  mobile      dob         email              gender  school       joining_date  batch          level</t>
+          <t>first_name  last_name  mobile      dob         parent_email        gender  school       joining_date  level</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Aarav       Sharma     9876543210  2014-08-23  aarav@family.in    male    DPS Noida    2026-04-01    MWF Morning</t>
+          <t>Aarav       Sharma     9876543210  2014-08-23  priya@family.in     male    DPS Noida    2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Diya        Kapoor     9812345678  2016-01-09                     female               2026-04-01    TTS Evening    2</t>
+          <t>Diya        Kapoor     9812345678  2016-01-09  raj@family.in       female               2026-04-01    2</t>
         </is>
       </c>
     </row>
@@ -17789,146 +16764,66 @@
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Why 'batch' matters more than it looks</t>
+          <t>Batches are NOT in this sheet</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Attendance registers are built from batch membership. A rider with no batch cannot be</t>
+          <t>Assign riders to a batch after uploading, from the Riders page — select several and</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>marked present, and a coach only sees batches they are assigned to. Filling this column</t>
+          <t>assign in one action. A class name typed here had to match ours character for</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>now saves assigning every rider by hand afterwards.</t>
+          <t>character, which made it the most error-prone cell in the file.</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Centre (upload while signed in here)</t>
+          <t>What happens after you upload</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Batch names — copy EXACTLY</t>
+          <t>Riders are created but HELD — they cannot be put on a register until the indemnity</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="112" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Equiwings Noida</t>
+          <t>and injury NOC are signed. Send the signing link from Riders &gt; Consent Collection;</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Friday batch 1
-Friday batch 2 
-Friday batch 3 
-Tuesday batch 1 
-Tuesday batch 2
-Wednesday batch 1 
-Wednesday batch 2 
-Wednesday batch 3</t>
+          <t>each rider goes active automatically once their parent signs. That link needs an</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="56" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Equiwings Silverline Archery</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>MWF Evening
-MWF Morning
-TTS Evening
-TTS Morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>GHRC Equiwings</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>beginner 
-girls session
-MWF Evening
-SUNDAY 
-SUNDAY MORNING BATCH 
-TTS Evening</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>HPS Hyderabad Equiwings</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>MWF Evening
-MWF Morning
-TTS Evening
-TTS Morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Pathways Aravali Equiwings</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>MWF Evening
-MWF Morning
-TTS Evening
-TTS Morning</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Batch names change — regenerate this file if a club adds one.</t>
+          <t>email address, which is why parent_email is the most important optional column.</t>
         </is>
       </c>
     </row>
